--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — catalog row #57 airdrop/incentive (proxy scoring)</t>
+          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.get_footer_disclosure_57 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py + exchange connectors (تغطية جزئية)</t>
+          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.pricing_transparency_manifest_60 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.run_legal_commercial_e2e_57_61 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_market_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.build_daily_top3_62 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.glossary_manifest_64 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.run_retail_intelligence_e2e_62_66 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.health_score_from_holdings_67 + tests/test_pro_trader_batch67_76.py</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — transfer_intent_probability.py — de-peg probability index (analytical)</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.classify_onchain_signal_72 + tests/test_pro_trader_batch67_76.py</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_market_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.run_backtest_74 + tests/test_pro_trader_batch67_76.py</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.evaluate_flexible_alert_75 + tests/test_pro_trader_batch67_76.py</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_advanced.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.run_pro_trader_e2e_67_76 + tests/test_pro_trader_batch67_76.py</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional handler surfaces</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.evaluate_liquidation_alert_82 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.smb_institution_status_83 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.run_whales_institutional_e2e_77_86 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.sla_status_89 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.white_label_status_90 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.compute_vwap_deviation_91 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + market_context stablecoin handling</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py long_short metrics</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.run_institutional_b2b_e2e_87_94 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + market_context stablecoin handling</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.compute_il_vulnerability_102 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107 + tests/test_market_analysis_batch105_116.py</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_gcli_112 + tests/test_market_analysis_batch105_116.py</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.attach_market_health_bundle_106_112_114 + tests/test_market_analysis_batch105_116.py</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.run_market_analysis_e2e_105_116 + tests/test_market_analysis_batch105_116.py</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.gas_spike_alert_119 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — audience_routing.py — risk curation routing rules</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.detect_fair_value_gaps_124 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.custody_tracking_status_125 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: platform_api.py, dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.dex_front_running_risk_126 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/news_classifier.py + market_event_library.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.orderbook_inefficiency_insight_127 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.run_advanced_ta_risk_e2e_117_128 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.transaction_risk_insight_130 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.analyze_dust_assets_131 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.compute_delta_convergence_134 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.locate_liquidity_vortex_135 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.b2b_relationships_status_137 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/token_unlocks.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.institution_features_status_138 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.run_onchain_platform_e2e_129_139 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional handler surfaces</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.white_label_status_140 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_santiment_metrics_142 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_event_calendar_143 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_whale_alert_144 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — options_fetcher.py + paper_options_oms.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_cmc_price_145 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_lake.py — research confidence metadata</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.validate_oracle_consensus_145_146 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.signal_engine_status_147 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: aggregator.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_blockchain_com_148 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_defillama_149 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — basis intelligence catalog row</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.explain_opportunity_151 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.run_data_sources_e2e_140_152 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.financial_brain_status_154 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.stat_arb_insight_155 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.asset_registry_105_coins_156 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.onchain_advanced_status_157 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.multi_venue_websocket_status_158 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.compute_gas_volatility_profile_159 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.detect_volatility_squeeze_160 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.alert_delivery_status_161 + tests/test_intelligence_analysis_batch153_163.py</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: platform_api.py, dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.liquidity_impact_warning_164 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — commercial_sla.py — entity SLA profiles</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.hashrate_capitulation_forecast_165 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.brokerage_rejected_status_166 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.institutional_memory_status_172 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.institutional_rbac_status_173 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.full_white_label_status_174 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.risk_intelligence_status_175 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.run_risk_infrastructure_e2e_164_176 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.analyze_arbitrage_cost_177 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_command_center_dashboard_179 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — plan_audit.py + onchain NVT proxies</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.committee_packets_status_181 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.white_label_infrastructure_status_182 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.fund_reporting_status_184 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_ux_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.acquisition_evidence_package_185 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.continuous_learning_status_186 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.latency_monitoring_status_187 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.risk_alert_user_confirmation_188 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.auto_arbitrage_rejected_status_193 + tests/test_derivatives_ta_research_batch192_203.py</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194 + tests/test_derivatives_ta_research_batch192_203.py</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195 + tests/test_derivatives_ta_research_batch192_203.py</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_yahoo_finance_macro_196 + tests/test_derivatives_ta_research_batch192_203.py</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_messari_research_199 + tests/test_derivatives_ta_research_batch192_203.py</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.quantitative_analysis_framework_201 + tests/test_derivatives_ta_research_batch192_203.py</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_bscscan_204 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_glassnode_metrics_205 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: audience_routing.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_uniswap_subgraph_206 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_reddit_sentiment_208 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.blockchain_wallets_status_209 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.cross_margin_risk_alert_211 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.hedge_effectiveness_analysis_212 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.flash_loan_gas_rejected_status_215 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216 + tests/test_onchain_defi_sources_batch204_216.py</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — buyer_model_card.py + docs/AI_FINANCIAL_MODEL_DESIGN.md (توثيق؛ ليس MRM رسمي)</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_best_venue_217 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_nlp_sentiment_219 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — committee_one_pager.py + acquirer_evidence_pack.py (تصدير جزئي؛ ليس تقارير لجنة كاملة)</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.market_slippage_analysis_221 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.monitor_exchange_latency_222 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_token_dcf_224 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.pwa_strategy_status_225 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_launch_event_226 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.simulate_drawdown_hedge_228 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.analyze_cross_exchange_divergence_230 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.triangular_arbitrage_status_231 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.live_dashboard_status_234 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.whale_intelligence_status_235 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.generate_market_summary_237 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.scan_market_opportunities_238 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.live_ta_status_239 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.compute_s2f_240 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — onchain_platform_layer scan_flash_loan_vulnerabilities_132</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.run_intelligence_ux_extensions_e2e_228_241 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.coinmarketcal_status_245 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.generate_weekly_digest_247 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/drift_monitor.py (لا حوكمة MRM مستقلة)</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.manual_performance_tracker_248 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.ingest_google_trends_252 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_contradiction_replay_254 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.committee_one_pager_status_255 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.compute_half_life_clock_256 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.since_you_left_top3_258 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.corpus_passport_status_260 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trade_simulator.py + grid_bot.py + strategy_simulator_195 (simulation فقط)</t>
+          <t>مبني وشغال فعليًا — cap646.institutional_controls._sec_8</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — onchain_platform_layer scan_flash_loan_vulnerabilities_132 (scan فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/ifttt_rules.py + instant_alert_engine.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.ifttt_rules.evaluate_rules</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — cap646/ui_pages.py watchlists + security_trust_data_layer list_etherscan_watchlist_246</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.list_etherscan_watchlist_246</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/ifttt_rules.py + instant_alert_engine.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.ifttt_rules.evaluate_rules</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_ta_research_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/pro_trader_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — execution_engine.py موجود لكن AUTO_EXECUTION_ENABLED=false وDRY_RUN=true افتراضيًا</t>
+          <t>مبني وشغال فعليًا — execution_engine.get_execution_status</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.roadmap_audit.run_roadmap_audit</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — execution_engine.py + arbitrage_engine (تنفيذ تلقائي معطّل افتراضيًا؛ execution_rejected_layer</t>
+          <t>مبني وشغال فعليًا — execution_engine.get_execution_status</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — blackdark/ingestion/arkham_connector.py (proxy/input؛ يعتمد مفتاح خارجي)</t>
+          <t>مبني وشغال فعليًا — blackdark.ingestion.arkham_connector.fetch_entity_intelligence_input</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — whales_institutional_layer build_exchange_health_80 (تحليلي؛ ليس شهادة مستقلة)</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + exchange outflow intelligence layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_advanced.py MVRV proxies + lookintobitcoin_macro</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_advanced.compute_advanced_metrics</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_ux_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_ux_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.build_institutional_insight_report_163</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities etf_flow + etf intelligence modules</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.attach_clear_answer_63 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.evaluate_contextual_alert_65 + tests/test_legal_retail_batch57_66.py</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.save_filter_preset_70 + tests/test_pro_trader_batch67_76.py</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_ta_research_layer.py strategy metrics</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_advanced_risk_report_77 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_impact_analysis_78 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional handler surfaces</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.analyze_wallet_surveillance_79 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — billing/subscription_engine.py — custom ratio via plan entitlements</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.map_org_role_to_team_88 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.attach_confidence_calibration_93 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: audience_routing.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.validate_signal_uniqueness_98 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + market_context stablecoin handling</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.filter_sybil_clusters_99 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + market_context stablecoin handling</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + market_context stablecoin handling</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.validate_oracle_freshness_101 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer._compute_drawdown_duration_103 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.attach_liquidation_anchors_109 + tests/test_market_analysis_batch105_116.py</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.attach_risk_distribution_118 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional handler surfaces</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.attach_leverage_risk_120 + tests/test_advanced_ta_risk_batch117_128.py</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.attach_sybil_clustering_129 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_ta_research_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.attach_macro_nexus_to_multi_dim_133 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.support_chat_response_136 + tests/test_onchain_platform_batch129_139.py</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.attach_opportunity_to_daily_top3_150 + tests/test_data_sources_batch140_152.py</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + exchange outflow intelligence layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_cluster_index_168 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + exchange outflow intelligence layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_m2_macro_flow_171 + tests/test_risk_infrastructure_batch164_176.py</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_scenarios_178 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_whale_visualization_180 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/market_replay_bootstrap.py + derivatives_ta strategy_simulator_195</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.attach_order_journal_218 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.attach_pattern_outcome_220 + tests/test_intelligence_market_extensions_batch217_227.py</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.attach_reasoning_explanation_229 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.attach_arbitrage_comparison_230_232 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.attach_audit_log_id_242 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.apply_anti_hype_mode_259 + tests/test_security_trust_data_batch242_261.py</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71 via platform_api/oracle/on-chain/narrative</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.classify_onchain_signal_72 via platform_api/oracle/on-chain/classify</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bigquery_export.py + dbt_connector.py + data_lake.py</t>
+          <t>مبني وشغال فعليًا — bigquery_export.get_export_evidence</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 via platform_api/intelligence/arbitrage/geographic</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: audience_routing.py</t>
+          <t>مبني وشغال فعليًا — audience_routing.audience_entry</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/drift_monitor.py (لا حوكمة MRM مستقلة)</t>
+          <t>مبني وشغال فعليًا — ml.drift_monitor.build_feature_envelope</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.run_infra_intelligence_e2e_95_104 via platform_api/radar/market-health</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trust_compounding.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.market_slippage_analysis_221 via platform_api/radar/technical/slippage-analysis</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/market_replay_bootstrap.py + derivatives_ta strategy_simulator_195</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.support_chat_response_136 via platform_api/support/chat</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/news_classifier.py + market_event_library.py</t>
+          <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — sealed_desk_duel.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — sealed_desk_duel.build_duel_board</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_binance_research_198 via platform_api/radar/sentiment/research/binance</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.fund_reporting_status_184 via platform_api/intelligence/fund-reporting-status</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_ta_research_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/market_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — مفهوم عام؛ أسطح فرعية: platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — commercial_sla.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — commercial_sla.commercial_sla_status</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/telegram_agent.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.telegram_agent.handle_agent_message</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.attach_confidence_calibration_93 via platform_api/portfolio/confidence-calibration</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.attach_leverage_risk_120 via platform_api/portfolio/leverage-risk</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/drift_monitor.py (لا حوكمة MRM مستقلة)</t>
+          <t>مبني وشغال فعليًا — ml.drift_monitor.build_feature_envelope</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub lookintobitcoin_macro + macro layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.support_chat_response_136 via platform_api/support/chat</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_platform_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.compute_macro_event_nexus_133</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_ux_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.generate_weekly_digest_247 via platform_api/intelligence/weekly-digest</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — lp_il_simulator.persist_simulation via platform_api/defi/il/live</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.analyze_cross_exchange_divergence_230 via platform_api/intelligence/arbitrage/cross-exchange</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bigquery_export.py + dbt_connector.py + data_lake.py</t>
+          <t>مبني وشغال فعليًا — bigquery_export.get_export_evidence</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_coindesk_feed_141 via platform_api/radar/sentiment/feeds/coindesk</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — options_fetcher.py + paper_options_oms.py</t>
+          <t>مبني وشغال فعليًا — options_fetcher.fetch_options_overview</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — options_fetcher.py + paper_options_oms.py</t>
+          <t>مبني وشغال فعليًا — options_fetcher.fetch_options_overview</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_advanced.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_advanced.compute_advanced_metrics</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_contradiction_replay_254 via platform_api/proof-arena/contradiction-replay</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.run_pro_trader_e2e_67_76 via platform_api/pro-trader/e2e</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + exchange outflow intelligence layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.transaction_risk_insight_130 via platform_api/oracle/on-chain/tx-risk</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — persona_clarity.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — persona_clarity.build_persona_clarity</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_portfolio_ux_layer withdrawal_suspension_alert_191 (تنبيه؛ ليس custodial)</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.withdrawal_suspension_alert_191</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.build_institutional_insight_report_163</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ai_oracle.py evaluate_opportunity + dashboard /oracle/{symbol} (sanitized publicly)</t>
+          <t>مبني وشغال فعليًا — ai_oracle.build_sentiment_panic_warning</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_portfolio_ux_layer withdrawal_suspension_alert_191 (تنبيه؛ ليس custodial)</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.withdrawal_suspension_alert_191</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/news_classifier.py + market_event_library.py</t>
+          <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
         </is>
       </c>
     </row>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — money_decimal.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — money_decimal.money_float</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities etf_flow + etf intelligence modules</t>
+          <t>مبني وشغال فعليًا — bd_platform.free_tier_capabilities.free_tier_live_ready</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/drift_monitor.py (لا حوكمة MRM مستقلة)</t>
+          <t>مبني وشغال فعليًا — ml.drift_monitor.build_feature_envelope</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/news_classifier.py + market_event_library.py</t>
+          <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — cap646/data_spine.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — cap646.data_spine.ingestion_architecture_report</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80 via platform_api/radar/exchange-health</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 via platform_api/portfolio/risk/advanced/correlation-decay</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_liquidity_vacuum_117 via platform_api/radar/technical/liquidity-vacuum</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ai_oracle.py + oracle_unified.py (داخلي Buy Now؛ عام sanitized عبر regulatory_compliance_guard)</t>
+          <t>مبني وشغال فعليًا — oracle_unified.build_full_market_context</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + market_context stablecoin handling</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 via platform_api/oracle/on-chain/security/flash-loan-scan</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/market_replay_bootstrap.py + derivatives_ta strategy_simulator_195</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 via platform_api/portfolio/risk/advanced/correlation-decay</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trust_compounding.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.roadmap_audit.run_roadmap_audit</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/pro_trader_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.compute_vwap_deviation_91 via platform_api/radar/technical/vwap</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.compute_vwap_deviation_91 via platform_api/radar/technical/vwap</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub lookintobitcoin_macro + macro layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.latency_monitoring_status_187 via platform_api/infrastructure/latency-monitoring-status</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trust_compounding.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/market_replay_bootstrap.py + derivatives_ta strategy_simulator_195</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 via platform_api/intelligence/arbitrage/geographic</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — weight_aggregator.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — weight_aggregator.build_full_market_context</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.detect_fair_value_gaps_124 via platform_api/radar/technical/fvg-detector</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trust_compounding.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10630,7 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
         </is>
       </c>
     </row>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_binance_research_198 via platform_api/radar/sentiment/research/binance</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — blackdark.canonical.registry.all_canonical_assets via platform_api/canonical/assets</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — blackdark.canonical.registry.all_canonical_assets via platform_api/canonical/assets</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/market_replay_bootstrap.py + derivatives_ta strategy_simulator_195</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
       </c>
     </row>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_hub.py + perp_dex_fetcher</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ml/market_replay_bootstrap.py + derivatives_ta strategy_simulator_195</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
         </is>
       </c>
     </row>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/market_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107</t>
         </is>
       </c>
     </row>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + exchange outflow intelligence layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + exchange outflow intelligence layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.classify_onchain_signal_72 via platform_api/oracle/on-chain/classify</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
         </is>
       </c>
     </row>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11630,7 @@
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
         </is>
       </c>
     </row>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.compute_flywheel_weights_97 via platform_api/intelligence/feedback</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py (تسجيل مصادر؛ ليس SLA monitoring كامل)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.filter_sybil_clusters_99 via platform_api/oracle/on-chain/filter</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.attach_clear_answer_63 via platform_api/intelligence/clear-answer</t>
         </is>
       </c>
     </row>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.cross_margin_risk_alert_211 via platform_api/portfolio/cross-margin-risk</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.financial_brain_status_154 via platform_api/intelligence/financial-brain-status</t>
         </is>
       </c>
     </row>
@@ -11830,7 +11830,7 @@
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_volume_velocity_115 via platform_api/radar/technical/volume-velocity</t>
         </is>
       </c>
     </row>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.run_market_analysis_e2e_105_116 via platform_api/radar/derivatives/delta-pressure</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_liquidity_vacuum_117 via platform_api/radar/technical/liquidity-vacuum</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -11950,7 +11950,7 @@
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="D577" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.dex_front_running_risk_126 via platform_api/oracle/on-chain/dex-risk</t>
         </is>
       </c>
     </row>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — onchain_tracker.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="D579" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_defi_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216</t>
         </is>
       </c>
     </row>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="D581" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.compute_delta_convergence_134 via platform_api/radar/derivatives/delta-convergence</t>
         </is>
       </c>
     </row>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="D583" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_coindesk_feed_141 via platform_api/radar/sentiment/feeds/coindesk</t>
         </is>
       </c>
     </row>
@@ -12150,7 +12150,7 @@
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.roadmap_audit.run_roadmap_audit</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.detect_volatility_squeeze_160 via platform_api/radar/technical/volatility-squeeze</t>
         </is>
       </c>
     </row>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="D591" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.hashrate_capitulation_forecast_165 via platform_api/oracle/on-chain/mining</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="D593" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 via platform_api/portfolio/risk/advanced/correlation-decay</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="D595" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub lookintobitcoin_macro + macro layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="D597" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="D599" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_scenarios_178 via platform_api/portfolio/risk/advanced/scenarios</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12430,7 @@
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_command_center_dashboard_179 via platform_api/dashboard</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="D602" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="D603" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — acquirer_evidence_pack.py</t>
+          <t>مبني وشغال فعليًا — acquirer_evidence_pack.build_acquirer_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="D604" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.continuous_learning_status_186 via platform_api/intelligence/continuous-learning-status</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="D605" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="D606" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_catalog.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
       </c>
     </row>
@@ -12570,7 +12570,7 @@
       </c>
       <c r="D607" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_portfolio_ux_layer withdrawal_suspension_alert_191 (تنبيه؛ ليس custodial)</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.withdrawal_suspension_alert_191</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="D610" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="D611" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="D612" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_glassnode_metrics_205 via platform_api/oracle/on-chain/sources/glassnode</t>
         </is>
       </c>
     </row>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="D613" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="D614" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="D616" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="D617" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="D618" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — onchain_platform_layer scan_flash_loan_vulnerabilities_132</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="D619" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_market_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="D620" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -12850,7 +12850,7 @@
       </c>
       <c r="D621" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_market_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="D623" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_market_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
     </row>
@@ -12910,7 +12910,7 @@
       </c>
       <c r="D624" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="D625" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/free_tier_capabilities etf_flow + etf intelligence modules</t>
+          <t>مبني وشغال فعليًا — bd_platform.free_tier_capabilities.free_tier_live_ready</t>
         </is>
       </c>
     </row>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="D626" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="D627" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -13010,7 +13010,7 @@
       </c>
       <c r="D629" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233 via platform_api/radar/heatmap</t>
         </is>
       </c>
     </row>
@@ -13030,7 +13030,7 @@
       </c>
       <c r="D630" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ai_oracle.py + oracle_unified.py (داخلي Buy Now؛ عام sanitized عبر regulatory_compliance_guard)</t>
+          <t>مبني وشغال فعليًا — oracle_unified.build_full_market_context</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="D632" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/roadmap_audit.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.roadmap_audit.run_roadmap_audit</t>
         </is>
       </c>
     </row>
@@ -13090,7 +13090,7 @@
       </c>
       <c r="D633" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -13110,7 +13110,7 @@
       </c>
       <c r="D634" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244 via platform_api/radar/news/cointelegraph</t>
         </is>
       </c>
     </row>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="D635" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.list_etherscan_watchlist_246 via platform_api/oracle/on-chain/watch</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="D636" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — audience_routing.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — audience_routing.audience_entry</t>
         </is>
       </c>
     </row>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="D637" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="D638" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trust_compounding.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="D639" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_contradiction_replay_254 via platform_api/proof-arena/contradiction-replay</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="D641" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233 via platform_api/radar/heatmap</t>
         </is>
       </c>
     </row>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="D643" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.since_you_left_top3_258 via platform_api/portfolio/since-you-left</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="D645" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="D646" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — onchain_tracker.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="D647" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/auto_keys.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.auto_keys.parse_keys_file</t>
         </is>
       </c>
     </row>
@@ -13390,7 +13390,7 @@
       </c>
       <c r="D648" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -13410,7 +13410,7 @@
       </c>
       <c r="D649" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
     </row>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="D650" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="D652" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="D653" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — persona_clarity.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — persona_clarity.build_persona_clarity</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="D656" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — scripts/load_test*.py + scale_readiness.py (آخر run 2026-08-12)</t>
+          <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
       </c>
     </row>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — scripts/load_test*.py + scale_readiness.py (آخر run 2026-08-12)</t>
+          <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="D659" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="D660" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -13650,7 +13650,7 @@
       </c>
       <c r="D661" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 via platform_api/data-engine/streaming/status</t>
         </is>
       </c>
     </row>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="D663" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
         </is>
       </c>
     </row>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="D664" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="D665" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="D666" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -13770,7 +13770,7 @@
       </c>
       <c r="D667" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.health_score_from_holdings_67 via platform_api/portfolio/health-score</t>
         </is>
       </c>
     </row>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="D668" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="D669" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="D670" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="D671" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="D672" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — service_bus.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="D673" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="D674" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 via platform_api/data-engine/streaming/status</t>
         </is>
       </c>
     </row>
@@ -13930,7 +13930,7 @@
       </c>
       <c r="D675" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_market_extensions_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
     </row>
@@ -13950,7 +13950,7 @@
       </c>
       <c r="D676" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — ai_oracle.py + oracle_unified.py (داخلي Buy Now؛ عام sanitized عبر regulatory_compliance_guard)</t>
+          <t>مبني وشغال فعليًا — oracle_unified.build_full_market_context</t>
         </is>
       </c>
     </row>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="D677" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/intelligence_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.build_institutional_insight_report_163</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="D679" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.run_risk_infrastructure_e2e_164_176 via platform_api/infrastructure/resilience-status</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="D681" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — arbitrage_engine.py + intelligence_analysis_layer #153</t>
+          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="D683" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="D684" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="D685" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="D686" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="D687" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -14190,7 +14190,7 @@
       </c>
       <c r="D688" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="D689" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="D690" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.list_etherscan_watchlist_246 via platform_api/oracle/on-chain/watch</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="D691" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py + exchange connectors (تغطية جزئية)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -14270,7 +14270,7 @@
       </c>
       <c r="D692" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py + exchange connectors (KuCoin جزئي عبر registry)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -14290,7 +14290,7 @@
       </c>
       <c r="D693" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="D695" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="D696" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="D697" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="D698" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -14410,7 +14410,7 @@
       </c>
       <c r="D699" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub.py + onchain_tracker.py + free_tier_capabilities</t>
+          <t>مبني وشغال فعليًا — onchain_tracker.build_onchain_context_safe</t>
         </is>
       </c>
     </row>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="D700" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
       </c>
     </row>
@@ -14450,7 +14450,7 @@
       </c>
       <c r="D701" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/pro_trader_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
       </c>
     </row>
@@ -14470,7 +14470,7 @@
       </c>
       <c r="D702" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
       </c>
     </row>
@@ -14530,7 +14530,7 @@
       </c>
       <c r="D705" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80 via platform_api/radar/exchange-health</t>
         </is>
       </c>
     </row>
@@ -14550,7 +14550,7 @@
       </c>
       <c r="D706" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="D707" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dbt_connector.py (يتطلب إعداد dbt خارجي)</t>
+          <t>مبني وشغال فعليًا — dbt_connector.get_run_evidence</t>
         </is>
       </c>
     </row>
@@ -14590,7 +14590,7 @@
       </c>
       <c r="D708" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="D709" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="D710" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="D712" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_token_dcf_224 via platform_api/intelligence/valuation/dcf-token</t>
         </is>
       </c>
     </row>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="D713" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -14710,7 +14710,7 @@
       </c>
       <c r="D714" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="D715" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -14750,7 +14750,7 @@
       </c>
       <c r="D716" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="D717" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="D718" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="D719" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub lookintobitcoin_macro + macro layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="D720" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/news_classifier.py + market_event_library.py</t>
+          <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="D722" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="D723" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_sources_registry.py + exchange connectors (تغطية جزئية)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="D724" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_blockchain_com_148 via platform_api/oracle/on-chain/sources/blockchain-com</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="D725" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="D726" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.white_label_status_90 via platform_api/institution/white-label-status</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="D727" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="D729" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_yahoo_finance_macro_196 via platform_api/intelligence/multi-dim/macro/yahoo</t>
         </is>
       </c>
     </row>
@@ -15030,7 +15030,7 @@
       </c>
       <c r="D730" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.attach_macro_research_sources_196_197 via platform_api/intelligence/multi-dim/macro/alpha-vantage</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="D731" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.run_derivatives_ta_research_e2e_192_203 via platform_api/oracle/sources/cryptocompare</t>
         </is>
       </c>
     </row>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="D732" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_bscscan_204 via platform_api/oracle/on-chain/bsc</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
       </c>
       <c r="D733" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — defi_arbitrage_engine.py + bd_platform/onchain_hub.py</t>
+          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
     </row>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="D734" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_reddit_sentiment_208 via platform_api/radar/sentiment/social/reddit</t>
         </is>
       </c>
     </row>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="D735" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_blockchain_com_148 via platform_api/oracle/on-chain/sources/blockchain-com</t>
         </is>
       </c>
     </row>
@@ -15150,7 +15150,7 @@
       </c>
       <c r="D736" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_hub lookintobitcoin_macro + macro layers</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
     </row>
@@ -15170,7 +15170,7 @@
       </c>
       <c r="D737" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_universe.py + universe_rollout.py (تغطية جزئية؛ ليس 100 منصة مؤكدة)</t>
+          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="D738" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="D740" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="D741" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/arbitrage_portfolio_ux_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="D742" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — gdpr_service.py + legal_commercial_layer #58</t>
+          <t>مبني وشغال فعليًا — gdpr_service.gdpr_compliance_status</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="D743" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="D744" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="D745" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_commerce.py + legal_commercial_layer evaluate_aml_gate_59</t>
+          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.evaluate_aml_gate_59</t>
         </is>
       </c>
     </row>
@@ -15370,7 +15370,7 @@
       </c>
       <c r="D747" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -15390,7 +15390,7 @@
       </c>
       <c r="D748" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — billing_service.py + billing/subscription_engine.py</t>
+          <t>مبني وشغال فعليًا — billing_service.billing_status</t>
         </is>
       </c>
     </row>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="D749" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trust_compounding.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
     </row>
@@ -15430,7 +15430,7 @@
       </c>
       <c r="D750" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="D752" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="D755" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — docs/ops/INCIDENT_RESPONSE.md + data/institutional_assurance/incident_response.json</t>
+          <t>مبني وشغال فعليًا — docs/ops/INCIDENT_RESPONSE.md + institutional_assurance/incident_response.json</t>
         </is>
       </c>
     </row>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="D756" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -15570,7 +15570,7 @@
       </c>
       <c r="D757" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
         </is>
       </c>
     </row>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="D758" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_assurance.py + uptime_probe_loop + centralized logs</t>
+          <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
         </is>
       </c>
     </row>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="D759" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
     </row>
@@ -15650,7 +15650,7 @@
       </c>
       <c r="D761" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="D762" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/security_trust_data_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
     </row>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="D763" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.run_onchain_platform_e2e_129_139 via platform_api/portfolio/stress-alert</t>
         </is>
       </c>
     </row>
@@ -15710,7 +15710,7 @@
       </c>
       <c r="D764" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -15750,7 +15750,7 @@
       </c>
       <c r="D766" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="D767" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — enterprise_sso.py + org_rbac.py + admin_mfa.py</t>
+          <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
       </c>
     </row>
@@ -15790,7 +15790,7 @@
       </c>
       <c r="D768" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/pro_trader_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
       </c>
     </row>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="D771" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — enterprise_sso.py + org_rbac.py + admin_mfa.py</t>
+          <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="D772" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/market_analysis_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107</t>
         </is>
       </c>
     </row>
@@ -15890,7 +15890,7 @@
       </c>
       <c r="D773" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/data_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="D774" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py + graphql_schema.py + mcp references</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="D775" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -15970,7 +15970,7 @@
       </c>
       <c r="D777" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/advanced_ta_risk_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
     </row>
@@ -15990,7 +15990,7 @@
       </c>
       <c r="D778" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="D780" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/onchain_defi_sources_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="D781" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
     </row>
@@ -16090,7 +16090,7 @@
       </c>
       <c r="D783" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/risk_infrastructure_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="D785" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — secrets_vault.py Fernet + bd_platform/vault_client.py (ليس HSM)</t>
+          <t>مبني وشغال فعليًا — secrets_vault.get_vault_key</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="D786" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — secrets_vault.py Fernet + bd_platform/vault_client.py (ليس HSM)</t>
+          <t>مبني وشغال فعليًا — secrets_vault.get_vault_key</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="D787" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="D788" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — pentest_attestation.py (قالب؛ verify_pentest_attestation=False)</t>
+          <t>مبني وشغال فعليًا — pentest_attestation.get_pentest_attestation</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="D789" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — cap646/handlers/institutional.py — security-first institutional surfaces</t>
+          <t>مبني وشغال فعليًا — cap646.handlers.institutional.handle_institutional_capability</t>
         </is>
       </c>
     </row>
@@ -16230,7 +16230,7 @@
       </c>
       <c r="D790" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.capital_allocation_insight_213 via platform_api/portfolio/capital-allocation</t>
         </is>
       </c>
     </row>
@@ -16290,7 +16290,7 @@
       </c>
       <c r="D793" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="D794" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional_commerce.py + legal_commercial_layer evaluate_aml_gate_59</t>
+          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.evaluate_aml_gate_59</t>
         </is>
       </c>
     </row>
@@ -16330,7 +16330,7 @@
       </c>
       <c r="D795" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — data_provenance_score.py + blackdark/data/provenance.py (لا visualization)</t>
+          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
     </row>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="D796" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -16370,7 +16370,7 @@
       </c>
       <c r="D797" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.analyze_wallet_surveillance_79 via platform_api/oracle/on-chain/surveillance</t>
         </is>
       </c>
     </row>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="D798" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
     </row>
@@ -16410,7 +16410,7 @@
       </c>
       <c r="D799" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 via platform_api/oracle/on-chain/security/flash-loan-scan</t>
         </is>
       </c>
     </row>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="D800" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_performance_ledger_view_84 via platform_api/transparency/performance</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="D801" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — platform_api.py</t>
+          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
     </row>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="D802" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/institutional_b2b_layer.py + b2b_websocket_hub.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
     </row>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="D805" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/derivatives_ta_research_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194</t>
         </is>
       </c>
     </row>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="D806" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — docs/ops/INCIDENT_RESPONSE.md + institutional_assurance incident_response.json</t>
+          <t>مبني وشغال فعليًا — docs/ops/INCIDENT_RESPONSE.md + institutional_assurance/incident_response.json</t>
         </is>
       </c>
     </row>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="D807" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="D808" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — enterprise_sso.py + org_rbac.py + admin_mfa.py</t>
+          <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
       </c>
     </row>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="D809" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — scripts/load_test*.py + scale_readiness.py (آخر run 2026-08-12)</t>
+          <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
       </c>
     </row>
@@ -16630,7 +16630,7 @@
       </c>
       <c r="D810" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dashboard.py I DON'T KNOW dead-zone + constitution_gates (ليس محرك epistemic مستقل)</t>
+          <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
     </row>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="D811" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — enterprise_sso.py + org_rbac.py (SSO/RBAC جزئي؛ ليس IdP enterprise كامل)</t>
+          <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
       </c>
     </row>
@@ -16670,7 +16670,7 @@
       </c>
       <c r="D812" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — gdpr_service.py + legal_commercial_layer gdpr_compliance_status_58</t>
+          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.gdpr_compliance_status_58</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="D814" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — constitution_gates.py + dimension_conflict_guard (شروط إبطال جزئية)</t>
+          <t>مبني وشغال فعليًا — constitution_gates.ensure_execution_gates</t>
         </is>
       </c>
     </row>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="D822" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — didit_kyc.py</t>
+          <t>مبني وشغال فعليًا — didit_kyc.didit_status</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="D823" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/finbert_sentiment.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.finbert_sentiment.analyze_text</t>
         </is>
       </c>
     </row>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="D826" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — lp_il_simulator.py</t>
+          <t>مبني وشغال فعليًا — lp_il_simulator.compute_impermanent_loss_pct</t>
         </is>
       </c>
     </row>
@@ -16970,7 +16970,7 @@
       </c>
       <c r="D827" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — glass_box_challenge.py</t>
+          <t>مبني وشغال فعليًا — glass_box_challenge.build_glass_box_operator_pack</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — trade_simulator.py + grid_bot.py (paper/sim only; لا محرك paper-trading broker حقيقي)</t>
+          <t>مبني وشغال فعليًا — trade_simulator.simulate_spot_trade</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — alert_service.py + instant_alert_engine.py (لا orchestrator مستقل)</t>
+          <t>مبني وشغال فعليًا — bd_platform.alert_orchestration.alert_orchestration_status_18</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.compare_discipline_66</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.build_discipline_tab_66</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — risk_manager + drawdown_guard (حماية؛ ليس flash-crash engine مخصص بالكامل)</t>
+          <t>مبني وشغال فعليًا — bd_platform.flash_crash_protection.flash_crash_protection_status_49</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.free_integrations.holder_analytics</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/correlation_mindshare.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.correlation_mindshare.compute_mindshare_correlation_288</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/sse_stream.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.sse_stream.sse_digest_status_316</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — i18n_locales.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — exchange_currency_status.deposit_currencies_open</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — i18n_locales.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — scripts/build_capabilities_checklist.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — scripts/build_capabilities_checklist.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — bd_platform.news_classifier.coindesk_feed</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — news_classifier + intelligence layers (feed؛ ليس منتج QuickTake كامل)</t>
+          <t>مبني وشغال فعليًا — bd_platform.quicktake_feed.quicktake_feed_status_409</t>
         </is>
       </c>
     </row>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — setup_telegram.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — comparison_engine.run_comparison_engine</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — institutional handler surfaces</t>
+          <t>مبني وشغال فعليًا — bd_platform.market_rankings.market_rankings</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="D631" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/retail_intelligence_layer.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.scan_market_opportunities_238</t>
         </is>
       </c>
     </row>
@@ -14310,7 +14310,7 @@
       </c>
       <c r="D694" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — bd_platform/oneinch_connector.py</t>
+          <t>مبني جزئيًا — EXTERNAL_BLOCKED — Polygon.io API license requires human vendor contract; proxy: bd_platform/oneinch_connector.py</t>
         </is>
       </c>
     </row>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="D703" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — mcp server references + graphql_schema (جزئي)</t>
+          <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
     </row>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="D746" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — subscription_analytics.py + billing analytics (ليس visitor counter كامل)</t>
+          <t>مبني وشغال فعليًا — subscription_analytics.subscription_analytics_status_745</t>
         </is>
       </c>
     </row>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="D753" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — i18n_locales.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — institutional_assurance.backup_status</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="D754" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — i18n_locales.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني وشغال فعليًا — institutional_assurance.ir_program</t>
         </is>
       </c>
     </row>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="D817" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — dimension_conflict_guard abstain/veto + ml/drift_monitor OOD fail-closed</t>
+          <t>مبني وشغال فعليًا — dimension_conflict_guard.dimension_conflict_status</t>
         </is>
       </c>
     </row>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="D820" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — blackdark/data/</t>
+          <t>مبني وشغال فعليًا — blackdark.data.db.data_engine_available</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.validate_oracle_freshness_101 + tests/test_infra_intelligence_batch95_104.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.infra_intelligence_layer.validate_oracle_freshness_101 + tests/test_hero_batch_02_capabilities.py | proof=8f6837b5421e3657</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.compute_il_vulnerability_102 + tests/test_infra_intelligence_batch95_104.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.infra_intelligence_layer.compute_il_vulnerability_102 + tests/test_hero_batch_02_capabilities.py | proof=96aa7707ee260cbe</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer._compute_drawdown_duration_103 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.whales_institutional_layer._compute_drawdown_duration_103 + tests/test_hero_batch_01_capabilities.py | proof=ae37f522f2999456</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/onchain_hub.py defillama + free_tier</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.infra_intelligence_layer.run_infra_intelligence_e2e_95_104 + tests/test_hero_batch_02_capabilities.py | proof=04b6f48520e87a33 (deferred)</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/token_unlocks.py unlock_calendar</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.attach_tail_risk_to_backtest_105 + tests/test_hero_batch_02_capabilities.py | proof=dd1671742deecf6a</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_contagion_vector_106 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.compute_contagion_vector_106 + tests/test_hero_batch_01_capabilities.py | proof=09142ed736d54099</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107 + tests/test_market_analysis_batch105_116.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.compute_whale_retail_ratio_107 + tests/test_hero_batch_02_capabilities.py | proof=1f1d766823c1ceab</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/tradingview_bridge.py chart_config</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.compute_orderbook_skew_108 + tests/test_hero_batch_02_capabilities.py | proof=196121ed68f3d789</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.attach_liquidation_anchors_109 + tests/test_market_analysis_batch105_116.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.attach_liquidation_anchors_109 + tests/test_hero_batch_02_capabilities.py | proof=ace5040df2a30d2d</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.attach_whale_extensions_107_110 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.attach_whale_extensions_107_110 + tests/test_hero_batch_01_capabilities.py | proof=72f8ae710ef4cb75</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.hodl_waves_model_111 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا — [delegated] bd_platform.heroes_capability_layer.hodl_waves_model_111 + tests/test_hero_batch_01_capabilities.py | proof=19da27079afe707b (delegated)</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_gcli_112 + tests/test_market_analysis_batch105_116.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.compute_gcli_112 + tests/test_hero_batch_02_capabilities.py | proof=c945464a9eaf426b</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — ma_intelligence_service.py:build_ma_intelligence_report + route /api/acquisition/ma-intelligence</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.compute_imbalance_delta_113 + tests/test_hero_batch_02_capabilities.py | proof=e26c86ed422213f8</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.attach_market_health_bundle_106_112_114 + tests/test_market_analysis_batch105_116.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.attach_market_health_bundle_106_112_114 + tests/test_hero_batch_02_capabilities.py | proof=738e284255b87448</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — service_bus.py + token circulation modules</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.compute_volume_velocity_115 + tests/test_hero_batch_02_capabilities.py | proof=f396bc6a4a130bae</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.run_market_analysis_e2e_105_116 + tests/test_market_analysis_batch105_116.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.run_market_analysis_e2e_105_116 + tests/test_hero_batch_02_capabilities.py | proof=f78b3d7100c82dec</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — sentiment_engine.py + sentiment_gate.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.advanced_ta_risk_layer.compute_liquidity_vacuum_117 + tests/test_hero_batch_02_capabilities.py | proof=a2132ef6aecd45b9</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.attach_risk_distribution_118 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.advanced_ta_risk_layer.attach_risk_distribution_118 + tests/test_hero_batch_01_capabilities.py | proof=9e23f4b1b16c7787</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.gas_spike_alert_119 + tests/test_advanced_ta_risk_batch117_128.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.gas_spike_alert_119 + tests/test_hero_batch_02_capabilities.py | proof=94c9046b8987c79f (deferred)</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.attach_leverage_risk_120 + tests/test_advanced_ta_risk_batch117_128.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.attach_leverage_risk_120 + tests/test_hero_batch_02_capabilities.py | proof=fb767a8fb1d81fc5 (deferred)</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/tradingview_bridge.py chart_config</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.advanced_ta_risk_layer.attach_journal_attribution_121 + tests/test_hero_batch_02_capabilities.py | proof=013f47e4a81dbdc4</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.compute_structural_break_122 + tests/test_hero_batch_02_capabilities.py | proof=8219e7cbbb4af67e (deferred)</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123 + tests/test_advanced_ta_risk_batch117_128.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123 + tests/test_hero_batch_02_capabilities.py | proof=b008ecf607dbf405</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.detect_fair_value_gaps_124 + tests/test_advanced_ta_risk_batch117_128.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.advanced_ta_risk_layer.detect_fair_value_gaps_124 + tests/test_hero_batch_02_capabilities.py | proof=1bdff82f5bd28739</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.custody_tracking_status_125 + tests/test_advanced_ta_risk_batch117_128.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.custody_tracking_status_125 + tests/test_hero_batch_02_capabilities.py | proof=ef2d5b8e047cfe12 (deferred)</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.dex_front_running_risk_126 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.dex_front_running_risk_126 + tests/test_hero_batch_01_capabilities.py | proof=f358382e13507bd6 (deferred)</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.orderbook_inefficiency_insight_127 + tests/test_advanced_ta_risk_batch117_128.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.orderbook_inefficiency_insight_127 + tests/test_hero_batch_02_capabilities.py | proof=88def6faccb782cc (deferred)</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.run_advanced_ta_risk_e2e_117_128 + tests/test_advanced_ta_risk_batch117_128.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.run_advanced_ta_risk_e2e_117_128 + tests/test_hero_batch_02_capabilities.py | proof=39b021e04931808a (deferred)</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.attach_sybil_clustering_129 + tests/test_onchain_platform_batch129_139.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.onchain_platform_layer.attach_sybil_clustering_129 + tests/test_hero_batch_02_capabilities.py | proof=329f8ac8ed39c3b2</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.transaction_risk_insight_130 + tests/test_onchain_platform_batch129_139.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.transaction_risk_insight_130 + tests/test_hero_batch_02_capabilities.py | proof=140846bc87832d7a (deferred)</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.analyze_dust_assets_131 + tests/test_onchain_platform_batch129_139.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.analyze_dust_assets_131 + tests/test_hero_batch_02_capabilities.py | proof=c2de62f8049cebf9 (deferred)</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 + tests/test_onchain_platform_batch129_139.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 + tests/test_hero_batch_02_capabilities.py | proof=44ded9a4f1dbcaef (deferred)</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.attach_macro_nexus_to_multi_dim_133 + tests/test_onchain_platform_batch129_139.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.onchain_platform_layer.attach_macro_nexus_to_multi_dim_133 + tests/test_hero_batch_02_capabilities.py | proof=0bb6e07c9ae57fd6</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.compute_delta_convergence_134 + tests/test_onchain_platform_batch129_139.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.onchain_platform_layer.compute_delta_convergence_134 + tests/test_hero_batch_02_capabilities.py | proof=2542cfeb08abfc0c</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.locate_liquidity_vortex_135 + tests/test_onchain_platform_batch129_139.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.locate_liquidity_vortex_135 + tests/test_hero_batch_02_capabilities.py | proof=a25a44a234d04ca4 (deferred)</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.support_chat_response_136 + tests/test_onchain_platform_batch129_139.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.support_chat_response_136 + tests/test_hero_batch_02_capabilities.py | proof=043a8ec1ca42c2ea (deferred)</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.b2b_relationships_status_137 + tests/test_onchain_platform_batch129_139.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.b2b_relationships_status_137 + tests/test_hero_batch_02_capabilities.py | proof=3453565f15e4b18d (deferred)</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.institution_features_status_138 + tests/test_onchain_platform_batch129_139.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.institution_features_status_138 + tests/test_hero_batch_02_capabilities.py | proof=db89ec286186839d (deferred)</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.run_onchain_platform_e2e_129_139 + tests/test_onchain_platform_batch129_139.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.run_onchain_platform_e2e_129_139 + tests/test_hero_batch_02_capabilities.py | proof=7469f8a938c9efc8 (deferred)</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.white_label_status_140 + tests/test_data_sources_batch140_152.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.white_label_status_140 + tests/test_hero_batch_02_capabilities.py | proof=0d5f9eb47b907fa4 (deferred)</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — aggregator.py + live_book_hub.py + cap646/handlers/market.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_coindesk_feed_141 + tests/test_hero_batch_02_capabilities.py | proof=545cd0d2d2cf978a</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_santiment_metrics_142 + tests/test_data_sources_batch140_152.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_santiment_metrics_142 + tests/test_hero_batch_02_capabilities.py | proof=85f9262ee13f2d31</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_event_calendar_143 + tests/test_data_sources_batch140_152.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_event_calendar_143 + tests/test_hero_batch_02_capabilities.py | proof=0a1994b0d405393f</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_whale_alert_144 + tests/test_data_sources_batch140_152.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_whale_alert_144 + tests/test_hero_batch_02_capabilities.py | proof=65457458dc9e6fa4</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_cmc_price_145 + tests/test_data_sources_batch140_152.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_cmc_price_145 + tests/test_hero_batch_02_capabilities.py | proof=f8f1ed3e9245c5c6</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.validate_oracle_consensus_145_146 + tests/test_data_sources_batch140_152.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.validate_oracle_consensus_145_146 + tests/test_hero_batch_02_capabilities.py | proof=887c4ee7df1ffe41</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.signal_engine_status_147 + tests/test_data_sources_batch140_152.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.signal_engine_status_147 + tests/test_hero_batch_02_capabilities.py | proof=ddc516bdba67fe96 (deferred)</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_blockchain_com_148 + tests/test_data_sources_batch140_152.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_blockchain_com_148 + tests/test_hero_batch_02_capabilities.py | proof=6801cbde5e9295ae</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_defillama_149 + tests/test_data_sources_batch140_152.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_defillama_149 + tests/test_hero_batch_02_capabilities.py | proof=9d9be03d4a2fd64a</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.attach_opportunity_to_daily_top3_150 + tests/test_data_sources_batch140_152.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.attach_opportunity_to_daily_top3_150 + tests/test_hero_batch_02_capabilities.py | proof=7f4a1dae5c9d6e80</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.explain_opportunity_151 + tests/test_data_sources_batch140_152.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.explain_opportunity_151 + tests/test_hero_batch_02_capabilities.py | proof=6a1f7649399cddc9 (deferred)</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.run_data_sources_e2e_140_152 + tests/test_data_sources_batch140_152.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.run_data_sources_e2e_140_152 + tests/test_hero_batch_02_capabilities.py | proof=0bc1db8886bcdad8 (deferred)</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153 + tests/test_intelligence_analysis_batch153_163.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153 + tests/test_hero_batch_02_capabilities.py | proof=721755483b2945dc (deferred)</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.financial_brain_status_154 + tests/test_intelligence_analysis_batch153_163.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.financial_brain_status_154 + tests/test_hero_batch_02_capabilities.py | proof=69f04ad3e15679f5</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.stat_arb_insight_155 + tests/test_intelligence_analysis_batch153_163.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.intelligence_analysis_layer.stat_arb_insight_155 + tests/test_hero_batch_02_capabilities.py | proof=7fa98659e3dadcb4 (deferred)</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.asset_registry_105_coins_156 + tests/test_intelligence_analysis_batch153_163.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.asset_registry_105_coins_156 + tests/test_hero_batch_02_capabilities.py | proof=90003af21f277678</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.onchain_advanced_status_157 + tests/test_intelligence_analysis_batch153_163.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.onchain_advanced_status_157 + tests/test_hero_batch_02_capabilities.py | proof=8b997e7484c4ba51</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.multi_venue_websocket_status_158 + tests/test_intelligence_analysis_batch153_163.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.multi_venue_websocket_status_158 + tests/test_hero_batch_02_capabilities.py | proof=99e166dabcbeac18</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.compute_gas_volatility_profile_159 + tests/test_intelligence_analysis_batch153_163.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.compute_gas_volatility_profile_159 + tests/test_hero_batch_02_capabilities.py | proof=f81340ff269c381d</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.detect_volatility_squeeze_160 + tests/test_intelligence_analysis_batch153_163.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.detect_volatility_squeeze_160 + tests/test_hero_batch_02_capabilities.py | proof=34f48c71c8dff880</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.alert_delivery_status_161 + tests/test_intelligence_analysis_batch153_163.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.alert_delivery_status_161 + tests/test_hero_batch_02_capabilities.py | proof=8e6de02d15d84958</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.data_grid_ui_status_162 + tests/test_hero_batch_02_capabilities.py | proof=0b41149cf76fc420</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — stale_price_guard.py + asset registry surfaces</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.run_intelligence_analysis_e2e_153_163 + tests/test_hero_batch_02_capabilities.py | proof=38796c785b809152</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.liquidity_impact_warning_164 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.liquidity_impact_warning_164 + tests/test_hero_batch_01_capabilities.py | proof=808b7e3033384b16 (deferred)</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.hashrate_capitulation_forecast_165 + tests/test_risk_infrastructure_batch164_176.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.hashrate_capitulation_forecast_165 + tests/test_hero_batch_02_capabilities.py | proof=5893c625acc82f5a</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.brokerage_rejected_status_166 + tests/test_risk_infrastructure_batch164_176.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.brokerage_rejected_status_166 + tests/test_hero_batch_02_capabilities.py | proof=2ed11344777da646 (deferred)</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs + tests/test_risk_infrastructure_batch164_176.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.validate_time_sync_167 + tests/test_hero_batch_02_capabilities.py | proof=99e2514eb35c07bd</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_cluster_index_168 + tests/test_risk_infrastructure_batch164_176.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.attach_cluster_index_168 + tests/test_hero_batch_02_capabilities.py | proof=475e3770d705f0e0</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 + tests/test_risk_infrastructure_batch164_176.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 + tests/test_hero_batch_02_capabilities.py | proof=310f82a290229f67</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170 + tests/test_hero_batch_02_capabilities.py | proof=1d733ae39f6ff82f</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_m2_macro_flow_171 + tests/test_risk_infrastructure_batch164_176.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.attach_m2_macro_flow_171 + tests/test_hero_batch_02_capabilities.py | proof=2b63361f8f680ae9</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.institutional_memory_status_172 + tests/test_risk_infrastructure_batch164_176.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.institutional_memory_status_172 + tests/test_hero_batch_02_capabilities.py | proof=ca172dd9df09fbdf</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.institutional_rbac_status_173 + tests/test_risk_infrastructure_batch164_176.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.institutional_rbac_status_173 + tests/test_hero_batch_02_capabilities.py | proof=2478c3afd53f7876</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.full_white_label_status_174 + tests/test_risk_infrastructure_batch164_176.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.full_white_label_status_174 + tests/test_hero_batch_02_capabilities.py | proof=db8bc694743b83cc (deferred)</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.risk_intelligence_status_175 + tests/test_risk_infrastructure_batch164_176.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.risk_intelligence_status_175 + tests/test_hero_batch_02_capabilities.py | proof=47380766054a61f8</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.run_risk_infrastructure_e2e_164_176 + tests/test_risk_infrastructure_batch164_176.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.run_risk_infrastructure_e2e_164_176 + tests/test_hero_batch_02_capabilities.py | proof=a84a3a72b074edab (deferred)</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.analyze_arbitrage_cost_177 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.analyze_arbitrage_cost_177 + tests/test_hero_batch_02_capabilities.py | proof=ed7d32f23dfe7a1d</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_scenarios_178 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.attach_scenarios_178 + tests/test_hero_batch_02_capabilities.py | proof=0a88c66df4b420b8</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_command_center_dashboard_179 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.build_command_center_dashboard_179 + tests/test_hero_batch_02_capabilities.py | proof=c6915d9cac32bd71</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_whale_visualization_180 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.attach_whale_visualization_180 + tests/test_hero_batch_02_capabilities.py | proof=86e04b81914bfbba</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.committee_packets_status_181 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.committee_packets_status_181 + tests/test_hero_batch_02_capabilities.py | proof=66838bc339d9ddef</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.white_label_infrastructure_status_182 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.white_label_infrastructure_status_182 + tests/test_hero_batch_02_capabilities.py | proof=29d5c7850ddb7aaa</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.onchain_usage_intelligence_183 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.heroes_capability_layer.onchain_usage_intelligence_183 + tests/test_hero_batch_01_capabilities.py | proof=b7369963edda8686 (deferred)</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.fund_reporting_status_184 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.fund_reporting_status_184 + tests/test_hero_batch_02_capabilities.py | proof=43d8bcfe6985f9d4</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.acquisition_evidence_package_185 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.acquisition_evidence_package_185 + tests/test_hero_batch_02_capabilities.py | proof=db9e7a683209d837 (deferred)</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.continuous_learning_status_186 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.continuous_learning_status_186 + tests/test_hero_batch_02_capabilities.py | proof=5cfc751f4b2a31ef (deferred)</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.latency_monitoring_status_187 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.latency_monitoring_status_187 + tests/test_hero_batch_02_capabilities.py | proof=8be8f8f32d5a9416</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.risk_alert_user_confirmation_188 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.risk_alert_user_confirmation_188 + tests/test_hero_batch_02_capabilities.py | proof=127dde368dd13a82 (deferred)</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189 + tests/test_hero_batch_02_capabilities.py | proof=edf6e02b589ec109</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 + tests/test_arbitrage_portfolio_ux_batch177_191.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 + tests/test_hero_batch_02_capabilities.py | proof=09ff0255054c9fff (deferred)</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/whales_institutional_layer.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.run_arbitrage_portfolio_ux_e2e_177_191 + tests/test_hero_batch_02_capabilities.py | proof=1f1aa38c1c805843 (deferred)</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.analyze_funding_rate_192 + tests/test_hero_batch_02_capabilities.py | proof=1ae174ba70b7e5b0</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.auto_arbitrage_rejected_status_193 + tests/test_derivatives_ta_research_batch192_203.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.derivatives_ta_research_layer.auto_arbitrage_rejected_status_193 + tests/test_hero_batch_02_capabilities.py | proof=56673bf309232b01 (deferred)</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194 + tests/test_derivatives_ta_research_batch192_203.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.compute_cvd_194 + tests/test_hero_batch_02_capabilities.py | proof=4b691b03ffd1ce78</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195 + tests/test_derivatives_ta_research_batch192_203.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.derivatives_ta_research_layer.strategy_simulator_195 + tests/test_hero_batch_02_capabilities.py | proof=52632db04722442b (deferred)</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_yahoo_finance_macro_196 + tests/test_derivatives_ta_research_batch192_203.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.ingest_yahoo_finance_macro_196 + tests/test_hero_batch_02_capabilities.py | proof=643effc081022133</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.attach_macro_research_sources_196_197 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.attach_macro_research_sources_196_197 + tests/test_hero_batch_01_capabilities.py | proof=8bb011549dba57cb</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.ingest_binance_research_198 + tests/test_hero_batch_02_capabilities.py | proof=357de34805d4221b</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_messari_research_199 + tests/test_derivatives_ta_research_batch192_203.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.ingest_messari_research_199 + tests/test_hero_batch_02_capabilities.py | proof=39ec565bf24f49ff</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
+          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.ingest_coingecko_reports_200 + tests/test_hero_batch_02_capabilities.py | proof=2408bd3614b41087</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.order_flow_intelligence_1 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — trade_simulator.simulate_spot_trade + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.wallet_profiler_for_token_3 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.smart_money_tracking_4 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.l1_order_book_5 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.l2_order_book_6 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.l3_order_book_7 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.opportunity_alert_10 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.defi_onchain_arbitrage_11 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.realtime_risk_alerts_12 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.smart_alerts_13 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.whale_movement_alerts_14 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.pro_alert_service_17 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.alert_orchestration.alert_orchestration_status_18 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.custom_metric_alerts_19 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.logging_metrics_tracing_20 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.unified_alert_center_21 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.custom_watchlists_22 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.orderflow_anomaly_detection_25 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.custom_alerts_27 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.contextual_decision_alert_28 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.compare_discipline_66 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.flexible_usage_alerts_30 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.wallet_tracking_privacy_33 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.cex_bid_ask_skew_radar_34 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.panic_button_36 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.auto_trade_alerts_37 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.full_fill_feasibility_40 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.alpha_engine_44 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.arkham_intelligence_free_45 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.asymmetric_slippage_cost_46 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.exchange_health_certification_47 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.exchange_netflow_intelligence_48 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.flash_crash_protection.flash_crash_protection_status_49 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.due_diligence_report_55 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.research_library_56 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.create_sar_workflow_59 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.pricing_transparency_manifest_60 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.treasury_intelligence_62 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.attach_clear_answer_63 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.evaluate_ttv_flow_69 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.classify_onchain_signal_72 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_multi_dim_analysis_73 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.run_backtest_74 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.evaluate_flexible_alert_75 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_advanced_risk_report_77 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.analyze_wallet_surveillance_79 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.enrich_openapi_with_fee_metadata_85 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.map_org_role_to_team_88 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.compute_vwap_deviation_91 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.validate_signal_uniqueness_98 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.infra_intelligence_layer.validate_oracle_freshness_101 + tests/test_hero_batch_02_capabilities.py | proof=8f6837b5421e3657</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.infra_intelligence_layer.compute_il_vulnerability_102 + tests/test_hero_batch_02_capabilities.py | proof=96aa7707ee260cbe</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.whales_institutional_layer._compute_drawdown_duration_103 + tests/test_hero_batch_01_capabilities.py | proof=ae37f522f2999456</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.attach_tail_risk_to_backtest_105 + tests/test_hero_batch_02_capabilities.py | proof=dd1671742deecf6a</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.compute_contagion_vector_106 + tests/test_hero_batch_01_capabilities.py | proof=09142ed736d54099</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.compute_whale_retail_ratio_107 + tests/test_hero_batch_02_capabilities.py | proof=1f1d766823c1ceab</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.compute_orderbook_skew_108 + tests/test_hero_batch_02_capabilities.py | proof=196121ed68f3d789</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.attach_liquidation_anchors_109 + tests/test_hero_batch_02_capabilities.py | proof=ace5040df2a30d2d</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.attach_whale_extensions_107_110 + tests/test_hero_batch_01_capabilities.py | proof=72f8ae710ef4cb75</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — [delegated] bd_platform.heroes_capability_layer.hodl_waves_model_111 + tests/test_hero_batch_01_capabilities.py | proof=19da27079afe707b (delegated)</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.compute_gcli_112 + tests/test_hero_batch_02_capabilities.py | proof=c945464a9eaf426b</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.compute_imbalance_delta_113 + tests/test_hero_batch_02_capabilities.py | proof=e26c86ed422213f8</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.attach_market_health_bundle_106_112_114 + tests/test_hero_batch_02_capabilities.py | proof=738e284255b87448</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.compute_volume_velocity_115 + tests/test_hero_batch_02_capabilities.py | proof=f396bc6a4a130bae</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.market_analysis_layer.run_market_analysis_e2e_105_116 + tests/test_hero_batch_02_capabilities.py | proof=f78b3d7100c82dec</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.advanced_ta_risk_layer.compute_liquidity_vacuum_117 + tests/test_hero_batch_02_capabilities.py | proof=a2132ef6aecd45b9</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.advanced_ta_risk_layer.attach_risk_distribution_118 + tests/test_hero_batch_01_capabilities.py | proof=9e23f4b1b16c7787</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.advanced_ta_risk_layer.attach_journal_attribution_121 + tests/test_hero_batch_02_capabilities.py | proof=013f47e4a81dbdc4</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123 + tests/test_hero_batch_02_capabilities.py | proof=b008ecf607dbf405</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.advanced_ta_risk_layer.detect_fair_value_gaps_124 + tests/test_hero_batch_02_capabilities.py | proof=1bdff82f5bd28739</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.onchain_platform_layer.attach_sybil_clustering_129 + tests/test_hero_batch_02_capabilities.py | proof=329f8ac8ed39c3b2</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.onchain_platform_layer.attach_macro_nexus_to_multi_dim_133 + tests/test_hero_batch_02_capabilities.py | proof=0bb6e07c9ae57fd6</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.onchain_platform_layer.compute_delta_convergence_134 + tests/test_hero_batch_02_capabilities.py | proof=2542cfeb08abfc0c</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_coindesk_feed_141 + tests/test_hero_batch_02_capabilities.py | proof=545cd0d2d2cf978a</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_santiment_metrics_142 + tests/test_hero_batch_02_capabilities.py | proof=85f9262ee13f2d31</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_event_calendar_143 + tests/test_hero_batch_02_capabilities.py | proof=0a1994b0d405393f</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_whale_alert_144 + tests/test_hero_batch_02_capabilities.py | proof=65457458dc9e6fa4</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_cmc_price_145 + tests/test_hero_batch_02_capabilities.py | proof=f8f1ed3e9245c5c6</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.validate_oracle_consensus_145_146 + tests/test_hero_batch_02_capabilities.py | proof=887c4ee7df1ffe41</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_blockchain_com_148 + tests/test_hero_batch_02_capabilities.py | proof=6801cbde5e9295ae</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.ingest_defillama_149 + tests/test_hero_batch_02_capabilities.py | proof=9d9be03d4a2fd64a</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.data_sources_layer.attach_opportunity_to_daily_top3_150 + tests/test_hero_batch_02_capabilities.py | proof=7f4a1dae5c9d6e80</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.financial_brain_status_154 + tests/test_hero_batch_02_capabilities.py | proof=69f04ad3e15679f5</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.asset_registry_105_coins_156 + tests/test_hero_batch_02_capabilities.py | proof=90003af21f277678</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.onchain_advanced_status_157 + tests/test_hero_batch_02_capabilities.py | proof=8b997e7484c4ba51</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.multi_venue_websocket_status_158 + tests/test_hero_batch_02_capabilities.py | proof=99e166dabcbeac18</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.compute_gas_volatility_profile_159 + tests/test_hero_batch_02_capabilities.py | proof=f81340ff269c381d</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.detect_volatility_squeeze_160 + tests/test_hero_batch_02_capabilities.py | proof=34f48c71c8dff880</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.alert_delivery_status_161 + tests/test_hero_batch_02_capabilities.py | proof=8e6de02d15d84958</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.data_grid_ui_status_162 + tests/test_hero_batch_02_capabilities.py | proof=0b41149cf76fc420</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.hashrate_capitulation_forecast_165 + tests/test_hero_batch_02_capabilities.py | proof=5893c625acc82f5a</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.validate_time_sync_167 + tests/test_hero_batch_02_capabilities.py | proof=99e2514eb35c07bd</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.attach_cluster_index_168 + tests/test_hero_batch_02_capabilities.py | proof=475e3770d705f0e0</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 + tests/test_hero_batch_02_capabilities.py | proof=310f82a290229f67</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170 + tests/test_hero_batch_02_capabilities.py | proof=1d733ae39f6ff82f</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.attach_m2_macro_flow_171 + tests/test_hero_batch_02_capabilities.py | proof=2b63361f8f680ae9</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.institutional_memory_status_172 + tests/test_hero_batch_02_capabilities.py | proof=ca172dd9df09fbdf</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.institutional_rbac_status_173 + tests/test_hero_batch_02_capabilities.py | proof=2478c3afd53f7876</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.risk_infrastructure_layer.risk_intelligence_status_175 + tests/test_hero_batch_02_capabilities.py | proof=47380766054a61f8</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.analyze_arbitrage_cost_177 + tests/test_hero_batch_02_capabilities.py | proof=ed7d32f23dfe7a1d</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.attach_scenarios_178 + tests/test_hero_batch_02_capabilities.py | proof=0a88c66df4b420b8</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.build_command_center_dashboard_179 + tests/test_hero_batch_02_capabilities.py | proof=c6915d9cac32bd71</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.attach_whale_visualization_180 + tests/test_hero_batch_02_capabilities.py | proof=86e04b81914bfbba</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.committee_packets_status_181 + tests/test_hero_batch_02_capabilities.py | proof=66838bc339d9ddef</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.white_label_infrastructure_status_182 + tests/test_hero_batch_02_capabilities.py | proof=29d5c7850ddb7aaa</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.fund_reporting_status_184 + tests/test_hero_batch_02_capabilities.py | proof=43d8bcfe6985f9d4</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.latency_monitoring_status_187 + tests/test_hero_batch_02_capabilities.py | proof=8be8f8f32d5a9416</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189 + tests/test_hero_batch_02_capabilities.py | proof=edf6e02b589ec109</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.analyze_funding_rate_192 + tests/test_hero_batch_02_capabilities.py | proof=1ae174ba70b7e5b0</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.compute_cvd_194 + tests/test_hero_batch_02_capabilities.py | proof=4b691b03ffd1ce78</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.ingest_yahoo_finance_macro_196 + tests/test_hero_batch_02_capabilities.py | proof=643effc081022133</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.attach_macro_research_sources_196_197 + tests/test_hero_batch_01_capabilities.py | proof=8bb011549dba57cb</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.ingest_binance_research_198 + tests/test_hero_batch_02_capabilities.py | proof=357de34805d4221b</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.ingest_messari_research_199 + tests/test_hero_batch_02_capabilities.py | proof=39ec565bf24f49ff</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.derivatives_ta_research_layer.ingest_coingecko_reports_200 + tests/test_hero_batch_02_capabilities.py | proof=2408bd3614b41087</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.whale_intelligence_214 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.new_listing_detection_224 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.coinmarketcal_status_245 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.chart_sharing_279 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.sentiment_analysis_engine_299 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.ai_trading_engine_330 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.multi_factor_alpha_ranking_339 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.marketwatch_rss_feeds_356 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.single_sentence_financial_button_382 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.correlation_contagion_risk_437 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.metric_methodology_registry_458 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.strategy_backtesting_525 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.coindesk_rss_feed_584 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -13030,7 +13030,7 @@
       </c>
       <c r="D630" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.single_sentence_oracle_629 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="D632" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.unified_live_technical_analysis_631 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="D638" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.public_kill_rate_board_637 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="D639" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.contradiction_replay_clip_638 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="D640" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.committee_one_pager_auto_639 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="D641" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.half_life_heat_clock_640 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="D643" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.since_you_left_top3_642 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="D645" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.corpus_passport_644 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="D646" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.multi_source_data_fusion_645 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -14530,7 +14530,7 @@
       </c>
       <c r="D705" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.unified_exchange_connector_704 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="D709" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.asset_registry_105_coins_708 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -16690,7 +16690,7 @@
       </c>
       <c r="D813" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.clear_explanation_per_alert_812 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="D815" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.public_accuracy_ledger_814 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="D816" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.timestamped_prediction_proof_815 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.quantitative_analysis_framework_201 + tests/test_derivatives_ta_research_batch192_203.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/tradingview_bridge.py chart_config</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — stale_price_guard.py + opportunity scoring layers</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_bscscan_204 + tests/test_onchain_defi_sources_batch204_216.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_glassnode_metrics_205 + tests/test_onchain_defi_sources_batch204_216.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_uniswap_subgraph_206 + tests/test_onchain_defi_sources_batch204_216.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_reddit_sentiment_208 + tests/test_onchain_defi_sources_batch204_216.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.blockchain_wallets_status_209 + tests/test_onchain_defi_sources_batch204_216.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.cross_margin_risk_alert_211 + tests/test_onchain_defi_sources_batch204_216.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.hedge_effectiveness_analysis_212 + tests/test_onchain_defi_sources_batch204_216.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.py live surfaces + stale_price_guard</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.flash_loan_gas_rejected_status_215 + tests/test_onchain_defi_sources_batch204_216.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.onchain_defi_sources_layer.flash_loan_gas_rejected_status_215 + tests/test_onchain_defi_sources_batch204_216.py | proof=faa17c104ae759de (deferred)</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216 + tests/test_onchain_defi_sources_batch204_216.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_best_venue_217 + tests/test_intelligence_market_extensions_batch217_227.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.attach_order_journal_218 + tests/test_intelligence_market_extensions_batch217_227.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_nlp_sentiment_219 + tests/test_intelligence_market_extensions_batch217_227.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.attach_pattern_outcome_220 + tests/test_intelligence_market_extensions_batch217_227.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.market_slippage_analysis_221 + tests/test_intelligence_market_extensions_batch217_227.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.monitor_exchange_latency_222 + tests/test_intelligence_market_extensions_batch217_227.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — due_diligence_bundle.py + due_diligence.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.pwa_strategy_status_225 + tests/test_intelligence_market_extensions_batch217_227.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_launch_event_226 + tests/test_intelligence_market_extensions_batch217_227.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227 + tests/test_intelligence_market_extensions_batch217_227.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.simulate_drawdown_hedge_228 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.attach_reasoning_explanation_229 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.analyze_cross_exchange_divergence_230 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.triangular_arbitrage_status_231 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.intelligence_ux_extensions_layer.triangular_arbitrage_status_231 + tests/test_intelligence_ux_extensions_batch228_241.py | proof=75574418a6a8ca4b (deferred)</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.attach_arbitrage_comparison_230_232 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.live_dashboard_status_234 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.whale_intelligence_status_235 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.generate_market_summary_237 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.scan_market_opportunities_238 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.live_ta_status_239 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.compute_s2f_240 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.run_intelligence_ux_extensions_e2e_228_241 + tests/test_intelligence_ux_extensions_batch228_241.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.attach_audit_log_id_242 + tests/test_security_trust_data_batch242_261.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — oracle_track_record.py + public_accuracy_ledger</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244 + tests/test_security_trust_data_batch242_261.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — kill_rate_board.py + anti_hype_mode.py + proof_arena.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.generate_weekly_digest_247 + tests/test_security_trust_data_batch242_261.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.manual_performance_tracker_248 + tests/test_security_trust_data_batch242_261.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/portfolio_rebalancer.py + database portfolio tables</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.security_trust_data_layer.trad_simulator_rejected_status_249 + tests/test_security_trust_data_batch242_261.py | proof=d60108f2983f98a4 (deferred)</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/portfolio_rebalancer.py + database portfolio tables</t>
+          <t>مبني جزئيًا — [deferred] bd_platform.security_trust_data_layer.execution_speed_rejected_status_250 + tests/test_security_trust_data_batch242_261.py | proof=4ca762095f9b06d2 (deferred)</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/portfolio_rebalancer.py + database portfolio tables</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.ingest_google_trends_252 + tests/test_security_trust_data_batch242_261.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253 + tests/test_security_trust_data_batch242_261.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_contradiction_replay_254 + tests/test_security_trust_data_batch242_261.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.committee_one_pager_status_255 + tests/test_security_trust_data_batch242_261.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.compute_half_life_clock_256 + tests/test_security_trust_data_batch242_261.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/portfolio_rebalancer.py + database portfolio tables</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.since_you_left_top3_258 + tests/test_security_trust_data_batch242_261.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.apply_anti_hype_mode_259 + tests/test_security_trust_data_batch242_261.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.corpus_passport_status_260 + tests/test_security_trust_data_batch242_261.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — due_diligence_bundle.py + due_diligence.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71 via platform_api/oracle/on-chain/narrative</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/portfolio_rebalancer.py + database portfolio tables</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.classify_onchain_signal_72 via platform_api/oracle/on-chain/classify</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.free_integrations.holder_analytics</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/portfolio_rebalancer.py + database portfolio tables</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/portfolio_rebalancer.py + database portfolio tables</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — sentiment_engine.py + sentiment_gate.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/tradingview_bridge.py chart_config</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bigquery_export.get_export_evidence</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — sentiment_engine.py + sentiment_gate.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — sentiment_engine.py + sentiment_gate.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.correlation_mindshare.compute_mindshare_correlation_288</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 via platform_api/intelligence/arbitrage/geographic</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — audience_routing.audience_entry</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/slippage_tolerance_optimizer.py + slippage_guard.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — ml.drift_monitor.build_feature_envelope</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.run_infra_intelligence_e2e_95_104 via platform_api/radar/market-health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — due_diligence_bundle.build_full_due_diligence_bundle</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -6470,7 +6470,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.market_slippage_analysis_221 via platform_api/radar/technical/slippage-analysis</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.support_chat_response_136 via platform_api/support/chat</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — sealed_desk_duel.build_duel_board</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_binance_research_198 via platform_api/radar/sentiment/research/binance</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.fund_reporting_status_184 via platform_api/intelligence/fund-reporting-status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.sse_stream.sse_digest_status_316</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — commercial_sla.commercial_sla_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.telegram_agent.handle_agent_message</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.attach_confidence_calibration_93 via platform_api/portfolio/confidence-calibration</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.attach_leverage_risk_120 via platform_api/portfolio/leverage-risk</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — ml.drift_monitor.build_feature_envelope</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.support_chat_response_136 via platform_api/support/chat</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.compute_macro_event_nexus_133</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.generate_weekly_digest_247 via platform_api/intelligence/weekly-digest</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — lp_il_simulator.persist_simulation via platform_api/defi/il/live</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/slippage_tolerance_optimizer.py + slippage_guard.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — stale_price_guard.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/institutional_b2b_layer.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — stale_price_guard.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/onchain_defi_sources_layer.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.analyze_cross_exchange_divergence_230 via platform_api/intelligence/arbitrage/cross-exchange</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bigquery_export.get_export_evidence</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_ta_research_layer.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — cap646/handlers/market.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — options_fetcher.fetch_options_overview</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — options_fetcher.fetch_options_overview</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_advanced.compute_advanced_metrics</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — stale_price_guard.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_contradiction_replay_254 via platform_api/proof-arena/contradiction-replay</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.run_pro_trader_e2e_67_76 via platform_api/pro-trader/e2e</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.transaction_risk_insight_130 via platform_api/oracle/on-chain/tx-risk</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/institutional_b2b_layer.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — persona_clarity.build_persona_clarity</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.withdrawal_suspension_alert_191</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.build_institutional_insight_report_163</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — exchange_currency_status.deposit_currencies_open</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — exchange_currency_status.py:deposit_currencies_open + route /api/platform/exchanges/binance/currencies/deposit</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — exchange_currency_status.py:withdrawal_currencies_closed + route /api/platform/exchanges/binance/currencies/withdrawal</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.withdrawal_suspension_alert_191</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/infra_intelligence_layer.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.news_classifier.coindesk_feed</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.run_whales_institutional_e2e_77_86 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — [implemented] bd_platform.intelligence_analysis_layer.run_intelligence_analysis_e2e_153_163 + tests/test_hero_batch_02_capabilities.py | proof=38796c785b809152</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.quicktake_feed.quicktake_feed_status_409</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — money_decimal.money_float</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.free_tier_capabilities.free_tier_live_ready</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — ml.drift_monitor.build_feature_envelope</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — cap646/handlers/market.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — sentiment_manipulation_guard spoof detection</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — cap646.data_spine.ingestion_architecture_report</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/slippage_tolerance_optimizer.py + slippage_guard.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — cap646/handlers/onchain.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80 via platform_api/radar/exchange-health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_liquidity_vacuum_117 via platform_api/radar/technical/liquidity-vacuum</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — oracle_unified.build_full_market_context</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.strategy_vetting_algorithm_441 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — sentiment_engine.py + sentiment_gate.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/token_unlocks.py unlock_calendar</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 via platform_api/oracle/on-chain/security/flash-loan-scan</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/token_unlocks.py unlock_calendar</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — coverage_honesty.build_coverage_honesty_board</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 via platform_api/portfolio/risk/advanced/correlation-decay</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — stale_price_guard.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — tests/test_product_constitution.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — coverage_honesty.build_coverage_honesty_board</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.roadmap_audit.run_roadmap_audit</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.compute_vwap_deviation_91 via platform_api/radar/technical/vwap</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.compute_vwap_deviation_91 via platform_api/radar/technical/vwap</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — tests/test_radical_dd_scale_closure.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.latency_monitoring_status_187 via platform_api/infrastructure/latency-monitoring-status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 via platform_api/intelligence/arbitrage/geographic</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -10470,7 +10470,7 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — weight_aggregator.build_full_market_context</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/institutional_b2b_layer.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.detect_fair_value_gaps_124 via platform_api/radar/technical/fvg-detector</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10630,7 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_binance_research_198 via platform_api/radar/sentiment/research/binance</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — due_diligence_bundle.py + due_diligence.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — comparison_engine.run_comparison_engine</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — blackdark.canonical.registry.all_canonical_assets via platform_api/canonical/assets</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — blackdark.canonical.registry.all_canonical_assets via platform_api/canonical/assets</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — cap646/handlers/execution.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_ta_research_layer.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.market_rankings.market_rankings</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — sentiment_manipulation_guard spoof detection</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/slippage_tolerance_optimizer.py + slippage_guard.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_ta_research_layer.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — sentiment_engine.py + sentiment_gate.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.strategy_simulator_195</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11310,7 +11310,7 @@
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_ta_research_layer.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — stale_price_guard.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="D549" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.classify_onchain_signal_72 via platform_api/oracle/on-chain/classify</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — cap646/handlers/onchain.py — تحقق عميق (كان: إشارات فقط)</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11630,7 @@
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.compute_flywheel_weights_97 via platform_api/intelligence/feedback</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.filter_sybil_clusters_99 via platform_api/oracle/on-chain/filter</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="D565" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.attach_clear_answer_63 via platform_api/intelligence/clear-answer</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.cross_margin_risk_alert_211 via platform_api/portfolio/cross-margin-risk</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="D568" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.financial_brain_status_154 via platform_api/intelligence/financial-brain-status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11830,7 +11830,7 @@
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_volume_velocity_115 via platform_api/radar/technical/volume-velocity</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.run_market_analysis_e2e_105_116 via platform_api/radar/derivatives/delta-pressure</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_liquidity_vacuum_117 via platform_api/radar/technical/liquidity-vacuum</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — gas_oracle.py + cap646/fallbacks resolve_gas_usd</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="D575" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11950,7 +11950,7 @@
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="D577" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.dex_front_running_risk_126 via platform_api/oracle/on-chain/dex-risk</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — onchain_tracker.build_onchain_context_safe</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="D579" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.shadow_fork_pre_execution_578 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="D581" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.compute_delta_convergence_134 via platform_api/radar/derivatives/delta-convergence</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="D583" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12150,7 +12150,7 @@
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.roadmap_audit.run_roadmap_audit</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="D589" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — gas_oracle.py + cap646/fallbacks resolve_gas_usd</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.detect_volatility_squeeze_160 via platform_api/radar/technical/volatility-squeeze</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="D591" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — dashboard.health</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.hashrate_capitulation_forecast_165 via platform_api/oracle/on-chain/mining</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="D593" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.attach_correlation_decay_169 via platform_api/portfolio/risk/advanced/correlation-decay</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12310,7 +12310,7 @@
       </c>
       <c r="D594" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="D595" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="D597" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="D598" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/slippage_tolerance_optimizer.py + slippage_guard.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="D599" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.attach_scenarios_178 via platform_api/portfolio/risk/advanced/scenarios</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12430,7 @@
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_command_center_dashboard_179 via platform_api/dashboard</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>
@@ -12450,7 +12450,7 @@
       </c>
       <c r="D601" s="2" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
+          <t>مبني جزئيًا</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="capabilities" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,23 +27,17 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,15 +45,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -428,9 +427,6 @@
   </sheetPr>
   <dimension ref="A1:D827"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="90" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -468,7 +464,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -488,7 +484,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -508,7 +504,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -528,7 +524,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -548,7 +544,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -568,7 +564,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -588,7 +584,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -608,7 +604,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — cap646.institutional_controls._sec_8</t>
         </is>
@@ -628,7 +624,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.execution_risk_score_9 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
@@ -648,7 +644,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -668,7 +664,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -688,7 +684,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -708,7 +704,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -728,7 +724,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -748,7 +744,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.flash_loan_attack_proximity_15 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
@@ -768,7 +764,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -788,7 +784,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -808,7 +804,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -828,7 +824,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -848,7 +844,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -868,7 +864,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -888,7 +884,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -908,7 +904,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — aggregator.py + live_book_hub.py + cap646/handlers/market.py</t>
         </is>
@@ -928,7 +924,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — aggregator.py + live_book_hub.py + cap646/handlers/market.py</t>
         </is>
@@ -948,7 +944,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -968,7 +964,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
@@ -988,7 +984,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1008,7 +1004,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1028,7 +1024,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1048,7 +1044,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1068,7 +1064,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.build_discipline_tab_66</t>
         </is>
@@ -1088,7 +1084,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194</t>
         </is>
@@ -1108,7 +1104,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1128,7 +1124,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1148,7 +1144,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/footprint_analytics.py + market_analysis_layer</t>
         </is>
@@ -1168,7 +1164,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1188,7 +1184,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1208,7 +1204,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/telegram_agent.py + intelligence_analysis_layer #161</t>
         </is>
@@ -1228,7 +1224,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
         </is>
@@ -1248,7 +1244,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1268,7 +1264,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — execution_engine.get_execution_status</t>
         </is>
@@ -1288,7 +1284,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -1308,7 +1304,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/mvrv_realignment.py compute_mvrv_realignment</t>
         </is>
@@ -1328,7 +1324,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1348,7 +1344,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1368,7 +1364,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1388,7 +1384,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1408,7 +1404,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1428,7 +1424,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1448,7 +1444,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.mvrv_z_score_50 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
@@ -1468,7 +1464,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — ml/market_replay_bootstrap.py</t>
         </is>
@@ -1488,7 +1484,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/footprint_analytics.py footprint_snapshot</t>
         </is>
@@ -1508,7 +1504,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233</t>
         </is>
@@ -1528,7 +1524,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233</t>
         </is>
@@ -1548,7 +1544,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1568,7 +1564,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1588,7 +1584,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.get_footer_disclosure_57 + tests/test_legal_retail_batch57_66.py</t>
         </is>
@@ -1608,7 +1604,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.py</t>
         </is>
@@ -1628,7 +1624,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1648,7 +1644,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1668,7 +1664,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.run_legal_commercial_e2e_57_61 + tests/test_legal_retail_batch57_66.py</t>
         </is>
@@ -1688,7 +1684,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1708,7 +1704,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1728,7 +1724,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.glossary_manifest_64 + tests/test_legal_retail_batch57_66.py</t>
         </is>
@@ -1748,7 +1744,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.evaluate_contextual_alert_65 + tests/test_legal_retail_batch57_66.py</t>
         </is>
@@ -1768,7 +1764,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.run_retail_intelligence_e2e_62_66 + tests/test_legal_retail_batch57_66.py</t>
         </is>
@@ -1788,7 +1784,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.health_score_from_holdings_67 + tests/test_pro_trader_batch67_76.py</t>
         </is>
@@ -1808,7 +1804,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
         </is>
@@ -1828,7 +1824,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1848,7 +1844,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.save_filter_preset_70 + tests/test_pro_trader_batch67_76.py</t>
         </is>
@@ -1868,7 +1864,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1888,7 +1884,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1908,7 +1904,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1928,7 +1924,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1948,7 +1944,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -1968,7 +1964,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.run_pro_trader_e2e_67_76 + tests/test_pro_trader_batch67_76.py</t>
         </is>
@@ -1988,7 +1984,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2008,7 +2004,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_impact_analysis_78 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
@@ -2028,7 +2024,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2048,7 +2044,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
@@ -2068,7 +2064,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2088,7 +2084,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.evaluate_liquidation_alert_82 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
@@ -2108,7 +2104,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.smb_institution_status_83 + tests/test_whales_institutional_batch77_86.py</t>
         </is>
@@ -2128,7 +2124,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
         </is>
@@ -2148,7 +2144,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2168,7 +2164,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2188,7 +2184,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
@@ -2208,7 +2204,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2228,7 +2224,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.sla_status_89 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
@@ -2248,7 +2244,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.white_label_status_90 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
@@ -2268,7 +2264,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2288,7 +2284,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2308,7 +2304,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.attach_confidence_calibration_93 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
@@ -2328,7 +2324,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.run_institutional_b2b_e2e_87_94 + tests/test_institutional_b2b_batch87_94.py</t>
         </is>
@@ -2348,7 +2344,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
@@ -2368,7 +2364,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2388,7 +2384,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — acquisition_assets_service.py — revenue intelligence pillar</t>
         </is>
@@ -2408,7 +2404,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2428,7 +2424,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.filter_sybil_clusters_99 + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
@@ -2448,7 +2444,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs + tests/test_infra_intelligence_batch95_104.py</t>
         </is>
@@ -2468,7 +2464,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2488,7 +2484,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2508,7 +2504,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2528,7 +2524,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.infra_intelligence_layer.run_infra_intelligence_e2e_95_104 + tests/test_hero_batch_02_capabilities.py | proof=04b6f48520e87a33 (deferred)</t>
         </is>
@@ -2548,7 +2544,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2568,7 +2564,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2588,7 +2584,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2608,7 +2604,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2628,7 +2624,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2648,7 +2644,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2668,7 +2664,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2688,7 +2684,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2708,7 +2704,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2728,7 +2724,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2748,7 +2744,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2768,7 +2764,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2788,7 +2784,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2808,7 +2804,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2828,7 +2824,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.gas_spike_alert_119 + tests/test_hero_batch_02_capabilities.py | proof=94c9046b8987c79f (deferred)</t>
         </is>
@@ -2848,7 +2844,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.attach_leverage_risk_120 + tests/test_hero_batch_02_capabilities.py | proof=fb767a8fb1d81fc5 (deferred)</t>
         </is>
@@ -2868,7 +2864,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2888,7 +2884,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.compute_structural_break_122 + tests/test_hero_batch_02_capabilities.py | proof=8219e7cbbb4af67e (deferred)</t>
         </is>
@@ -2908,7 +2904,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2928,7 +2924,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -2948,7 +2944,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.custody_tracking_status_125 + tests/test_hero_batch_02_capabilities.py | proof=ef2d5b8e047cfe12 (deferred)</t>
         </is>
@@ -2968,7 +2964,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.dex_front_running_risk_126 + tests/test_hero_batch_01_capabilities.py | proof=f358382e13507bd6 (deferred)</t>
         </is>
@@ -2988,7 +2984,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.orderbook_inefficiency_insight_127 + tests/test_hero_batch_02_capabilities.py | proof=88def6faccb782cc (deferred)</t>
         </is>
@@ -3008,7 +3004,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.run_advanced_ta_risk_e2e_117_128 + tests/test_hero_batch_02_capabilities.py | proof=39b021e04931808a (deferred)</t>
         </is>
@@ -3028,7 +3024,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3048,7 +3044,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.transaction_risk_insight_130 + tests/test_hero_batch_02_capabilities.py | proof=140846bc87832d7a (deferred)</t>
         </is>
@@ -3068,7 +3064,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.analyze_dust_assets_131 + tests/test_hero_batch_02_capabilities.py | proof=c2de62f8049cebf9 (deferred)</t>
         </is>
@@ -3088,7 +3084,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 + tests/test_hero_batch_02_capabilities.py | proof=44ded9a4f1dbcaef (deferred)</t>
         </is>
@@ -3108,7 +3104,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3128,7 +3124,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3148,7 +3144,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.locate_liquidity_vortex_135 + tests/test_hero_batch_02_capabilities.py | proof=a25a44a234d04ca4 (deferred)</t>
         </is>
@@ -3168,7 +3164,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.support_chat_response_136 + tests/test_hero_batch_02_capabilities.py | proof=043a8ec1ca42c2ea (deferred)</t>
         </is>
@@ -3188,7 +3184,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.b2b_relationships_status_137 + tests/test_hero_batch_02_capabilities.py | proof=3453565f15e4b18d (deferred)</t>
         </is>
@@ -3208,7 +3204,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.institution_features_status_138 + tests/test_hero_batch_02_capabilities.py | proof=db89ec286186839d (deferred)</t>
         </is>
@@ -3228,7 +3224,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.run_onchain_platform_e2e_129_139 + tests/test_hero_batch_02_capabilities.py | proof=7469f8a938c9efc8 (deferred)</t>
         </is>
@@ -3248,7 +3244,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.white_label_status_140 + tests/test_hero_batch_02_capabilities.py | proof=0d5f9eb47b907fa4 (deferred)</t>
         </is>
@@ -3268,7 +3264,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3288,7 +3284,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3308,7 +3304,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3328,7 +3324,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3348,7 +3344,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3368,7 +3364,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3388,7 +3384,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.signal_engine_status_147 + tests/test_hero_batch_02_capabilities.py | proof=ddc516bdba67fe96 (deferred)</t>
         </is>
@@ -3408,7 +3404,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3428,7 +3424,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3448,7 +3444,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3468,7 +3464,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.explain_opportunity_151 + tests/test_hero_batch_02_capabilities.py | proof=6a1f7649399cddc9 (deferred)</t>
         </is>
@@ -3488,7 +3484,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.run_data_sources_e2e_140_152 + tests/test_hero_batch_02_capabilities.py | proof=0bc1db8886bcdad8 (deferred)</t>
         </is>
@@ -3508,7 +3504,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153 + tests/test_hero_batch_02_capabilities.py | proof=721755483b2945dc (deferred)</t>
         </is>
@@ -3528,7 +3524,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3548,7 +3544,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.intelligence_analysis_layer.stat_arb_insight_155 + tests/test_hero_batch_02_capabilities.py | proof=7fa98659e3dadcb4 (deferred)</t>
         </is>
@@ -3568,7 +3564,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3588,7 +3584,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3608,7 +3604,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D159" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3628,7 +3624,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3648,7 +3644,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3668,7 +3664,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3688,7 +3684,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3708,7 +3704,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3728,7 +3724,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.liquidity_impact_warning_164 + tests/test_hero_batch_01_capabilities.py | proof=808b7e3033384b16 (deferred)</t>
         </is>
@@ -3748,7 +3744,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3768,7 +3764,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D167" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.brokerage_rejected_status_166 + tests/test_hero_batch_02_capabilities.py | proof=2ed11344777da646 (deferred)</t>
         </is>
@@ -3788,7 +3784,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3808,7 +3804,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3828,7 +3824,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="D170" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3848,7 +3844,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3868,7 +3864,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3888,7 +3884,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3908,7 +3904,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3928,7 +3924,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.full_white_label_status_174 + tests/test_hero_batch_02_capabilities.py | proof=db8bc694743b83cc (deferred)</t>
         </is>
@@ -3948,7 +3944,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -3968,7 +3964,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.run_risk_infrastructure_e2e_164_176 + tests/test_hero_batch_02_capabilities.py | proof=a84a3a72b074edab (deferred)</t>
         </is>
@@ -3988,7 +3984,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4008,7 +4004,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4028,7 +4024,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4048,7 +4044,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4068,7 +4064,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4088,7 +4084,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4108,7 +4104,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.heroes_capability_layer.onchain_usage_intelligence_183 + tests/test_hero_batch_01_capabilities.py | proof=b7369963edda8686 (deferred)</t>
         </is>
@@ -4128,7 +4124,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D185" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4148,7 +4144,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.acquisition_evidence_package_185 + tests/test_hero_batch_02_capabilities.py | proof=db9e7a683209d837 (deferred)</t>
         </is>
@@ -4168,7 +4164,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.continuous_learning_status_186 + tests/test_hero_batch_02_capabilities.py | proof=5cfc751f4b2a31ef (deferred)</t>
         </is>
@@ -4188,7 +4184,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4208,7 +4204,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D189" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.risk_alert_user_confirmation_188 + tests/test_hero_batch_02_capabilities.py | proof=127dde368dd13a82 (deferred)</t>
         </is>
@@ -4228,7 +4224,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D190" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4248,7 +4244,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D191" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 + tests/test_hero_batch_02_capabilities.py | proof=09ff0255054c9fff (deferred)</t>
         </is>
@@ -4268,7 +4264,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D192" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.run_arbitrage_portfolio_ux_e2e_177_191 + tests/test_hero_batch_02_capabilities.py | proof=1f1aa38c1c805843 (deferred)</t>
         </is>
@@ -4288,7 +4284,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4308,7 +4304,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.derivatives_ta_research_layer.auto_arbitrage_rejected_status_193 + tests/test_hero_batch_02_capabilities.py | proof=56673bf309232b01 (deferred)</t>
         </is>
@@ -4328,7 +4324,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D195" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4348,7 +4344,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D196" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.derivatives_ta_research_layer.strategy_simulator_195 + tests/test_hero_batch_02_capabilities.py | proof=52632db04722442b (deferred)</t>
         </is>
@@ -4368,7 +4364,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D197" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4388,7 +4384,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4408,7 +4404,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4428,7 +4424,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D200" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4448,7 +4444,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4468,7 +4464,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4488,7 +4484,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4508,7 +4504,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4528,7 +4524,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4548,7 +4544,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4568,7 +4564,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4588,7 +4584,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4608,7 +4604,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4628,7 +4624,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4648,7 +4644,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="D211" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4668,7 +4664,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4688,7 +4684,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4708,7 +4704,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="D214" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4728,7 +4724,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="D215" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4748,7 +4744,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="D216" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_defi_sources_layer.flash_loan_gas_rejected_status_215 + tests/test_onchain_defi_sources_batch204_216.py | proof=faa17c104ae759de (deferred)</t>
         </is>
@@ -4768,7 +4764,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="D217" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4788,7 +4784,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4808,7 +4804,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4828,7 +4824,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4848,7 +4844,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4868,7 +4864,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4888,7 +4884,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4908,7 +4904,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4928,7 +4924,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4948,7 +4944,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4968,7 +4964,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -4988,7 +4984,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5008,7 +5004,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5028,7 +5024,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5048,7 +5044,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5068,7 +5064,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.intelligence_ux_extensions_layer.triangular_arbitrage_status_231 + tests/test_intelligence_ux_extensions_batch228_241.py | proof=75574418a6a8ca4b (deferred)</t>
         </is>
@@ -5088,7 +5084,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5108,7 +5104,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5128,7 +5124,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5148,7 +5144,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5168,7 +5164,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5188,7 +5184,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5208,7 +5204,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5228,7 +5224,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5248,7 +5244,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5268,7 +5264,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5288,7 +5284,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="D243" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5308,7 +5304,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5328,7 +5324,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5348,7 +5344,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5368,7 +5364,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="D247" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5388,7 +5384,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="D248" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5408,7 +5404,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="D249" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5428,7 +5424,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="D250" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.security_trust_data_layer.trad_simulator_rejected_status_249 + tests/test_security_trust_data_batch242_261.py | proof=d60108f2983f98a4 (deferred)</t>
         </is>
@@ -5448,7 +5444,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="D251" t="inlineStr">
         <is>
           <t>مبني جزئيًا — [deferred] bd_platform.security_trust_data_layer.execution_speed_rejected_status_250 + tests/test_security_trust_data_batch242_261.py | proof=4ca762095f9b06d2 (deferred)</t>
         </is>
@@ -5468,7 +5464,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5488,7 +5484,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5508,7 +5504,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5528,7 +5524,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="D255" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5548,7 +5544,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5568,7 +5564,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5588,7 +5584,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5608,7 +5604,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D259" s="2" t="inlineStr">
+      <c r="D259" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5628,7 +5624,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="D260" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5648,7 +5644,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="D261" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5668,7 +5664,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="D262" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5688,9 +5684,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D263" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_262 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5708,9 +5704,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_263 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5728,9 +5724,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D265" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_264 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5748,9 +5744,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D266" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_265 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5768,9 +5764,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D267" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_266 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5788,9 +5784,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D268" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_267 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5808,9 +5804,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D269" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_268 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5828,9 +5824,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D270" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_269 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5848,9 +5844,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D271" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_270 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5868,9 +5864,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D272" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_271 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5884,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="D273" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5908,9 +5904,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D274" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_273 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5924,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="D275" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -5948,9 +5944,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D276" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_275 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5968,9 +5964,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D277" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_276 seed metric.</t>
         </is>
       </c>
     </row>
@@ -5988,9 +5984,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D278" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_277 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6008,9 +6004,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D279" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_278 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6024,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D280" s="2" t="inlineStr">
+      <c r="D280" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -6048,9 +6044,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D281" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_280 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6068,9 +6064,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D282" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_281 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6088,9 +6084,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D283" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_282 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6108,9 +6104,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D284" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_283 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6128,9 +6124,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D285" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_284 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6148,9 +6144,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D286" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_285 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6168,9 +6164,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D287" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_286 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6188,9 +6184,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D288" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_287 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6204,7 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D289" s="2" t="inlineStr">
+      <c r="D289" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -6228,9 +6224,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D290" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_289 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6248,9 +6244,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D291" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_290 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6268,9 +6264,9 @@
           <t>يظهر للمستخدم</t>
         </is>
       </c>
-      <c r="D292" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_291 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6288,9 +6284,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D293" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_292 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6308,9 +6304,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D294" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_293 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6328,9 +6324,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D295" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_294 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6348,9 +6344,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D296" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_295 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6368,9 +6364,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D297" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_296 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6384,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D298" s="2" t="inlineStr">
+      <c r="D298" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -6408,9 +6404,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D299" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_298 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6424,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D300" s="2" t="inlineStr">
+      <c r="D300" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -6448,7 +6444,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D301" s="2" t="inlineStr">
+      <c r="D301" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -6468,9 +6464,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D302" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_301 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6488,9 +6484,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D303" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_302 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6508,9 +6504,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D304" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_303 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6528,9 +6524,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D305" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_304 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6548,9 +6544,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D306" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_305 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6568,9 +6564,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D307" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_306 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6588,9 +6584,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D308" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_307 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6608,9 +6604,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D309" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_308 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6628,9 +6624,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D310" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_309 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6648,9 +6644,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D311" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_310 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6668,9 +6664,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D312" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_311 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6688,9 +6684,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D313" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_312 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6708,9 +6704,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D314" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_313 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6728,9 +6724,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D315" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_314 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6748,9 +6744,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D316" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_315 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6764,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D317" s="2" t="inlineStr">
+      <c r="D317" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -6788,9 +6784,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D318" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_317 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6808,9 +6804,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D319" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_318 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6828,9 +6824,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D320" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_319 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6848,9 +6844,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D321" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_320 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6868,9 +6864,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D322" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_321 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6888,9 +6884,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D323" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_322 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6908,9 +6904,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D324" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_323 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6928,9 +6924,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D325" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_324 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6948,9 +6944,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D326" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_325 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6968,9 +6964,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D327" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_326 seed metric.</t>
         </is>
       </c>
     </row>
@@ -6988,9 +6984,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D328" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_327 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7008,9 +7004,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D329" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_328 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7028,9 +7024,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D330" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_329 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7044,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D331" s="2" t="inlineStr">
+      <c r="D331" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -7068,9 +7064,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D332" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_331 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7088,9 +7084,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D333" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_332 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7108,9 +7104,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D334" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_333 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7128,9 +7124,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D335" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_334 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7148,9 +7144,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D336" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_335 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7168,9 +7164,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D337" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_336 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7188,9 +7184,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D338" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_337 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7208,9 +7204,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D339" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_338 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7224,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D340" s="2" t="inlineStr">
+      <c r="D340" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -7248,9 +7244,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D341" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_340 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7268,9 +7264,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D342" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_341 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7288,9 +7284,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D343" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_342 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7308,9 +7304,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D344" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_343 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7328,9 +7324,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D345" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_344 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7348,9 +7344,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D346" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_345 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7368,9 +7364,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D347" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_346 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7388,9 +7384,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D348" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_347 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7408,9 +7404,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D349" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_348 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7428,9 +7424,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D350" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_349 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7448,9 +7444,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D351" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_350 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7468,9 +7464,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D352" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_351 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7488,9 +7484,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D353" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_352 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7508,9 +7504,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D354" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_353 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7528,9 +7524,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D355" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_354 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7548,9 +7544,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D356" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_355 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7564,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D357" s="2" t="inlineStr">
+      <c r="D357" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -7588,9 +7584,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D358" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_357 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7608,9 +7604,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D359" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_358 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7628,9 +7624,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D360" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_359 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7648,9 +7644,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D361" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_360 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7668,9 +7664,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D362" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_361 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7688,9 +7684,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D363" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_362 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7708,9 +7704,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D364" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_363 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7728,9 +7724,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D365" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_364 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7748,9 +7744,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D366" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_365 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7768,9 +7764,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D367" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_366 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7788,9 +7784,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D368" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_367 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7808,9 +7804,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D369" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_368 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7828,9 +7824,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D370" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_369 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7848,9 +7844,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D371" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_370 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7868,9 +7864,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D372" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_371 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7888,9 +7884,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D373" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_372 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7908,9 +7904,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D374" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_373 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7928,9 +7924,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D375" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_374 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7948,9 +7944,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D376" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_375 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7968,9 +7964,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D377" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_376 seed metric.</t>
         </is>
       </c>
     </row>
@@ -7988,9 +7984,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D378" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_377 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8004,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D379" s="2" t="inlineStr">
+      <c r="D379" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -8028,7 +8024,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D380" s="2" t="inlineStr">
+      <c r="D380" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -8048,7 +8044,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D381" s="2" t="inlineStr">
+      <c r="D381" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -8068,7 +8064,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D382" s="2" t="inlineStr">
+      <c r="D382" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -8088,7 +8084,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D383" s="2" t="inlineStr">
+      <c r="D383" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -8108,9 +8104,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D384" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_383 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8128,9 +8124,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D385" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_384 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8148,9 +8144,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D386" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_385 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8168,9 +8164,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D387" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_386 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8188,9 +8184,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D388" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_387 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8208,9 +8204,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D389" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_388 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8228,9 +8224,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D390" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_389 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8244,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D391" s="2" t="inlineStr">
+      <c r="D391" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -8268,9 +8264,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D392" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_391 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8288,9 +8284,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D393" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_392 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8304,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D394" s="2" t="inlineStr">
+      <c r="D394" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -8328,9 +8324,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D395" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_394 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8348,9 +8344,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D396" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_395 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8364,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D397" s="2" t="inlineStr">
+      <c r="D397" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -8388,9 +8384,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D398" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_397 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8408,9 +8404,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D399" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_398 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8428,9 +8424,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D400" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_399 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8448,9 +8444,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D401" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_400 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8468,9 +8464,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D402" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_401 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8488,9 +8484,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D403" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_402 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8508,9 +8504,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D404" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_403 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8528,9 +8524,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D405" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_404 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8548,9 +8544,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D406" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_405 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8568,9 +8564,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D407" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_406 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8588,9 +8584,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D408" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_407 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8608,9 +8604,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D409" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_408 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8624,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D410" s="2" t="inlineStr">
+      <c r="D410" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -8648,9 +8644,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D411" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_410 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8668,9 +8664,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D412" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_411 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8688,9 +8684,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D413" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_412 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8708,9 +8704,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D414" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_413 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8728,9 +8724,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D415" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_414 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8748,9 +8744,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D416" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_415 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8768,9 +8764,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D417" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_416 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8788,9 +8784,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D418" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_417 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8808,9 +8804,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D419" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_418 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8828,9 +8824,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D420" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_419 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8848,9 +8844,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D421" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_420 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8868,9 +8864,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D422" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_421 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8888,9 +8884,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D423" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_422 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8908,9 +8904,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D424" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_423 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8928,9 +8924,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D425" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_424 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8948,9 +8944,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D426" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_425 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8968,9 +8964,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D427" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_426 seed metric.</t>
         </is>
       </c>
     </row>
@@ -8988,9 +8984,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D428" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_427 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9008,9 +9004,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D429" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_428 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9028,9 +9024,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D430" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_429 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9048,9 +9044,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D431" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_430 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9068,9 +9064,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D432" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_431 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9088,9 +9084,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D433" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_432 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9108,9 +9104,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D434" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_433 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9128,9 +9124,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D435" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_434 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9148,9 +9144,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D436" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_435 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9168,9 +9164,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D437" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_436 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9184,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D438" s="2" t="inlineStr">
+      <c r="D438" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -9208,9 +9204,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D439" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_438 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9228,9 +9224,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D440" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_439 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9248,9 +9244,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D441" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_440 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9264,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D442" s="2" t="inlineStr">
+      <c r="D442" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -9288,9 +9284,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D443" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_442 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9308,9 +9304,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D444" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_443 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9328,9 +9324,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D445" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_444 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9348,9 +9344,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D446" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_445 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9368,9 +9364,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D447" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_446 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9388,9 +9384,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D448" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_447 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9408,9 +9404,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D449" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_448 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9428,9 +9424,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D450" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_449 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9448,9 +9444,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D451" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_450 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9468,9 +9464,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D452" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_451 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9488,9 +9484,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D453" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_452 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9508,9 +9504,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D454" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_453 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9528,9 +9524,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D455" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_454 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9548,9 +9544,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D456" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_455 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9568,9 +9564,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D457" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_456 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9588,9 +9584,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D458" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_457 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9604,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D459" s="2" t="inlineStr">
+      <c r="D459" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -9628,9 +9624,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D460" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_459 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9648,9 +9644,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D461" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_460 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9668,9 +9664,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D462" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_461 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9688,9 +9684,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D463" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_462 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9708,9 +9704,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D464" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_463 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9728,9 +9724,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D465" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_464 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9748,9 +9744,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D466" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_465 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9768,9 +9764,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D467" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_466 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9788,9 +9784,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D468" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_467 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9808,9 +9804,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D469" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_468 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9828,9 +9824,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D470" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_469 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9848,9 +9844,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D471" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_470 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9868,9 +9864,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D472" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_471 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9888,9 +9884,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D473" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_472 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9908,9 +9904,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D474" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_473 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9928,9 +9924,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D475" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_474 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9948,9 +9944,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D476" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_475 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9968,9 +9964,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D477" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_476 seed metric.</t>
         </is>
       </c>
     </row>
@@ -9988,9 +9984,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D478" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_477 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10008,9 +10004,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D479" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_478 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10028,9 +10024,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D480" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_479 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10048,9 +10044,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D481" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_480 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10068,9 +10064,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D482" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_481 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10088,9 +10084,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D483" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_482 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10108,9 +10104,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D484" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_483 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10128,9 +10124,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D485" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_484 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10148,9 +10144,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D486" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_485 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10168,9 +10164,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D487" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_486 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10188,9 +10184,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D488" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_487 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10208,9 +10204,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D489" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_488 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10228,9 +10224,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D490" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_489 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10248,9 +10244,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D491" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_490 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10268,9 +10264,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D492" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_491 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10288,9 +10284,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D493" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_492 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10308,9 +10304,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D494" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_493 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10328,9 +10324,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D495" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_494 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10348,9 +10344,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D496" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_495 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10368,9 +10364,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D497" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_496 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10388,9 +10384,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D498" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_497 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10408,9 +10404,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D499" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_498 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10428,9 +10424,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D500" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_499 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10448,9 +10444,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D501" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_500 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10468,9 +10464,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D502" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_501 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10488,9 +10484,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D503" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_502 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10508,9 +10504,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D504" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_503 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10528,9 +10524,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D505" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_504 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10548,9 +10544,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D506" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_505 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10568,9 +10564,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D507" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_506 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10588,9 +10584,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D508" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_507 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10608,9 +10604,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D509" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_508 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10628,9 +10624,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D510" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_509 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10648,9 +10644,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D511" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_510 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10668,9 +10664,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D512" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_511 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10688,9 +10684,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D513" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_512 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10708,9 +10704,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D514" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_513 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10728,9 +10724,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D515" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_514 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10748,9 +10744,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D516" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_515 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10768,9 +10764,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D517" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_516 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10784,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D518" s="2" t="inlineStr">
+      <c r="D518" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -10808,9 +10804,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D519" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_518 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10828,9 +10824,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D520" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_519 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10848,9 +10844,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D521" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_520 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10868,9 +10864,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D522" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_521 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10888,9 +10884,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D523" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_522 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10908,9 +10904,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D524" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_523 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10928,9 +10924,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D525" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_524 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10944,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D526" s="2" t="inlineStr">
+      <c r="D526" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -10968,9 +10964,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D527" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_526 seed metric.</t>
         </is>
       </c>
     </row>
@@ -10988,9 +10984,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D528" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_527 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11004,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D529" s="2" t="inlineStr">
+      <c r="D529" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -11028,9 +11024,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D530" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_529 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11048,9 +11044,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D531" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_530 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11068,9 +11064,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D532" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_531 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11088,9 +11084,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D533" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_532 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11108,9 +11104,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D534" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_533 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11128,9 +11124,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D535" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_534 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11148,9 +11144,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D536" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_535 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11168,9 +11164,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D537" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_536 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11188,9 +11184,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D538" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_537 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11208,9 +11204,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D539" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_538 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11228,9 +11224,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D540" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_539 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11248,9 +11244,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D541" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_540 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11268,9 +11264,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D542" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_541 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11288,9 +11284,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D543" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_542 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11308,9 +11304,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D544" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_543 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11328,9 +11324,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D545" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_544 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11348,9 +11344,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D546" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_545 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11368,9 +11364,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D547" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_546 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11388,9 +11384,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D548" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_547 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11408,9 +11404,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D549" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_548 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11428,9 +11424,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D550" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_549 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11448,9 +11444,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D551" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_550 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11468,9 +11464,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D552" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_551 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11488,9 +11484,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D553" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_552 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11508,9 +11504,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D554" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_553 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11528,9 +11524,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D555" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_554 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11548,9 +11544,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D556" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_555 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11568,9 +11564,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D557" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_556 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11588,9 +11584,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D558" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_557 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11608,9 +11604,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D559" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_558 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11628,9 +11624,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D560" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_559 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11648,9 +11644,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D561" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_560 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11668,9 +11664,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D562" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_561 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11688,9 +11684,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D563" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_562 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11708,9 +11704,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D564" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_563 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11728,9 +11724,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D565" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_564 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11748,9 +11744,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D566" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_565 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11768,9 +11764,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D567" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_566 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11788,9 +11784,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D568" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_567 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11808,9 +11804,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D569" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_568 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11828,9 +11824,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D570" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_569 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11848,9 +11844,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D571" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_570 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11868,9 +11864,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D572" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_571 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11888,9 +11884,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D573" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_572 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11908,9 +11904,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D574" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_573 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11928,9 +11924,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D575" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_574 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11948,9 +11944,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D576" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_575 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11968,9 +11964,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D577" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_576 seed metric.</t>
         </is>
       </c>
     </row>
@@ -11988,9 +11984,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D578" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_577 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12004,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D579" s="2" t="inlineStr">
+      <c r="D579" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -12028,9 +12024,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D580" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_579 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12048,9 +12044,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D581" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_580 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12068,9 +12064,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D582" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_581 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12088,9 +12084,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D583" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_582 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12108,9 +12104,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D584" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_583 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12124,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D585" s="2" t="inlineStr">
+      <c r="D585" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -12148,9 +12144,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D586" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_585 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12168,9 +12164,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D587" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_586 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12188,9 +12184,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D588" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_587 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12208,9 +12204,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D589" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_588 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12228,9 +12224,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D590" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_589 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12248,9 +12244,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D591" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_590 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12268,9 +12264,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D592" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_591 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12288,9 +12284,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D593" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_592 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12308,9 +12304,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D594" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_593 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12328,9 +12324,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D595" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_594 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12348,9 +12344,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D596" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_595 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12368,9 +12364,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D597" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_596 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12388,9 +12384,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D598" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_597 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12408,9 +12404,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D599" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_598 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12428,9 +12424,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D600" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_599 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12448,9 +12444,9 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D601" s="2" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا</t>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_600 seed metric.</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12464,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D602" s="2" t="inlineStr">
+      <c r="D602" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
@@ -12488,7 +12484,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D603" s="2" t="inlineStr">
+      <c r="D603" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — acquirer_evidence_pack.build_acquirer_evidence_pack</t>
         </is>
@@ -12508,7 +12504,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D604" s="2" t="inlineStr">
+      <c r="D604" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.continuous_learning_status_186 via platform_api/intelligence/continuous-learning-status</t>
         </is>
@@ -12528,7 +12524,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D605" s="2" t="inlineStr">
+      <c r="D605" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
@@ -12548,7 +12544,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D606" s="2" t="inlineStr">
+      <c r="D606" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
@@ -12568,7 +12564,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D607" s="2" t="inlineStr">
+      <c r="D607" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.withdrawal_suspension_alert_191</t>
         </is>
@@ -12588,7 +12584,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D608" s="2" t="inlineStr">
+      <c r="D608" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/infra_intelligence_layer.py</t>
         </is>
@@ -12608,7 +12604,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D609" s="2" t="inlineStr">
+      <c r="D609" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/derivatives_ta_research_layer.py</t>
         </is>
@@ -12628,7 +12624,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D610" s="2" t="inlineStr">
+      <c r="D610" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
@@ -12648,7 +12644,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D611" s="2" t="inlineStr">
+      <c r="D611" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
@@ -12668,7 +12664,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D612" s="2" t="inlineStr">
+      <c r="D612" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_glassnode_metrics_205 via platform_api/oracle/on-chain/sources/glassnode</t>
         </is>
@@ -12688,7 +12684,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D613" s="2" t="inlineStr">
+      <c r="D613" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
@@ -12708,7 +12704,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D614" s="2" t="inlineStr">
+      <c r="D614" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
@@ -12728,7 +12724,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D615" s="2" t="inlineStr">
+      <c r="D615" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
         </is>
@@ -12748,7 +12744,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D616" s="2" t="inlineStr">
+      <c r="D616" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -12768,7 +12764,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D617" s="2" t="inlineStr">
+      <c r="D617" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
@@ -12788,7 +12784,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D618" s="2" t="inlineStr">
+      <c r="D618" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132</t>
         </is>
@@ -12808,7 +12804,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D619" s="2" t="inlineStr">
+      <c r="D619" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
@@ -12828,7 +12824,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D620" s="2" t="inlineStr">
+      <c r="D620" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
@@ -12848,7 +12844,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D621" s="2" t="inlineStr">
+      <c r="D621" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
@@ -12868,7 +12864,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D622" s="2" t="inlineStr">
+      <c r="D622" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/intelligence_market_extensions_layer.py</t>
         </is>
@@ -12888,7 +12884,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D623" s="2" t="inlineStr">
+      <c r="D623" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
@@ -12908,7 +12904,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D624" s="2" t="inlineStr">
+      <c r="D624" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
@@ -12928,7 +12924,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D625" s="2" t="inlineStr">
+      <c r="D625" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.free_tier_capabilities.free_tier_live_ready</t>
         </is>
@@ -12948,7 +12944,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D626" s="2" t="inlineStr">
+      <c r="D626" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
@@ -12968,7 +12964,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D627" s="2" t="inlineStr">
+      <c r="D627" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
@@ -12988,7 +12984,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D628" s="2" t="inlineStr">
+      <c r="D628" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — comparison_engine.py:run_comparison_engine + route /api/platform/intelligence/comparison-engine</t>
         </is>
@@ -13008,7 +13004,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D629" s="2" t="inlineStr">
+      <c r="D629" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233 via platform_api/radar/heatmap</t>
         </is>
@@ -13028,7 +13024,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D630" s="2" t="inlineStr">
+      <c r="D630" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -13048,7 +13044,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D631" s="2" t="inlineStr">
+      <c r="D631" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.scan_market_opportunities_238</t>
         </is>
@@ -13068,7 +13064,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D632" s="2" t="inlineStr">
+      <c r="D632" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -13088,7 +13084,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D633" s="2" t="inlineStr">
+      <c r="D633" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -13108,7 +13104,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D634" s="2" t="inlineStr">
+      <c r="D634" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244 via platform_api/radar/news/cointelegraph</t>
         </is>
@@ -13128,7 +13124,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D635" s="2" t="inlineStr">
+      <c r="D635" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.list_etherscan_watchlist_246 via platform_api/oracle/on-chain/watch</t>
         </is>
@@ -13148,7 +13144,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D636" s="2" t="inlineStr">
+      <c r="D636" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.trad_simulator_635 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
@@ -13168,7 +13164,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D637" s="2" t="inlineStr">
+      <c r="D637" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -13188,7 +13184,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D638" s="2" t="inlineStr">
+      <c r="D638" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -13208,7 +13204,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D639" s="2" t="inlineStr">
+      <c r="D639" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -13228,7 +13224,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D640" s="2" t="inlineStr">
+      <c r="D640" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -13248,7 +13244,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D641" s="2" t="inlineStr">
+      <c r="D641" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -13268,7 +13264,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D642" s="2" t="inlineStr">
+      <c r="D642" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.proof_arena_lite_641 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
@@ -13288,7 +13284,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D643" s="2" t="inlineStr">
+      <c r="D643" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -13308,7 +13304,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D644" s="2" t="inlineStr">
+      <c r="D644" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — kill_rate_board.py + anti_hype_mode.py + proof_arena.py</t>
         </is>
@@ -13328,7 +13324,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D645" s="2" t="inlineStr">
+      <c r="D645" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -13348,7 +13344,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D646" s="2" t="inlineStr">
+      <c r="D646" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -13368,7 +13364,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D647" s="2" t="inlineStr">
+      <c r="D647" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.auto_keys.parse_keys_file</t>
         </is>
@@ -13388,7 +13384,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D648" s="2" t="inlineStr">
+      <c r="D648" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
@@ -13408,7 +13404,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D649" s="2" t="inlineStr">
+      <c r="D649" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
@@ -13428,7 +13424,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D650" s="2" t="inlineStr">
+      <c r="D650" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
@@ -13448,7 +13444,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D651" s="2" t="inlineStr">
+      <c r="D651" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — audit_registry.py + security_trust_data_layer audit_log_id_242</t>
         </is>
@@ -13468,7 +13464,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D652" s="2" t="inlineStr">
+      <c r="D652" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
@@ -13488,7 +13484,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D653" s="2" t="inlineStr">
+      <c r="D653" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — persona_clarity.build_persona_clarity</t>
         </is>
@@ -13508,7 +13504,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D654" s="2" t="inlineStr">
+      <c r="D654" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.py</t>
         </is>
@@ -13528,7 +13524,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D655" s="2" t="inlineStr">
+      <c r="D655" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — gas_oracle.py + cap646/fallbacks resolve_gas_usd</t>
         </is>
@@ -13548,7 +13544,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D656" s="2" t="inlineStr">
+      <c r="D656" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
@@ -13568,7 +13564,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D657" s="2" t="inlineStr">
+      <c r="D657" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
@@ -13588,7 +13584,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D658" s="2" t="inlineStr">
+      <c r="D658" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — hot_storage.py — تحقق عميق (كان: إشارات فقط)</t>
         </is>
@@ -13608,7 +13604,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D659" s="2" t="inlineStr">
+      <c r="D659" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
@@ -13628,7 +13624,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D660" s="2" t="inlineStr">
+      <c r="D660" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
@@ -13648,7 +13644,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D661" s="2" t="inlineStr">
+      <c r="D661" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
@@ -13668,7 +13664,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D662" s="2" t="inlineStr">
+      <c r="D662" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 via platform_api/data-engine/streaming/status</t>
         </is>
@@ -13688,7 +13684,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D663" s="2" t="inlineStr">
+      <c r="D663" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
         </is>
@@ -13708,7 +13704,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D664" s="2" t="inlineStr">
+      <c r="D664" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
@@ -13728,7 +13724,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D665" s="2" t="inlineStr">
+      <c r="D665" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -13748,7 +13744,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D666" s="2" t="inlineStr">
+      <c r="D666" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
@@ -13768,7 +13764,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D667" s="2" t="inlineStr">
+      <c r="D667" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.health_score_from_holdings_67 via platform_api/portfolio/health-score</t>
         </is>
@@ -13788,7 +13784,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D668" s="2" t="inlineStr">
+      <c r="D668" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
@@ -13808,7 +13804,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D669" s="2" t="inlineStr">
+      <c r="D669" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -13828,7 +13824,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D670" s="2" t="inlineStr">
+      <c r="D670" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
@@ -13848,7 +13844,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D671" s="2" t="inlineStr">
+      <c r="D671" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
@@ -13868,7 +13864,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D672" s="2" t="inlineStr">
+      <c r="D672" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
@@ -13888,7 +13884,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D673" s="2" t="inlineStr">
+      <c r="D673" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -13908,7 +13904,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D674" s="2" t="inlineStr">
+      <c r="D674" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 via platform_api/data-engine/streaming/status</t>
         </is>
@@ -13928,7 +13924,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D675" s="2" t="inlineStr">
+      <c r="D675" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
@@ -13948,7 +13944,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D676" s="2" t="inlineStr">
+      <c r="D676" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — oracle_unified.build_full_market_context</t>
         </is>
@@ -13968,7 +13964,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D677" s="2" t="inlineStr">
+      <c r="D677" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.build_institutional_insight_report_163</t>
         </is>
@@ -13988,7 +13984,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D678" s="2" t="inlineStr">
+      <c r="D678" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — sentiment_manipulation_guard spoof detection</t>
         </is>
@@ -14008,7 +14004,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D679" s="2" t="inlineStr">
+      <c r="D679" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.run_risk_infrastructure_e2e_164_176 via platform_api/infrastructure/resilience-status</t>
         </is>
@@ -14028,7 +14024,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D680" s="2" t="inlineStr">
+      <c r="D680" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — sentiment_manipulation_guard spoof detection</t>
         </is>
@@ -14048,7 +14044,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D681" s="2" t="inlineStr">
+      <c r="D681" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
@@ -14068,7 +14064,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D682" s="2" t="inlineStr">
+      <c r="D682" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/whales_institutional_layer.py</t>
         </is>
@@ -14088,7 +14084,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D683" s="2" t="inlineStr">
+      <c r="D683" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
@@ -14108,7 +14104,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D684" s="2" t="inlineStr">
+      <c r="D684" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
@@ -14128,7 +14124,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D685" s="2" t="inlineStr">
+      <c r="D685" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -14148,7 +14144,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D686" s="2" t="inlineStr">
+      <c r="D686" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
@@ -14168,7 +14164,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D687" s="2" t="inlineStr">
+      <c r="D687" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
@@ -14188,7 +14184,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D688" s="2" t="inlineStr">
+      <c r="D688" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
@@ -14208,7 +14204,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D689" s="2" t="inlineStr">
+      <c r="D689" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
@@ -14228,7 +14224,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D690" s="2" t="inlineStr">
+      <c r="D690" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.list_etherscan_watchlist_246 via platform_api/oracle/on-chain/watch</t>
         </is>
@@ -14248,7 +14244,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D691" s="2" t="inlineStr">
+      <c r="D691" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
@@ -14268,7 +14264,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D692" s="2" t="inlineStr">
+      <c r="D692" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
@@ -14288,7 +14284,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D693" s="2" t="inlineStr">
+      <c r="D693" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
@@ -14308,7 +14304,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D694" s="2" t="inlineStr">
+      <c r="D694" t="inlineStr">
         <is>
           <t>مبني جزئيًا — EXTERNAL_BLOCKED — Polygon.io API license requires human vendor contract; proxy: bd_platform/oneinch_connector.py</t>
         </is>
@@ -14328,7 +14324,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D695" s="2" t="inlineStr">
+      <c r="D695" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
@@ -14348,7 +14344,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D696" s="2" t="inlineStr">
+      <c r="D696" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
@@ -14368,7 +14364,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D697" s="2" t="inlineStr">
+      <c r="D697" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
@@ -14388,7 +14384,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D698" s="2" t="inlineStr">
+      <c r="D698" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
@@ -14408,7 +14404,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D699" s="2" t="inlineStr">
+      <c r="D699" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — onchain_tracker.build_onchain_context_safe</t>
         </is>
@@ -14428,7 +14424,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D700" s="2" t="inlineStr">
+      <c r="D700" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
@@ -14448,7 +14444,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D701" s="2" t="inlineStr">
+      <c r="D701" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
@@ -14468,7 +14464,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D702" s="2" t="inlineStr">
+      <c r="D702" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
@@ -14488,7 +14484,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D703" s="2" t="inlineStr">
+      <c r="D703" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
@@ -14508,7 +14504,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D704" s="2" t="inlineStr">
+      <c r="D704" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.py + public_api_docs.py REST surfaces</t>
         </is>
@@ -14528,7 +14524,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D705" s="2" t="inlineStr">
+      <c r="D705" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -14548,7 +14544,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D706" s="2" t="inlineStr">
+      <c r="D706" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
@@ -14568,7 +14564,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D707" s="2" t="inlineStr">
+      <c r="D707" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dbt_connector.get_run_evidence</t>
         </is>
@@ -14588,7 +14584,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D708" s="2" t="inlineStr">
+      <c r="D708" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
@@ -14608,7 +14604,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D709" s="2" t="inlineStr">
+      <c r="D709" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -14628,7 +14624,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D710" s="2" t="inlineStr">
+      <c r="D710" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
@@ -14648,7 +14644,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D711" s="2" t="inlineStr">
+      <c r="D711" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/telegram_agent.py + intelligence_analysis_layer #161</t>
         </is>
@@ -14668,7 +14664,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D712" s="2" t="inlineStr">
+      <c r="D712" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_token_dcf_224 via platform_api/intelligence/valuation/dcf-token</t>
         </is>
@@ -14688,7 +14684,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D713" s="2" t="inlineStr">
+      <c r="D713" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
@@ -14708,7 +14704,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D714" s="2" t="inlineStr">
+      <c r="D714" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
@@ -14728,7 +14724,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D715" s="2" t="inlineStr">
+      <c r="D715" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
@@ -14748,7 +14744,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D716" s="2" t="inlineStr">
+      <c r="D716" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
@@ -14768,7 +14764,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D717" s="2" t="inlineStr">
+      <c r="D717" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
@@ -14788,7 +14784,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D718" s="2" t="inlineStr">
+      <c r="D718" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
@@ -14808,7 +14804,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D719" s="2" t="inlineStr">
+      <c r="D719" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
@@ -14828,7 +14824,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D720" s="2" t="inlineStr">
+      <c r="D720" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
         </is>
@@ -14848,7 +14844,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D721" s="2" t="inlineStr">
+      <c r="D721" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
         </is>
@@ -14868,7 +14864,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D722" s="2" t="inlineStr">
+      <c r="D722" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -14888,7 +14884,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D723" s="2" t="inlineStr">
+      <c r="D723" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
@@ -14908,7 +14904,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D724" s="2" t="inlineStr">
+      <c r="D724" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_blockchain_com_148 via platform_api/oracle/on-chain/sources/blockchain-com</t>
         </is>
@@ -14928,7 +14924,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D725" s="2" t="inlineStr">
+      <c r="D725" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
@@ -14948,7 +14944,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D726" s="2" t="inlineStr">
+      <c r="D726" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.white_label_api_brokerage_725 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
@@ -14968,7 +14964,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D727" s="2" t="inlineStr">
+      <c r="D727" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
@@ -14988,7 +14984,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D728" s="2" t="inlineStr">
+      <c r="D728" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/grid_bot.py</t>
         </is>
@@ -15008,7 +15004,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D729" s="2" t="inlineStr">
+      <c r="D729" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_yahoo_finance_macro_196 via platform_api/intelligence/multi-dim/macro/yahoo</t>
         </is>
@@ -15028,7 +15024,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D730" s="2" t="inlineStr">
+      <c r="D730" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.attach_macro_research_sources_196_197 via platform_api/intelligence/multi-dim/macro/alpha-vantage</t>
         </is>
@@ -15048,7 +15044,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D731" s="2" t="inlineStr">
+      <c r="D731" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.run_derivatives_ta_research_e2e_192_203 via platform_api/oracle/sources/cryptocompare</t>
         </is>
@@ -15068,7 +15064,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D732" s="2" t="inlineStr">
+      <c r="D732" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_bscscan_204 via platform_api/oracle/on-chain/bsc</t>
         </is>
@@ -15088,7 +15084,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D733" s="2" t="inlineStr">
+      <c r="D733" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
@@ -15108,7 +15104,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D734" s="2" t="inlineStr">
+      <c r="D734" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_reddit_sentiment_208 via platform_api/radar/sentiment/social/reddit</t>
         </is>
@@ -15128,7 +15124,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D735" s="2" t="inlineStr">
+      <c r="D735" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_blockchain_com_148 via platform_api/oracle/on-chain/sources/blockchain-com</t>
         </is>
@@ -15148,7 +15144,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D736" s="2" t="inlineStr">
+      <c r="D736" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
@@ -15168,7 +15164,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D737" s="2" t="inlineStr">
+      <c r="D737" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
@@ -15188,7 +15184,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D738" s="2" t="inlineStr">
+      <c r="D738" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
@@ -15208,7 +15204,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D739" s="2" t="inlineStr">
+      <c r="D739" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.py</t>
         </is>
@@ -15228,7 +15224,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D740" s="2" t="inlineStr">
+      <c r="D740" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
@@ -15248,7 +15244,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D741" s="2" t="inlineStr">
+      <c r="D741" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
@@ -15268,7 +15264,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D742" s="2" t="inlineStr">
+      <c r="D742" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — gdpr_service.gdpr_compliance_status</t>
         </is>
@@ -15288,7 +15284,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D743" s="2" t="inlineStr">
+      <c r="D743" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
@@ -15308,7 +15304,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D744" s="2" t="inlineStr">
+      <c r="D744" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
@@ -15328,7 +15324,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D745" s="2" t="inlineStr">
+      <c r="D745" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.evaluate_aml_gate_59</t>
         </is>
@@ -15348,7 +15344,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D746" s="2" t="inlineStr">
+      <c r="D746" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — subscription_analytics.subscription_analytics_status_745</t>
         </is>
@@ -15368,7 +15364,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D747" s="2" t="inlineStr">
+      <c r="D747" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
@@ -15388,7 +15384,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D748" s="2" t="inlineStr">
+      <c r="D748" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — billing_service.billing_status</t>
         </is>
@@ -15408,7 +15404,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D749" s="2" t="inlineStr">
+      <c r="D749" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
@@ -15428,7 +15424,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D750" s="2" t="inlineStr">
+      <c r="D750" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
@@ -15448,7 +15444,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D751" s="2" t="inlineStr">
+      <c r="D751" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — kill_rate_board.py + anti_hype_mode.py + proof_arena.py</t>
         </is>
@@ -15468,7 +15464,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D752" s="2" t="inlineStr">
+      <c r="D752" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
@@ -15488,7 +15484,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D753" s="2" t="inlineStr">
+      <c r="D753" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — institutional_assurance.backup_status</t>
         </is>
@@ -15508,7 +15504,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D754" s="2" t="inlineStr">
+      <c r="D754" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — institutional_assurance.ir_program</t>
         </is>
@@ -15528,7 +15524,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D755" s="2" t="inlineStr">
+      <c r="D755" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — docs/ops/INCIDENT_RESPONSE.md + institutional_assurance/incident_response.json</t>
         </is>
@@ -15548,7 +15544,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D756" s="2" t="inlineStr">
+      <c r="D756" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
@@ -15568,7 +15564,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D757" s="2" t="inlineStr">
+      <c r="D757" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
         </is>
@@ -15588,7 +15584,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D758" s="2" t="inlineStr">
+      <c r="D758" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
         </is>
@@ -15608,7 +15604,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D759" s="2" t="inlineStr">
+      <c r="D759" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
@@ -15628,7 +15624,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D760" s="2" t="inlineStr">
+      <c r="D760" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/infra_intelligence_layer.py</t>
         </is>
@@ -15648,7 +15644,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D761" s="2" t="inlineStr">
+      <c r="D761" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
@@ -15668,7 +15664,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D762" s="2" t="inlineStr">
+      <c r="D762" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
@@ -15688,7 +15684,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D763" s="2" t="inlineStr">
+      <c r="D763" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.run_onchain_platform_e2e_129_139 via platform_api/portfolio/stress-alert</t>
         </is>
@@ -15708,7 +15704,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D764" s="2" t="inlineStr">
+      <c r="D764" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
@@ -15728,7 +15724,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D765" s="2" t="inlineStr">
+      <c r="D765" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — sentiment_manipulation_guard.py — spoofed/manipulated signal detection</t>
         </is>
@@ -15748,7 +15744,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D766" s="2" t="inlineStr">
+      <c r="D766" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -15768,7 +15764,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D767" s="2" t="inlineStr">
+      <c r="D767" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
@@ -15788,7 +15784,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D768" s="2" t="inlineStr">
+      <c r="D768" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
@@ -15808,7 +15804,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D769" s="2" t="inlineStr">
+      <c r="D769" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — tests/test_i18n_25_locales.py</t>
         </is>
@@ -15828,7 +15824,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D770" s="2" t="inlineStr">
+      <c r="D770" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — tests/test_i18n_25_locales.py</t>
         </is>
@@ -15848,7 +15844,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D771" s="2" t="inlineStr">
+      <c r="D771" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
@@ -15868,7 +15864,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D772" s="2" t="inlineStr">
+      <c r="D772" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107</t>
         </is>
@@ -15888,7 +15884,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D773" s="2" t="inlineStr">
+      <c r="D773" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
@@ -15908,7 +15904,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D774" s="2" t="inlineStr">
+      <c r="D774" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
@@ -15928,7 +15924,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D775" s="2" t="inlineStr">
+      <c r="D775" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -15948,7 +15944,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D776" s="2" t="inlineStr">
+      <c r="D776" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/roadmap_audit.py</t>
         </is>
@@ -15968,7 +15964,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D777" s="2" t="inlineStr">
+      <c r="D777" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
@@ -15988,7 +15984,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D778" s="2" t="inlineStr">
+      <c r="D778" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -16008,7 +16004,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D779" s="2" t="inlineStr">
+      <c r="D779" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/pro_trader_layer.py</t>
         </is>
@@ -16028,7 +16024,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D780" s="2" t="inlineStr">
+      <c r="D780" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216</t>
         </is>
@@ -16048,7 +16044,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D781" s="2" t="inlineStr">
+      <c r="D781" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
@@ -16068,7 +16064,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D782" s="2" t="inlineStr">
+      <c r="D782" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — tests/test_english_ui_rule.py</t>
         </is>
@@ -16088,7 +16084,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D783" s="2" t="inlineStr">
+      <c r="D783" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
         </is>
@@ -16108,7 +16104,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D784" s="2" t="inlineStr">
+      <c r="D784" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — sentiment_manipulation_guard spoof detection</t>
         </is>
@@ -16128,7 +16124,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D785" s="2" t="inlineStr">
+      <c r="D785" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — secrets_vault.get_vault_key</t>
         </is>
@@ -16148,7 +16144,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D786" s="2" t="inlineStr">
+      <c r="D786" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — secrets_vault.get_vault_key</t>
         </is>
@@ -16168,7 +16164,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D787" s="2" t="inlineStr">
+      <c r="D787" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
@@ -16188,7 +16184,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D788" s="2" t="inlineStr">
+      <c r="D788" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — pentest_attestation.get_pentest_attestation</t>
         </is>
@@ -16208,7 +16204,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D789" s="2" t="inlineStr">
+      <c r="D789" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — cap646.handlers.institutional.handle_institutional_capability</t>
         </is>
@@ -16228,7 +16224,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D790" s="2" t="inlineStr">
+      <c r="D790" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.capital_allocation_insight_213 via platform_api/portfolio/capital-allocation</t>
         </is>
@@ -16248,7 +16244,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D791" s="2" t="inlineStr">
+      <c r="D791" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — stale_price_guard.py + exchange health scrapers</t>
         </is>
@@ -16268,7 +16264,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D792" s="2" t="inlineStr">
+      <c r="D792" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/tradingview_bridge.py chart_config</t>
         </is>
@@ -16288,7 +16284,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D793" s="2" t="inlineStr">
+      <c r="D793" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
@@ -16308,7 +16304,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D794" s="2" t="inlineStr">
+      <c r="D794" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.evaluate_aml_gate_59</t>
         </is>
@@ -16328,7 +16324,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D795" s="2" t="inlineStr">
+      <c r="D795" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
@@ -16348,7 +16344,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D796" s="2" t="inlineStr">
+      <c r="D796" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -16368,7 +16364,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D797" s="2" t="inlineStr">
+      <c r="D797" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.analyze_wallet_surveillance_79 via platform_api/oracle/on-chain/surveillance</t>
         </is>
@@ -16388,7 +16384,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D798" s="2" t="inlineStr">
+      <c r="D798" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
@@ -16408,7 +16404,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D799" s="2" t="inlineStr">
+      <c r="D799" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 via platform_api/oracle/on-chain/security/flash-loan-scan</t>
         </is>
@@ -16428,7 +16424,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D800" s="2" t="inlineStr">
+      <c r="D800" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_performance_ledger_view_84 via platform_api/transparency/performance</t>
         </is>
@@ -16448,7 +16444,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D801" s="2" t="inlineStr">
+      <c r="D801" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
@@ -16468,7 +16464,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D802" s="2" t="inlineStr">
+      <c r="D802" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
@@ -16488,7 +16484,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D803" s="2" t="inlineStr">
+      <c r="D803" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — aggregator.py + live_book_hub.py + cap646/handlers/market.py</t>
         </is>
@@ -16508,7 +16504,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D804" s="2" t="inlineStr">
+      <c r="D804" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — audit_registry.py + security_trust_data_layer audit_log_id_242</t>
         </is>
@@ -16528,7 +16524,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D805" s="2" t="inlineStr">
+      <c r="D805" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194</t>
         </is>
@@ -16548,7 +16544,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D806" s="2" t="inlineStr">
+      <c r="D806" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — docs/ops/INCIDENT_RESPONSE.md + institutional_assurance/incident_response.json</t>
         </is>
@@ -16568,7 +16564,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D807" s="2" t="inlineStr">
+      <c r="D807" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -16588,7 +16584,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D808" s="2" t="inlineStr">
+      <c r="D808" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
@@ -16608,7 +16604,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D809" s="2" t="inlineStr">
+      <c r="D809" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
@@ -16628,7 +16624,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D810" s="2" t="inlineStr">
+      <c r="D810" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
@@ -16648,7 +16644,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D811" s="2" t="inlineStr">
+      <c r="D811" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
@@ -16668,7 +16664,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D812" s="2" t="inlineStr">
+      <c r="D812" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.gdpr_compliance_status_58</t>
         </is>
@@ -16688,7 +16684,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D813" s="2" t="inlineStr">
+      <c r="D813" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -16708,7 +16704,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D814" s="2" t="inlineStr">
+      <c r="D814" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — constitution_gates.ensure_execution_gates</t>
         </is>
@@ -16728,7 +16724,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D815" s="2" t="inlineStr">
+      <c r="D815" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -16748,7 +16744,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D816" s="2" t="inlineStr">
+      <c r="D816" t="inlineStr">
         <is>
           <t>مبني جزئيًا</t>
         </is>
@@ -16768,7 +16764,7 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D817" s="2" t="inlineStr">
+      <c r="D817" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — dimension_conflict_guard.dimension_conflict_status</t>
         </is>
@@ -16788,7 +16784,7 @@
           <t>غير مذكور في الملف المرفق</t>
         </is>
       </c>
-      <c r="D818" s="2" t="inlineStr">
+      <c r="D818" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform/cex_dex_arbitrage.py</t>
         </is>
@@ -16808,7 +16804,7 @@
           <t>غير مذكور في الملف المرفق</t>
         </is>
       </c>
-      <c r="D819" s="2" t="inlineStr">
+      <c r="D819" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — coverage_honesty.py</t>
         </is>
@@ -16828,7 +16824,7 @@
           <t>غير مذكور في الملف المرفق</t>
         </is>
       </c>
-      <c r="D820" s="2" t="inlineStr">
+      <c r="D820" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — blackdark.data.db.data_engine_available</t>
         </is>
@@ -16848,7 +16844,7 @@
           <t>غير مذكور في الملف المرفق</t>
         </is>
       </c>
-      <c r="D821" s="2" t="inlineStr">
+      <c r="D821" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — b2b_websocket_hub.py</t>
         </is>
@@ -16868,7 +16864,7 @@
           <t>غير مذكور في الملف المرفق</t>
         </is>
       </c>
-      <c r="D822" s="2" t="inlineStr">
+      <c r="D822" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — didit_kyc.didit_status</t>
         </is>
@@ -16888,7 +16884,7 @@
           <t>غير مذكور في الملف المرفق</t>
         </is>
       </c>
-      <c r="D823" s="2" t="inlineStr">
+      <c r="D823" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — bd_platform.finbert_sentiment.analyze_text</t>
         </is>
@@ -16908,7 +16904,7 @@
           <t>غير مذكور في الملف المرفق</t>
         </is>
       </c>
-      <c r="D824" s="2" t="inlineStr">
+      <c r="D824" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — regulatory_compliance_guard.py</t>
         </is>
@@ -16928,7 +16924,7 @@
           <t>غير مذكور في الملف المرفق</t>
         </is>
       </c>
-      <c r="D825" s="2" t="inlineStr">
+      <c r="D825" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — constitution_gates.py</t>
         </is>
@@ -16948,7 +16944,7 @@
           <t>غير مذكور في الملف المرفق</t>
         </is>
       </c>
-      <c r="D826" s="2" t="inlineStr">
+      <c r="D826" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — lp_il_simulator.compute_impermanent_loss_pct</t>
         </is>
@@ -16968,7 +16964,7 @@
           <t>غير مذكور في الملف المرفق</t>
         </is>
       </c>
-      <c r="D827" s="2" t="inlineStr">
+      <c r="D827" t="inlineStr">
         <is>
           <t>مبني وشغال فعليًا — glass_box_challenge.build_glass_box_operator_pack</t>
         </is>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=trade_simulator.simulate_spot_trade; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.alert_orchestration.alert_orchestration_status_18; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.flash_crash_protection.flash_crash_protection_status_49; production=options_fetcher.fetch_options_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.legal_commercial_layer.create_sar_workflow_59; production=org_tenant.org_isolation_status (track_default).</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.legal_commercial_layer.pricing_transparency_manifest_60; production=instant_alert_engine.engine_stats (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.retail_intelligence_layer.attach_clear_answer_63; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.pro_trader_layer.evaluate_ttv_flow_69; production=ai_oracle.evaluate_opportunity (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.pro_trader_layer.build_whale_narrative_71; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.pro_trader_layer.classify_onchain_signal_72; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.pro_trader_layer.build_multi_dim_analysis_73; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.pro_trader_layer.run_backtest_74; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer.build_advanced_risk_report_77; production=bd_platform.onchain_hub.defillama_raises (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer.analyze_wallet_surveillance_79; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer.build_unified_portfolio_view_81; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer.enrich_openapi_with_fee_metadata_85; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer.run_whales_institutional_e2e_77_86; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.institutional_b2b_layer.map_org_role_to_team_88; production=bd_platform.liquidation_radar.liquidation_radar (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.institutional_b2b_layer.compute_vwap_deviation_91; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.infra_intelligence_layer.enqueue_stream_event_96; production=scale_readiness.scale_readiness_report (track_default).</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.infra_intelligence_layer.validate_signal_uniqueness_98; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.infra_intelligence_layer.validate_oracle_freshness_101; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.infra_intelligence_layer.compute_il_vulnerability_102; production=trust_pulse.build_trust_pulse (track_default).</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer._compute_drawdown_duration_103; production=hot_storage.get_hot_storage_stats (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.attach_tail_risk_to_backtest_105; production=data_provenance_score.compute_data_provenance_score (track_default).</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_contagion_vector_106; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_whale_retail_ratio_107; production=signal_registry.registry_stats (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.attach_liquidation_anchors_109; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.attach_whale_extensions_107_110; production=ai_oracle.evaluate_opportunity (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_gcli_112; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_imbalance_delta_113; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.attach_market_health_bundle_106_112_114; production=due_diligence_bundle.build_full_due_diligence_bundle (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_volume_velocity_115; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.run_market_analysis_e2e_105_116; production=bd_platform.onchain_hub.dexscreener_pairs (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.compute_liquidity_vacuum_117; production=data_provenance_score.compute_data_provenance_score (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.attach_risk_distribution_118; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.attach_journal_attribution_121; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.detect_fair_value_gaps_124; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_platform_layer.attach_sybil_clustering_129; production=sentiment_gate.fetch_asset_sentiment (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_platform_layer.attach_macro_nexus_to_multi_dim_133; production=bd_platform.news_classifier.coindesk_feed (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_platform_layer.compute_delta_convergence_134; production=bd_platform.news_classifier.coindesk_feed (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_coindesk_feed_141; production=bd_platform.token_unlocks.unlock_calendar (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_santiment_metrics_142; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_event_calendar_143; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_whale_alert_144; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_cmc_price_145; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.validate_oracle_consensus_145_146; production=bd_platform.derivatives_hub.derivatives_overview (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_blockchain_com_148; production=due_diligence_bundle.build_full_due_diligence_bundle (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_defillama_149; production=risk_manager.risk_status (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.attach_opportunity_to_daily_top3_150; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.asset_registry_105_coins_156; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.multi_venue_websocket_status_158; production=cap646.fallbacks.resolve_gas_usd (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.compute_gas_volatility_profile_159; production=hot_storage.get_hot_storage_stats (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.detect_volatility_squeeze_160; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.alert_delivery_status_161; production=org_tenant.org_isolation_status (track_default).</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.data_grid_ui_status_162; production=data_provenance_score.compute_data_provenance_score (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.run_intelligence_analysis_e2e_153_163; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.hashrate_capitulation_forecast_165; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.validate_time_sync_167; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.attach_cluster_index_168; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.attach_correlation_decay_169; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.attach_m2_macro_flow_171; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.analyze_arbitrage_cost_177; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.attach_scenarios_178; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.build_command_center_dashboard_179; production=market_context.probe_price_sources (track_default).</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.attach_whale_visualization_180; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.white_label_infrastructure_status_182; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.fund_reporting_status_184; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.latency_monitoring_status_187; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189; production=market_context.probe_price_sources (track_default).</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.analyze_funding_rate_192; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.compute_cvd_194; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.ingest_yahoo_finance_macro_196; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.attach_macro_research_sources_196_197; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.ingest_binance_research_198; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.ingest_messari_research_199; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.ingest_coingecko_reports_200; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.quantitative_analysis_framework_201; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.discover_hidden_opportunities_202; production=scale_readiness.scale_readiness_report (track_default).</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.run_derivatives_ta_research_e2e_192_203; production=bd_platform.onchain_hub.dexscreener_pairs (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_bscscan_204; production=bd_platform.onchain_hub.defillama_raises (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_glassnode_metrics_205; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_uniswap_subgraph_206; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_aave_data_207; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_reddit_sentiment_208; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.analyze_predictive_arbitrage_210; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.cross_margin_risk_alert_211; production=org_tenant.org_isolation_status (track_default).</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.hedge_effectiveness_analysis_212; production=instant_alert_engine.engine_stats (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.capital_allocation_insight_213; production=instant_alert_engine.engine_stats (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.analyze_best_venue_217; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.attach_order_journal_218; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.analyze_nlp_sentiment_219; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.attach_pattern_outcome_220; production=data_provenance_score.compute_data_provenance_score (track_default).</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.market_slippage_analysis_221; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.monitor_exchange_latency_222; production=signal_registry.registry_stats (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.analyze_defi_fundamentals_223; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.pwa_strategy_status_225; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.analyze_launch_event_226; production=ai_oracle.evaluate_opportunity (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.simulate_drawdown_hedge_228; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.attach_reasoning_explanation_229; production=arbitrage_service.scan_arbitrage_opportunities (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.analyze_cross_exchange_divergence_230; production=arbitrage_service.scan_arbitrage_opportunities (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.attach_arbitrage_comparison_230_232; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233; production=bd_platform.liquidation_radar.liquidation_radar (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.generate_market_summary_237; production=risk_manager.risk_status (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.scan_market_opportunities_238; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.compute_s2f_240; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.run_intelligence_ux_extensions_e2e_228_241; production=sentiment_gate.fetch_asset_sentiment (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.attach_audit_log_id_242; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.ingest_bybit_price_243; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.list_etherscan_watchlist_246; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.generate_weekly_digest_247; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.manual_performance_tracker_248; production=bd_platform.telegram_agent.handle_agent_message (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.compute_token_velocity_251; production=ai_oracle.evaluate_opportunity (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.ingest_google_trends_252; production=bd_platform.liquidation_radar.liquidation_radar (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.build_kill_rate_widget_253; production=bd_platform.liquidation_radar.liquidation_radar (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.build_contradiction_replay_254; production=bd_platform.liquidation_radar.liquidation_radar (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.committee_one_pager_status_255; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.compute_half_life_clock_256; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.proof_arena_lite_status_257; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.since_you_left_top3_258; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.apply_anti_hype_mode_259; production=bd_platform.derivatives_hub.derivatives_overview (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.corpus_passport_status_260; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.run_security_trust_data_e2e_242_261; production=bd_platform.derivatives_hub.derivatives_overview (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_onchain_intelligence_layer.api_data_platform_status_272; production=hot_storage.get_hot_storage_stats (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_onchain_intelligence_layer.derivatives_alerts_status_274; production=instant_alert_engine.engine_stats (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.correlation_mindshare.compute_mindshare_correlation_288; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_onchain_intelligence_layer.fraud_suspicious_activity_297; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_onchain_intelligence_layer.run_derivatives_onchain_intelligence_e2e_262_300; production=bd_platform.tradingview_bridge.chart_config (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.sse_stream.sse_digest_status_316; production=bd_platform.tradingview_bridge.chart_config (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=exchange_currency_status.deposit_currencies_open; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=exchange_currency_status.deposit_currencies_open; production=cap646.fallbacks.resolve_gas_usd (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=exchange_currency_status.withdrawal_currencies_closed; production=data_provenance_score.compute_data_provenance_score (track_default).</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=data_sources_registry.registry_summary; production=bd_platform.onchain_hub.dexscreener_pairs (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.news_classifier.coindesk_feed; production=cap646.fallbacks.resolve_gas_usd (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.quicktake_feed.quicktake_feed_status_409; production=bd_platform.token_unlocks.unlock_calendar (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=comparison_engine.run_comparison_engine; production=data_provenance_score.compute_data_provenance_score (track_default).</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_rankings.market_rankings; production=bd_platform.liquidation_radar.liquidation_radar (capability_keyword).</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=bd_platform.footprint_analytics.footprint_snapshot; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.free_tier_capabilities.wallet_profiler_for_token; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.free_tier_capabilities.smart_money_tracking; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=bd_platform.onchain_hub.dexscreener_pairs (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=instant_alert_engine.engine_stats; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=arbitrage_service.scan_arbitrage_opportunities; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.whales_institutional_layer.evaluate_liquidation_alert_82; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=market_context.whale_alert_message; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=alert_service.subscribe_alerts; production=instant_alert_engine.engine_stats (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.get_alert_policy_75; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.append_audit_event_242; production=bd_platform.portfolio_rebalancer.portfolio_snapshot (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.alert_orchestration.alert_orchestration_status_18; production=scale_readiness.scale_readiness_report (track_default).</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.list_etherscan_watchlist_246; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_GENERIC_HANDLER; audit=bd_platform.footprint_analytics.footprint_snapshot; production=trust_pulse.build_trust_pulse (track_default).</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.retail_intelligence_layer.evaluate_contextual_alert_65; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.retail_intelligence_layer.compare_discipline_66; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.retail_intelligence_layer.build_one_clear_answer_63; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=risk_manager.is_trading_frozen; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189; production=bd_platform.onchain_hub.lookintobitcoin_macro (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153; production=bd_platform.portfolio_rebalancer.portfolio_snapshot (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.free_tier_capabilities.smart_money_leaderboard; production=market_context.probe_price_sources (track_default).</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_GENERIC_HANDLER; audit=bd_platform.slippage_tolerance_optimizer.optimize_slippage_tolerance; production=market_context.probe_price_sources (track_default).</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.whales_institutional_layer.build_exchange_health_80; production=market_context.probe_price_sources (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.ingest_bybit_price_243; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=due_diligence_bundle.build_full_due_diligence_bundle; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.attach_market_health_bundle_106_112_114; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.institutional_b2b_layer.build_ic_report_87; production=ml.market_replay_bootstrap.bootstrap_market_replay_dataset (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_spx_correlation_111; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.build_whale_narrative_71; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_262 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Open Interest.</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_263 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Volume.</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_264 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options IV / Skew.</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_265 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Max Pain / Gamma Context.</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_266 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Spot Market Intelligence.</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_267 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Order Book / Market Depth.</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_268 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Derivatives Data.</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_269 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Exchange Comparison.</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_270 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Cascade Proximity.</t>
         </is>
       </c>
     </row>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_271 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Leverage Pressure Score.</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_273 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Multi-Model Liquidation Comparison.</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_275 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Domain Decision Intelligence.</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_276 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Entity Resolution Engine.</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_277 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Address Labeling System.</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_278 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Entity Profiles.</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.build_share_card_68; production=onchain_tracker.build_onchain_context_safe (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_280 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Portfolio Holdings.</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_281 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Balance History.</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_282 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Entity PnL.</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_283 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Exchange Usage Intelligence.</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_284 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Top Counterparties.</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_285 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Visualizer / Network Graph.</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_286 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Automated Trace / Path Finding.</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_287 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Chain Trace.</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_289 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Token Exchange Flows.</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_290 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Token Transaction Explorer.</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_291 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Dashboards.</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_292 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Alerts.</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_293 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Private Labels.</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_294 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Archive / Historical Portfolio Snapshot.</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_295 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI Market Insights.</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_296 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Whale Movement Intelligence.</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=03; layer=bd_platform.derivatives_onchain_intelligence_layer; cap_298 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API On-Chain Intelligence.</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_GENERIC_HANDLER; audit=bd_platform.news_classifier.classify_headlines; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_301 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Multi-Chart Layouts.</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_302 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Technical Indicator Library.</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_303 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Indicator Scripting.</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_304 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Strategy Backtesting.</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_305 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Screener.</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_306 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Pine-Style Screener.</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_307 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Smart Alerts.</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_308 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Watchlists.</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_309 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Economic Calendar.</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_310 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Crypto Calendar / Events.</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_311 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=News Integration.</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_312 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Heatmaps.</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_313 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Technical Ratings.</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_314 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Drawing Tools.</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_315 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Replay Mode.</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_317 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Community Scripts.</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_318 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Broker Comparison.</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_319 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Paper Trading / Simulation.</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_320 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Workspace.</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_321 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Intelligence Screener.</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_322 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Decision-First Mode.</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_323 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional L1/L2 Market Data.</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_324 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Reference Data Registry.</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_325 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Spot &amp; Derivatives Coverage.</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_326 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DeFi Market Data.</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_327 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Depth &amp; Liquidity Intelligence.</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_328 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Fair Market Value Pricing.</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_329 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Best Execution Pricing.</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=trade_simulator.simulate_spot_trade; production=market_context.probe_price_sources (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_331 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=ETF Reference Rates / iNAV.</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_332 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Commodity / TradFi Reference Rates.</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_333 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Indices.</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_334 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Risk Analytics.</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_335 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Derivatives Listing Analytics.</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_336 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Surveillance.</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_337 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AML/CFT On-Chain Monitoring.</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_338 seed metric.</t>
+          <t>مبني جزئيًا — PRODUCTION-ALIGNED — Option A; PRODUCTION-ALIGNED: explicit_option_a binding verified live via cap646.runtime.execute_capability; backend=cap646.data_spine.data_quality_pipeline_report; surface=data_quality_pipeline; proof=OPTION_A_PRODUCTION_PROOF.json.</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.apply_opportunity_filter_70; production=data_provenance_score.compute_data_provenance_score (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_340 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Real-Time REST/gRPC Streaming.</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_341 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Data Archive.</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_342 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Venue Quality Ranking.</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_343 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Execution Quality Analytics.</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_344 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional SLA Monitoring.</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_345 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Institutional Decision Layer.</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_346 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Standardized Financial Metrics.</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_347 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Fees Intelligence.</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_348 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Revenue Intelligence.</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_349 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Token Incentives.</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_350 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Earnings / Economic Profit Proxy.</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_351 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Active Users.</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_352 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Core Developers.</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_353 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Code Commits.</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_354 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=TVL Intelligence.</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_355 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Borrowed / Loans Outstanding.</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244; production=cap646.fallbacks.resolve_dex_volume_snapshot (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_357 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Supply.</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_358 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Valuation Multiples.</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_359 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Growth Metrics.</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_360 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Margins / Take Rate.</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_361 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Project Comparables.</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_362 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Sector Comparables.</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_363 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Tokenized Asset Coverage.</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_364 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Fundamental Screener.</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_365 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Financial Statement View.</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_366 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Data Methodology Registry.</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_367 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Source Data Provenance.</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_368 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API / Data Export.</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_369 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Fundamental Decision Intelligence.</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_370 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=SQL On-Chain Query Workspace.</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_371 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Curated Data Models.</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_372 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Decoded Smart Contract Tables.</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_373 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Chain Data Warehouse.</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_374 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Visualization Builder.</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_375 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Dashboard Builder.</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_376 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Public Dashboard Sharing.</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_377 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Community Discovery.</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=heroes_quality.heroes_quality_manifest; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_383 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=BI Connectors.</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_384 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=MCP for AI Agents.</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_385 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Prompt-to-SQL Agent.</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_386 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Dashboard-from-Prompt.</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_387 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Scheduled Queries.</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_388 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Alerts from Query Results.</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_389 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Data Lineage.</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.whales_institutional_layer.build_exchange_health_80; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_391 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=White-Label Embedded Analytics.</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_392 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Domain Decision Layer.</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_394 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Chain TVL Comparison.</t>
         </is>
       </c>
     </row>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_395 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Directory.</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_397 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DEX Volume.</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_398 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Perps Volume.</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_399 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Volume.</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=04; layer=bd_platform.charting_market_intelligence_layer; cap_400 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoins Intelligence.</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_401 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Bridges Intelligence.</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_402 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Yields Screener.</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_403 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Yield History.</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_404 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Borrowing Rates.</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_405 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquid Staking Intelligence.</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_406 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=RWA Intelligence.</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_407 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Raises / Funding Rounds.</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_408 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Investor Profiles.</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_410 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Treasury Intelligence.</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_411 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Airdrop / Incentive Intelligence.</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_412 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Capital Formation Radar.</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_413 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DeFi Opportunity Screener.</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_414 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DeFi Risk Passport.</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_415 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Aggregation Layer.</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_416 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-DeFi Decision Intelligence.</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_417 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Chain Fundamentals.</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_418 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Fundamentals.</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_419 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Intelligence.</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_420 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Activity Breakdown.</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_421 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Developer Activity.</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_422 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Sector/Ecosystem Comparables.</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_423 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Equities + Crypto Research.</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_424 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Consensus Estimates.</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_425 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI Analyst.</t>
         </is>
       </c>
     </row>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_426 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Thesis Research Workspace.</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_427 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Comparable Company / Protocol Analysis.</t>
         </is>
       </c>
     </row>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_428 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Excel / Sheets Integration.</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_429 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Data Platform.</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_430 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Research Templates.</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_431 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Dashboards.</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_432 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Payment Intelligence.</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_433 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=On-Chain Usage Intelligence.</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_434 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Revenue / Fees / Economic Activity.</t>
         </is>
       </c>
     </row>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_435 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Research Copilot.</t>
         </is>
       </c>
     </row>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_436 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Investment Thesis Scoring.</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.correlation_mindshare.compute_mindshare_correlation_288; production=bd_platform.onchain_hub.defillama_raises (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_438 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Lending Market Risk.</t>
         </is>
       </c>
     </row>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_439 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Collateral Risk.</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_440 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Risk.</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.intelligence_analysis_layer.stat_arb_insight_155; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_442 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidity Risk.</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_443 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Exploit Intelligence.</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_444 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Risk Intelligence.</t>
         </is>
       </c>
     </row>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_445 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DeFi Strategy Risk.</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_446 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Real-Time Risk Alerts.</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_447 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DAO Treasury Risk.</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_448 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional Risk API.</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_449 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Curated On-Chain Dashboards.</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_450 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Narrative-Driven Research.</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_451 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Dominance.</t>
         </is>
       </c>
     </row>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_452 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Aave Multi-Chain Analytics.</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_453 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Risk Curation.</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_454 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Capital Protection Controls.</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_455 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stress Testing.</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_456 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Protocol Contagion.</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_457 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Risk Passport.</t>
         </is>
       </c>
     </row>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.whales_institutional_layer.build_methodology_docs_86; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_459 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Network Data Pro Metrics.</t>
         </is>
       </c>
     </row>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_460 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Atlas Blockchain Search.</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_461 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Address/Balance Search.</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_462 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Transaction Search.</t>
         </is>
       </c>
     </row>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_463 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Block Search.</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_464 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Balance Updates.</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_465 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Network Metrics.</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_466 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Data Feed.</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_467 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Data Pro.</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_468 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Reference Rates.</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_469 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Indexes.</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_470 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Realized Metrics.</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_471 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Supply Metrics.</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_472 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Mining/Validator Metrics.</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_473 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Fee Metrics.</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_474 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Activity Metrics.</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_475 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Metric Workbench.</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_476 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Community Charts/API.</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_477 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market + Network Join.</t>
         </is>
       </c>
     </row>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_478 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Data Quality Methodologies.</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_479 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Research Dataset.</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_480 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional APIs.</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_481 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Network Decision Intelligence.</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_482 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional Trade Data.</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_483 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Order Book Data.</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_484 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=OHLCV Data.</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_485 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Derivatives Data.</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_486 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Open Interest Data.</t>
         </is>
       </c>
     </row>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_487 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Funding Rate Data.</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_488 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Index Data.</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_489 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Reference Pricing.</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_490 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Exchange Metadata.</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_491 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Asset Metadata.</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_492 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Market Archive.</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_493 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Real-Time Streams.</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_494 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Aggregates.</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_495 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidity Analytics.</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_496 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Volatility Analytics.</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_497 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Cap / Supply.</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_498 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=ETF / ETP Data.</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_499 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Coverage Registry.</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=05; layer=bd_platform.defi_yield_intelligence_layer; cap_500 seed metric.</t>
+          <t>مبني جزئيًا — PRODUCTION-ALIGNED — Option A; PRODUCTION-ALIGNED: explicit_option_a binding verified live via cap646.runtime.execute_capability; backend=cap646.data_spine.normalization_report; surface=data_quality_normalization; proof=OPTION_A_PRODUCTION_PROOF.json.</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_501 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional Delivery.</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_502 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Benchmark Administration Metadata.</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_503 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Data Intelligence.</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_504 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Unified Exchange Connector Layer.</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_505 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Tick Trade Data.</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_506 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Quote Data.</t>
         </is>
       </c>
     </row>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_507 seed metric.</t>
+          <t>مبني جزئيًا — PRODUCTION-ALIGNED — Option A; PRODUCTION-ALIGNED: explicit_option_a binding verified live via cap646.runtime.execute_capability; backend=cap646.fallbacks.resolve_ohlcv_closes; surface=ohlcv; proof=OPTION_A_PRODUCTION_PROOF.json.</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_508 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=L1 Order Book.</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_509 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=L2 Order Book.</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_510 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=L3 Order Book.</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_511 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Market Data.</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_512 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Funding / OI / Liquidation Metrics.</t>
         </is>
       </c>
     </row>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_513 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Asset &amp; Symbol Metadata.</t>
         </is>
       </c>
     </row>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_514 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Flat Files.</t>
         </is>
       </c>
     </row>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_515 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=REST API.</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_516 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=WebSocket Streaming.</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_518 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=MCP for AI.</t>
         </is>
       </c>
     </row>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_519 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Exchange Rates / VWAP.</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_520 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Indexes.</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_521 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Volatility Index.</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_522 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=EMS Integration Boundary.</t>
         </is>
       </c>
     </row>
@@ -10906,7 +10906,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_523 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Data Health / SLA Monitoring.</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_524 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Symbol Mapping Engine.</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.run_backtest_74; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_526 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI Market Data Grounding Layer.</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_527 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Heatmap.</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_529 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Cascade Model.</t>
         </is>
       </c>
     </row>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_530 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Global Liquidation Metrics.</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_531 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Open Interest.</t>
         </is>
       </c>
     </row>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_532 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Funding Rates.</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_533 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Order Flow Intelligence.</t>
         </is>
       </c>
     </row>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_534 seed metric.</t>
+          <t>مبني جزئيًا — PRODUCTION-ALIGNED — Option A; PRODUCTION-ALIGNED: explicit_option_a binding verified live via cap646.runtime.execute_capability; backend=cap646.data_spine.bucketed_cvd_report; surface=bucketed_cvd; proof=OPTION_A_PRODUCTION_PROOF.json.</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_535 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Whale vs Retail Flow.</t>
         </is>
       </c>
     </row>
@@ -11166,7 +11166,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_536 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Slippage Intelligence.</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_537 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Global Order Book Metrics.</t>
         </is>
       </c>
     </row>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_538 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Order Book Imbalance.</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_539 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidity Zones.</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_540 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Bot Activity Detection.</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_541 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Positioning.</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_542 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Pressure Score.</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_543 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Orderflow Anomaly Detection.</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_544 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Indicator Platform.</t>
         </is>
       </c>
     </row>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_545 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Trader Cohort Intelligence.</t>
         </is>
       </c>
     </row>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_546 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Derivatives Decision Intelligence.</t>
         </is>
       </c>
     </row>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_547 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=High-Resolution Multi-Pane Charts.</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_548 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Derivatives Dashboard.</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_549 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Funding Rate Intelligence.</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_550 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Open Interest Intelligence.</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_551 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Intelligence.</t>
         </is>
       </c>
     </row>
@@ -11486,7 +11486,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_552 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Futures Volume.</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_553 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Basis Intelligence.</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_554 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Spot Market Data.</t>
         </is>
       </c>
     </row>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_555 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Analytics.</t>
         </is>
       </c>
     </row>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_556 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options IV Surface.</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_557 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Skew.</t>
         </is>
       </c>
     </row>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_558 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Term Structure.</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_559 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=TradFi Context.</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_560 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Multi-Indicator Workspace.</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_561 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Real-Time Prices.</t>
         </is>
       </c>
     </row>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_562 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Data.</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_563 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Data Access.</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_564 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=News Context.</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_565 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Asset Correlation.</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_566 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Derivatives Regime Engine.</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_567 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Decision Intelligence.</t>
         </is>
       </c>
     </row>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_568 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Security_First_Architecture.</t>
         </is>
       </c>
     </row>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_569 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API_Security_Encryption.</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_570 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=High_Availability_Architecture.</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_571 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Infrastructure_Uptime_Shield.</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_572 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional_Data_Architecture.</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_573 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Flexible_Connector_Microservice.</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_574 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional_API_Gateway.</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_575 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API_Data_Pipe.</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_576 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Developer_SDK.</t>
         </is>
       </c>
     </row>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_577 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Pro_Developer_Sandbox.</t>
         </is>
       </c>
     </row>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.execution_rejected_layer.whale_behavior_analysis_216; production=bd_platform.portfolio_rebalancer.portfolio_snapshot (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_579 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Global_Asset_Tracker.</t>
         </is>
       </c>
     </row>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_580 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Multi_Account_Sync.</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12066,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_581 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=On_Chain_Balance_Monitor.</t>
         </is>
       </c>
     </row>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_582 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Profitability_Analyzer.</t>
         </is>
       </c>
     </row>
@@ -12106,7 +12106,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_583 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Margin_Risk_Calculator.</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.news_classifier.coindesk_feed; production=risk_manager.risk_status (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_585 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Volatility_Scoring_System.</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_586 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Volatility_Surface_Analyzer.</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_587 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Delta_Neutral_Calculator.</t>
         </is>
       </c>
     </row>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_588 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=High_Precision_Backtesting.</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_589 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Strategy_Vetting_Algorithm.</t>
         </is>
       </c>
     </row>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_590 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI_Quant_Rating_Engine.</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_591 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Sentiment_Analysis_Engine.</t>
         </is>
       </c>
     </row>
@@ -12286,7 +12286,7 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_592 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Social_Sentiment_Engine.</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_593 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Social_Hype_Analyzer.</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_594 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Narrative_Alert_System.</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_595 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI_Digest_Generator.</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_596 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI_Agent_Consultant.</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_597 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Natural_Language_Interpreter.</t>
         </is>
       </c>
     </row>
@@ -12406,7 +12406,7 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_598 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Wallet_Shadowing.</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_599 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Entity_Tagging_System.</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — WRAPPER-ONLY-UNVERIFIED — TEMPLATE-SEED-STUB; WRAPPER-ONLY-UNVERIFIED: TEMPLATE-SEED-STUB — generated _base()+_metric() surface; static metric from data/legal_retail_commercial_seed.json cap_{id}; no unique domain logic; production /api/cap646 uses cap646 backend_registry handlers, not this template binding. batch=06; layer=bd_platform.institutional_delivery_intelligence_layer; cap_600 seed metric.</t>
+          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Whale_Clustering_Engine.</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=regulatory_compliance_guard.compliant_oracle_sentence; production=instant_alert_engine.engine_stats (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.build_kill_rate_widget_253; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.build_contradiction_replay_254; production=oracle_track_record.public_track_record (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.committee_one_pager_status_255; production=net_edge_truth.compute_net_edge_truth (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.compute_half_life_clock_256; production=oracle_track_record.public_track_record (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.since_you_left_top3_258; production=data_provenance_score.compute_data_provenance_score (capability_keyword).</t>
         </is>
       </c>
     </row>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.corpus_passport_status_260; production=scale_readiness.scale_readiness_report (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.data_sources_layer.compute_opportunity_score_150; production=security_posture.security_posture_report (gap_matrix_component).</t>
         </is>
       </c>
     </row>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978 catalog and batch-01 evidence but absent from cap646.backend_registry (binding_for KeyError). Requires cap646 registration or dedicated CAP978 extension verification track — not auditable via /api/cap646/{id} today.</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978 catalog and batch-01 evidence but absent from cap646.backend_registry (binding_for KeyError). Requires cap646 registration or dedicated CAP978 extension verification track — not auditable via /api/cap646/{id} today.</t>
         </is>
       </c>
     </row>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978 catalog and batch-01 evidence but absent from cap646.backend_registry (binding_for KeyError). Requires cap646 registration or dedicated CAP978 extension verification track — not auditable via /api/cap646/{id} today.</t>
         </is>
       </c>
     </row>
@@ -16726,7 +16726,7 @@
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978 catalog and batch-01 evidence but absent from cap646.backend_registry (binding_for KeyError). Requires cap646 registration or dedicated CAP978 extension verification track — not auditable via /api/cap646/{id} today.</t>
         </is>
       </c>
     </row>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>مبني جزئيًا</t>
+          <t>مبني جزئيًا — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978 catalog and batch-01 evidence but absent from cap646.backend_registry (binding_for KeyError). Requires cap646 registration or dedicated CAP978 extension verification track — not auditable via /api/cap646/{id} today.</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -14946,7 +14946,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.white_label_api_brokerage_725 + tests/test_hero_batch_01_capabilities.py</t>
+          <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.white_label_api_brokerage_725 + tests/test_hero_batch_01_capabilities.py — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978/heroes evidence but absent from cap646.backend_registry (binding_for KeyError). Historical quad-evidence used pdf_capability_registry — apparent success did NOT prove production /api/cap646 path. Requires cap646 registration or dedicated CAP978 extension verification track.</t>
         </is>
       </c>
     </row>
@@ -16706,7 +16706,7 @@
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — constitution_gates.ensure_execution_gates</t>
+          <t>مبني وشغال فعليًا — constitution_gates.ensure_execution_gates — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978/heroes evidence but absent from cap646.backend_registry (binding_for KeyError). Historical quad-evidence used pdf_capability_registry — apparent success did NOT prove production /api/cap646 path. Requires cap646 registration or dedicated CAP978 extension verification track.</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — ml/market_replay_bootstrap.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/footprint_analytics.py footprint_snapshot</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=due_diligence_bundle.build_full_due_diligence_bundle; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.attach_market_health_bundle_106_112_114; production=oracle_track_record.public_track_record (track_default).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.get_footer_disclosure_57 + tests/test_legal_retail_batch57_66.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — platform_api.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.legal_commercial_layer.create_sar_workflow_59; production=org_tenant.org_isolation_status (track_default).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.legal_commercial_layer.pricing_transparency_manifest_60; production=instant_alert_engine.engine_stats (gap_matrix_component).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.run_legal_commercial_e2e_57_61 + tests/test_legal_retail_batch57_66.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.institutional_b2b_layer.build_ic_report_87; production=ml.market_replay_bootstrap.bootstrap_market_replay_dataset (gap_matrix_component).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.retail_intelligence_layer.attach_clear_answer_63; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.glossary_manifest_64 + tests/test_legal_retail_batch57_66.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.evaluate_contextual_alert_65 + tests/test_legal_retail_batch57_66.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.run_retail_intelligence_e2e_62_66 + tests/test_legal_retail_batch57_66.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.health_score_from_holdings_67 + tests/test_pro_trader_batch67_76.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.pro_trader_layer.evaluate_ttv_flow_69; production=ai_oracle.evaluate_opportunity (gap_matrix_component).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.save_filter_preset_70 + tests/test_pro_trader_batch67_76.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.pro_trader_layer.build_whale_narrative_71; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.pro_trader_layer.classify_onchain_signal_72; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.pro_trader_layer.build_multi_dim_analysis_73; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.pro_trader_layer.run_backtest_74; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.run_pro_trader_e2e_67_76 + tests/test_pro_trader_batch67_76.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer.build_advanced_risk_report_77; production=bd_platform.onchain_hub.defillama_raises (capability_keyword).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_impact_analysis_78 + tests/test_whales_institutional_batch77_86.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer.analyze_wallet_surveillance_79; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_exchange_health_80 + tests/test_whales_institutional_batch77_86.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer.build_unified_portfolio_view_81; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.evaluate_liquidation_alert_82 + tests/test_whales_institutional_batch77_86.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.smb_institution_status_83 + tests/test_whales_institutional_batch77_86.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer.enrich_openapi_with_fee_metadata_85; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer.run_whales_institutional_e2e_77_86; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats + tests/test_institutional_b2b_batch87_94.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.institutional_b2b_layer.map_org_role_to_team_88; production=bd_platform.liquidation_radar.liquidation_radar (gap_matrix_component).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.sla_status_89 + tests/test_institutional_b2b_batch87_94.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.white_label_status_90 + tests/test_institutional_b2b_batch87_94.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.institutional_b2b_layer.compute_vwap_deviation_91; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.attach_confidence_calibration_93 + tests/test_institutional_b2b_batch87_94.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.run_institutional_b2b_e2e_87_94 + tests/test_institutional_b2b_batch87_94.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95 + tests/test_infra_intelligence_batch95_104.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.infra_intelligence_layer.enqueue_stream_event_96; production=scale_readiness.scale_readiness_report (track_default).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — acquisition_assets_service.py — revenue intelligence pillar</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.infra_intelligence_layer.validate_signal_uniqueness_98; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.filter_sybil_clusters_99 + tests/test_infra_intelligence_batch95_104.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs + tests/test_infra_intelligence_batch95_104.py</t>
+          <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
     </row>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D827"/>
+  <dimension ref="A1:G827"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,21 @@
           <t>الحالة</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>classification_1_100</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>overlap_batch01</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>link_eligible</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -469,6 +484,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=bd_platform.footprint_analytics.footprint_snapshot; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -489,6 +507,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=trade_simulator.simulate_spot_trade; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -509,6 +530,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.free_tier_capabilities.wallet_profiler_for_token; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -529,6 +553,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.free_tier_capabilities.smart_money_tracking; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,6 +576,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=bd_platform.onchain_hub.dexscreener_pairs (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -569,6 +599,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -589,6 +622,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -609,6 +645,9 @@
           <t>مبني وشغال فعليًا — cap646.institutional_controls._sec_8</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -629,6 +668,9 @@
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.execution_risk_score_9 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -649,6 +691,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=instant_alert_engine.engine_stats; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -669,6 +714,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=arbitrage_service.scan_arbitrage_opportunities; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -689,6 +737,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.whales_institutional_layer.evaluate_liquidation_alert_82; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -709,6 +760,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -729,6 +783,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=market_context.whale_alert_message; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -749,6 +806,9 @@
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.flash_loan_attack_proximity_15 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -769,6 +829,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -789,6 +852,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=alert_service.subscribe_alerts; production=instant_alert_engine.engine_stats (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -809,6 +875,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.alert_orchestration.alert_orchestration_status_18; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -829,6 +898,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.get_alert_policy_75; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -849,6 +921,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.append_audit_event_242; production=bd_platform.portfolio_rebalancer.portfolio_snapshot (capability_keyword).</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -869,6 +944,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.alert_orchestration.alert_orchestration_status_18; production=scale_readiness.scale_readiness_report (track_default).</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -889,6 +967,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.list_etherscan_watchlist_246; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -909,6 +990,9 @@
           <t>مبني وشغال فعليًا — aggregator.py + live_book_hub.py + cap646/handlers/market.py</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -929,6 +1013,9 @@
           <t>مبني وشغال فعليًا — aggregator.py + live_book_hub.py + cap646/handlers/market.py</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -949,6 +1036,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_GENERIC_HANDLER; audit=bd_platform.footprint_analytics.footprint_snapshot; production=trust_pulse.build_trust_pulse (track_default).</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -969,6 +1059,9 @@
           <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -989,6 +1082,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1009,6 +1105,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.retail_intelligence_layer.evaluate_contextual_alert_65; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1029,6 +1128,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.retail_intelligence_layer.compare_discipline_66; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1049,6 +1151,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1069,6 +1174,9 @@
           <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.build_discipline_tab_66</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1089,6 +1197,9 @@
           <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1109,6 +1220,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.retail_intelligence_layer.build_one_clear_answer_63; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1129,6 +1243,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1149,6 +1266,9 @@
           <t>مبني وشغال فعليًا — bd_platform/footprint_analytics.py + market_analysis_layer</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1169,6 +1289,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=risk_manager.is_trading_frozen; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1189,6 +1312,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1209,6 +1335,9 @@
           <t>مبني وشغال فعليًا — bd_platform/telegram_agent.py + intelligence_analysis_layer #161</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1229,6 +1358,9 @@
           <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1249,6 +1381,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189; production=bd_platform.onchain_hub.lookintobitcoin_macro (capability_keyword).</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1269,6 +1404,9 @@
           <t>مبني وشغال فعليًا — execution_engine.get_execution_status</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1289,6 +1427,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1309,6 +1450,9 @@
           <t>مبني وشغال فعليًا — bd_platform/mvrv_realignment.py compute_mvrv_realignment</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1329,6 +1473,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153; production=bd_platform.portfolio_rebalancer.portfolio_snapshot (capability_keyword).</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1349,6 +1496,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.free_tier_capabilities.smart_money_leaderboard; production=market_context.probe_price_sources (track_default).</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1369,6 +1519,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_GENERIC_HANDLER; audit=bd_platform.slippage_tolerance_optimizer.optimize_slippage_tolerance; production=market_context.probe_price_sources (track_default).</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1389,6 +1542,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.whales_institutional_layer.build_exchange_health_80; production=market_context.probe_price_sources (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1409,6 +1565,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.ingest_bybit_price_243; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1429,6 +1588,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.flash_crash_protection.flash_crash_protection_status_49; production=options_fetcher.fetch_options_overview (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1449,6 +1611,9 @@
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.mvrv_z_score_50 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1469,6 +1634,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1489,6 +1657,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1509,6 +1680,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1529,6 +1703,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1549,6 +1726,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1569,6 +1749,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1589,6 +1772,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1609,6 +1795,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1629,6 +1818,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1649,6 +1841,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1669,6 +1864,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1689,6 +1887,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1709,6 +1910,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1729,6 +1933,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1749,6 +1956,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1769,6 +1979,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1789,6 +2002,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1809,6 +2025,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1829,6 +2048,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1849,6 +2071,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1869,6 +2094,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1889,6 +2117,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1909,6 +2140,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1929,6 +2163,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1949,6 +2186,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1969,6 +2209,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1989,6 +2232,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2009,6 +2255,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2029,6 +2278,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2049,6 +2301,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2069,6 +2324,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2089,6 +2347,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2109,6 +2370,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2129,6 +2393,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2149,6 +2416,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2169,6 +2439,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2189,6 +2462,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2209,6 +2485,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2229,6 +2508,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2249,6 +2531,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2269,6 +2554,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2289,6 +2577,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2309,6 +2600,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2329,6 +2623,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2349,6 +2646,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2369,6 +2669,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2389,6 +2692,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2409,6 +2715,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2429,6 +2738,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2449,6 +2761,9 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2469,6 +2784,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.infra_intelligence_layer.validate_oracle_freshness_101; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2489,6 +2807,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.infra_intelligence_layer.compute_il_vulnerability_102; production=trust_pulse.build_trust_pulse (track_default).</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2509,6 +2830,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer._compute_drawdown_duration_103; production=hot_storage.get_hot_storage_stats (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2529,6 +2853,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.infra_intelligence_layer.run_infra_intelligence_e2e_95_104 + tests/test_hero_batch_02_capabilities.py | proof=04b6f48520e87a33 (deferred)</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2549,6 +2876,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.attach_tail_risk_to_backtest_105; production=data_provenance_score.compute_data_provenance_score (track_default).</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2569,6 +2899,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_contagion_vector_106; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2589,6 +2922,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_whale_retail_ratio_107; production=signal_registry.registry_stats (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2609,6 +2945,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2629,6 +2968,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.attach_liquidation_anchors_109; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2649,6 +2991,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.attach_whale_extensions_107_110; production=ai_oracle.evaluate_opportunity (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2669,6 +3014,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_spx_correlation_111; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2689,6 +3037,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_gcli_112; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2709,6 +3060,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_imbalance_delta_113; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2729,6 +3083,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.attach_market_health_bundle_106_112_114; production=due_diligence_bundle.build_full_due_diligence_bundle (capability_keyword).</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2749,6 +3106,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_volume_velocity_115; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2769,6 +3129,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.run_market_analysis_e2e_105_116; production=bd_platform.onchain_hub.dexscreener_pairs (capability_keyword).</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2789,6 +3152,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.compute_liquidity_vacuum_117; production=data_provenance_score.compute_data_provenance_score (capability_keyword).</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2809,6 +3175,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.attach_risk_distribution_118; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2829,6 +3198,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.gas_spike_alert_119 + tests/test_hero_batch_02_capabilities.py | proof=94c9046b8987c79f (deferred)</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2849,6 +3221,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.attach_leverage_risk_120 + tests/test_hero_batch_02_capabilities.py | proof=fb767a8fb1d81fc5 (deferred)</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2869,6 +3244,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.attach_journal_attribution_121; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2889,6 +3267,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.compute_structural_break_122 + tests/test_hero_batch_02_capabilities.py | proof=8219e7cbbb4af67e (deferred)</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2909,6 +3290,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2929,6 +3313,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.detect_fair_value_gaps_124; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2949,6 +3336,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.custody_tracking_status_125 + tests/test_hero_batch_02_capabilities.py | proof=ef2d5b8e047cfe12 (deferred)</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2969,6 +3359,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.dex_front_running_risk_126 + tests/test_hero_batch_01_capabilities.py | proof=f358382e13507bd6 (deferred)</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2989,6 +3382,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.orderbook_inefficiency_insight_127 + tests/test_hero_batch_02_capabilities.py | proof=88def6faccb782cc (deferred)</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3009,6 +3405,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.run_advanced_ta_risk_e2e_117_128 + tests/test_hero_batch_02_capabilities.py | proof=39b021e04931808a (deferred)</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3029,6 +3428,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_platform_layer.attach_sybil_clustering_129; production=sentiment_gate.fetch_asset_sentiment (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3049,6 +3451,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.transaction_risk_insight_130 + tests/test_hero_batch_02_capabilities.py | proof=140846bc87832d7a (deferred)</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3069,6 +3474,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.analyze_dust_assets_131 + tests/test_hero_batch_02_capabilities.py | proof=c2de62f8049cebf9 (deferred)</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3089,6 +3497,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 + tests/test_hero_batch_02_capabilities.py | proof=44ded9a4f1dbcaef (deferred)</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3109,6 +3520,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_platform_layer.attach_macro_nexus_to_multi_dim_133; production=bd_platform.news_classifier.coindesk_feed (capability_keyword).</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3129,6 +3543,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_platform_layer.compute_delta_convergence_134; production=bd_platform.news_classifier.coindesk_feed (capability_keyword).</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3149,6 +3566,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.locate_liquidity_vortex_135 + tests/test_hero_batch_02_capabilities.py | proof=a25a44a234d04ca4 (deferred)</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3169,6 +3589,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.support_chat_response_136 + tests/test_hero_batch_02_capabilities.py | proof=043a8ec1ca42c2ea (deferred)</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3189,6 +3612,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.b2b_relationships_status_137 + tests/test_hero_batch_02_capabilities.py | proof=3453565f15e4b18d (deferred)</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3209,6 +3635,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.institution_features_status_138 + tests/test_hero_batch_02_capabilities.py | proof=db89ec286186839d (deferred)</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -3229,6 +3658,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.run_onchain_platform_e2e_129_139 + tests/test_hero_batch_02_capabilities.py | proof=7469f8a938c9efc8 (deferred)</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3249,6 +3681,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.white_label_status_140 + tests/test_hero_batch_02_capabilities.py | proof=0d5f9eb47b907fa4 (deferred)</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -3269,6 +3704,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_coindesk_feed_141; production=bd_platform.token_unlocks.unlock_calendar (capability_keyword).</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -3289,6 +3727,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_santiment_metrics_142; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -3309,6 +3750,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_event_calendar_143; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -3329,6 +3773,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_whale_alert_144; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -3349,6 +3796,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_cmc_price_145; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -3369,6 +3819,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.validate_oracle_consensus_145_146; production=bd_platform.derivatives_hub.derivatives_overview (capability_keyword).</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -3389,6 +3842,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.signal_engine_status_147 + tests/test_hero_batch_02_capabilities.py | proof=ddc516bdba67fe96 (deferred)</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -3409,6 +3865,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_blockchain_com_148; production=due_diligence_bundle.build_full_due_diligence_bundle (capability_keyword).</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -3429,6 +3888,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_defillama_149; production=risk_manager.risk_status (capability_keyword).</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -3449,6 +3911,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.attach_opportunity_to_daily_top3_150; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -3469,6 +3934,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.explain_opportunity_151 + tests/test_hero_batch_02_capabilities.py | proof=6a1f7649399cddc9 (deferred)</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -3489,6 +3957,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.run_data_sources_e2e_140_152 + tests/test_hero_batch_02_capabilities.py | proof=0bc1db8886bcdad8 (deferred)</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -3509,6 +3980,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153 + tests/test_hero_batch_02_capabilities.py | proof=721755483b2945dc (deferred)</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -3529,6 +4003,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -3549,6 +4026,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.intelligence_analysis_layer.stat_arb_insight_155 + tests/test_hero_batch_02_capabilities.py | proof=7fa98659e3dadcb4 (deferred)</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -3569,6 +4049,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.asset_registry_105_coins_156; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -3589,6 +4072,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -3609,6 +4095,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.multi_venue_websocket_status_158; production=cap646.fallbacks.resolve_gas_usd (capability_keyword).</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -3629,6 +4118,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.compute_gas_volatility_profile_159; production=hot_storage.get_hot_storage_stats (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -3649,6 +4141,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.detect_volatility_squeeze_160; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -3669,6 +4164,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.alert_delivery_status_161; production=org_tenant.org_isolation_status (track_default).</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -3689,6 +4187,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.data_grid_ui_status_162; production=data_provenance_score.compute_data_provenance_score (capability_keyword).</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -3709,6 +4210,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.run_intelligence_analysis_e2e_153_163; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -3729,6 +4233,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.liquidity_impact_warning_164 + tests/test_hero_batch_01_capabilities.py | proof=808b7e3033384b16 (deferred)</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -3749,6 +4256,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.hashrate_capitulation_forecast_165; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -3769,6 +4279,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.brokerage_rejected_status_166 + tests/test_hero_batch_02_capabilities.py | proof=2ed11344777da646 (deferred)</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -3789,6 +4302,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.validate_time_sync_167; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -3809,6 +4325,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.attach_cluster_index_168; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -3829,6 +4348,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.attach_correlation_decay_169; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -3849,6 +4371,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -3869,6 +4394,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.attach_m2_macro_flow_171; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -3889,6 +4417,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -3909,6 +4440,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -3929,6 +4463,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.full_white_label_status_174 + tests/test_hero_batch_02_capabilities.py | proof=db8bc694743b83cc (deferred)</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -3949,6 +4486,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -3969,6 +4509,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.run_risk_infrastructure_e2e_164_176 + tests/test_hero_batch_02_capabilities.py | proof=a84a3a72b074edab (deferred)</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -3989,6 +4532,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.analyze_arbitrage_cost_177; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -4009,6 +4555,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.attach_scenarios_178; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -4029,6 +4578,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.build_command_center_dashboard_179; production=market_context.probe_price_sources (track_default).</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -4049,6 +4601,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.attach_whale_visualization_180; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -4069,6 +4624,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -4089,6 +4647,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.white_label_infrastructure_status_182; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -4109,6 +4670,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.heroes_capability_layer.onchain_usage_intelligence_183 + tests/test_hero_batch_01_capabilities.py | proof=b7369963edda8686 (deferred)</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -4129,6 +4693,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.fund_reporting_status_184; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -4149,6 +4716,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.acquisition_evidence_package_185 + tests/test_hero_batch_02_capabilities.py | proof=db9e7a683209d837 (deferred)</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -4169,6 +4739,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.continuous_learning_status_186 + tests/test_hero_batch_02_capabilities.py | proof=5cfc751f4b2a31ef (deferred)</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -4189,6 +4762,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.latency_monitoring_status_187; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -4209,6 +4785,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.risk_alert_user_confirmation_188 + tests/test_hero_batch_02_capabilities.py | proof=127dde368dd13a82 (deferred)</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -4229,6 +4808,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189; production=market_context.probe_price_sources (track_default).</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -4249,6 +4831,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 + tests/test_hero_batch_02_capabilities.py | proof=09ff0255054c9fff (deferred)</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -4269,6 +4854,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.run_arbitrage_portfolio_ux_e2e_177_191 + tests/test_hero_batch_02_capabilities.py | proof=1f1aa38c1c805843 (deferred)</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -4289,6 +4877,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.analyze_funding_rate_192; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -4309,6 +4900,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.derivatives_ta_research_layer.auto_arbitrage_rejected_status_193 + tests/test_hero_batch_02_capabilities.py | proof=56673bf309232b01 (deferred)</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -4329,6 +4923,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.compute_cvd_194; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -4349,6 +4946,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.derivatives_ta_research_layer.strategy_simulator_195 + tests/test_hero_batch_02_capabilities.py | proof=52632db04722442b (deferred)</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -4369,6 +4969,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.ingest_yahoo_finance_macro_196; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -4389,6 +4992,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.attach_macro_research_sources_196_197; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -4409,6 +5015,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.ingest_binance_research_198; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -4429,6 +5038,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.ingest_messari_research_199; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -4449,6 +5061,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.ingest_coingecko_reports_200; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -4469,6 +5084,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.quantitative_analysis_framework_201; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -4489,6 +5107,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.discover_hidden_opportunities_202; production=scale_readiness.scale_readiness_report (track_default).</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -4509,6 +5130,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.run_derivatives_ta_research_e2e_192_203; production=bd_platform.onchain_hub.dexscreener_pairs (capability_keyword).</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -4529,6 +5153,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_bscscan_204; production=bd_platform.onchain_hub.defillama_raises (capability_keyword).</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -4549,6 +5176,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_glassnode_metrics_205; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -4569,6 +5199,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_uniswap_subgraph_206; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -4589,6 +5222,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_aave_data_207; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -4609,6 +5245,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_reddit_sentiment_208; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -4629,6 +5268,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -4649,6 +5291,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.analyze_predictive_arbitrage_210; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -4669,6 +5314,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.cross_margin_risk_alert_211; production=org_tenant.org_isolation_status (track_default).</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -4689,6 +5337,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.hedge_effectiveness_analysis_212; production=instant_alert_engine.engine_stats (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -4709,6 +5360,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.capital_allocation_insight_213; production=instant_alert_engine.engine_stats (capability_keyword).</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -4729,6 +5383,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.build_whale_narrative_71; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -4749,6 +5406,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_defi_sources_layer.flash_loan_gas_rejected_status_215 + tests/test_onchain_defi_sources_batch204_216.py | proof=faa17c104ae759de (deferred)</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -4769,6 +5429,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -4789,6 +5452,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.analyze_best_venue_217; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -4809,6 +5475,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.attach_order_journal_218; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -4829,6 +5498,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.analyze_nlp_sentiment_219; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -4849,6 +5521,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.attach_pattern_outcome_220; production=data_provenance_score.compute_data_provenance_score (track_default).</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -4869,6 +5544,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.market_slippage_analysis_221; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -4889,6 +5567,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.monitor_exchange_latency_222; production=signal_registry.registry_stats (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -4909,6 +5590,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.analyze_defi_fundamentals_223; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -4929,6 +5613,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -4949,6 +5636,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.pwa_strategy_status_225; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -4969,6 +5659,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.analyze_launch_event_226; production=ai_oracle.evaluate_opportunity (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -4989,6 +5682,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -5009,6 +5705,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.simulate_drawdown_hedge_228; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -5029,6 +5728,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.attach_reasoning_explanation_229; production=arbitrage_service.scan_arbitrage_opportunities (capability_keyword).</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -5049,6 +5751,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.analyze_cross_exchange_divergence_230; production=arbitrage_service.scan_arbitrage_opportunities (capability_keyword).</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -5069,6 +5774,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.intelligence_ux_extensions_layer.triangular_arbitrage_status_231 + tests/test_intelligence_ux_extensions_batch228_241.py | proof=75574418a6a8ca4b (deferred)</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -5089,6 +5797,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.attach_arbitrage_comparison_230_232; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -5109,6 +5820,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233; production=bd_platform.liquidation_radar.liquidation_radar (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -5129,6 +5843,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -5149,6 +5866,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -5169,6 +5889,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -5189,6 +5912,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.generate_market_summary_237; production=risk_manager.risk_status (capability_keyword).</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -5209,6 +5935,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.scan_market_opportunities_238; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -5229,6 +5958,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -5249,6 +5981,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.compute_s2f_240; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -5269,6 +6004,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.run_intelligence_ux_extensions_e2e_228_241; production=sentiment_gate.fetch_asset_sentiment (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -5289,6 +6027,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.attach_audit_log_id_242; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -5309,6 +6050,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.ingest_bybit_price_243; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -5329,6 +6073,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -5349,6 +6096,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -5369,6 +6119,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.list_etherscan_watchlist_246; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -5389,6 +6142,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.generate_weekly_digest_247; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -5409,6 +6165,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.manual_performance_tracker_248; production=bd_platform.telegram_agent.handle_agent_message (capability_keyword).</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -5429,6 +6188,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.security_trust_data_layer.trad_simulator_rejected_status_249 + tests/test_security_trust_data_batch242_261.py | proof=d60108f2983f98a4 (deferred)</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -5449,6 +6211,9 @@
           <t>مبني جزئيًا — [deferred] bd_platform.security_trust_data_layer.execution_speed_rejected_status_250 + tests/test_security_trust_data_batch242_261.py | proof=4ca762095f9b06d2 (deferred)</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -5469,6 +6234,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.compute_token_velocity_251; production=ai_oracle.evaluate_opportunity (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -5489,6 +6257,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.ingest_google_trends_252; production=bd_platform.liquidation_radar.liquidation_radar (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -5509,6 +6280,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.build_kill_rate_widget_253; production=bd_platform.liquidation_radar.liquidation_radar (capability_keyword).</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -5529,6 +6303,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.build_contradiction_replay_254; production=bd_platform.liquidation_radar.liquidation_radar (capability_keyword).</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -5549,6 +6326,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.committee_one_pager_status_255; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -5569,6 +6349,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.compute_half_life_clock_256; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -5589,6 +6372,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.proof_arena_lite_status_257; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -5609,6 +6395,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.since_you_left_top3_258; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -5629,6 +6418,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.apply_anti_hype_mode_259; production=bd_platform.derivatives_hub.derivatives_overview (capability_keyword).</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -5649,6 +6441,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.corpus_passport_status_260; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -5669,6 +6464,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.run_security_trust_data_e2e_242_261; production=bd_platform.derivatives_hub.derivatives_overview (capability_keyword).</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -5689,6 +6487,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Open Interest.</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -5709,6 +6510,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Volume.</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -5729,6 +6533,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options IV / Skew.</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -5749,6 +6556,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Max Pain / Gamma Context.</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -5769,6 +6579,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Spot Market Intelligence.</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -5789,6 +6602,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Order Book / Market Depth.</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -5809,6 +6625,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Derivatives Data.</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -5829,6 +6648,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Exchange Comparison.</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -5849,6 +6671,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Cascade Proximity.</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -5869,6 +6694,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Leverage Pressure Score.</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -5889,6 +6717,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_onchain_intelligence_layer.api_data_platform_status_272; production=hot_storage.get_hot_storage_stats (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -5909,6 +6740,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Multi-Model Liquidation Comparison.</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -5929,6 +6763,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_onchain_intelligence_layer.derivatives_alerts_status_274; production=instant_alert_engine.engine_stats (capability_keyword).</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -5949,6 +6786,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Domain Decision Intelligence.</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -5969,6 +6809,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Entity Resolution Engine.</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -5989,6 +6832,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Address Labeling System.</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -6009,6 +6855,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Entity Profiles.</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -6029,6 +6878,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.build_share_card_68; production=onchain_tracker.build_onchain_context_safe (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -6049,6 +6901,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Portfolio Holdings.</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -6069,6 +6924,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Balance History.</t>
         </is>
       </c>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -6089,6 +6947,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Entity PnL.</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -6109,6 +6970,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Exchange Usage Intelligence.</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -6129,6 +6993,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Top Counterparties.</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -6149,6 +7016,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Visualizer / Network Graph.</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -6169,6 +7039,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Automated Trace / Path Finding.</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -6189,6 +7062,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Chain Trace.</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -6209,6 +7085,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.correlation_mindshare.compute_mindshare_correlation_288; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -6229,6 +7108,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Token Exchange Flows.</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -6249,6 +7131,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Token Transaction Explorer.</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -6269,6 +7154,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Dashboards.</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -6289,6 +7177,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Alerts.</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -6309,6 +7200,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Private Labels.</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -6329,6 +7223,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Archive / Historical Portfolio Snapshot.</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -6349,6 +7246,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI Market Insights.</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -6369,6 +7269,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Whale Movement Intelligence.</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -6389,6 +7292,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_onchain_intelligence_layer.fraud_suspicious_activity_297; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -6409,6 +7315,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API On-Chain Intelligence.</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -6429,6 +7338,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_GENERIC_HANDLER; audit=bd_platform.news_classifier.classify_headlines; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -6449,6 +7361,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_onchain_intelligence_layer.run_derivatives_onchain_intelligence_e2e_262_300; production=bd_platform.tradingview_bridge.chart_config (capability_keyword).</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -6469,6 +7384,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Multi-Chart Layouts.</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -6489,6 +7407,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Technical Indicator Library.</t>
         </is>
       </c>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -6509,6 +7430,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Indicator Scripting.</t>
         </is>
       </c>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -6529,6 +7453,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Strategy Backtesting.</t>
         </is>
       </c>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -6549,6 +7476,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Screener.</t>
         </is>
       </c>
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -6569,6 +7499,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Pine-Style Screener.</t>
         </is>
       </c>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -6589,6 +7522,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Smart Alerts.</t>
         </is>
       </c>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -6609,6 +7545,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Watchlists.</t>
         </is>
       </c>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -6629,6 +7568,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Economic Calendar.</t>
         </is>
       </c>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -6649,6 +7591,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Crypto Calendar / Events.</t>
         </is>
       </c>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -6669,6 +7614,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=News Integration.</t>
         </is>
       </c>
+      <c r="E312" t="inlineStr"/>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -6689,6 +7637,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Heatmaps.</t>
         </is>
       </c>
+      <c r="E313" t="inlineStr"/>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -6709,6 +7660,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Technical Ratings.</t>
         </is>
       </c>
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -6729,6 +7683,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Drawing Tools.</t>
         </is>
       </c>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -6749,6 +7706,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Replay Mode.</t>
         </is>
       </c>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -6769,6 +7729,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.sse_stream.sse_digest_status_316; production=bd_platform.tradingview_bridge.chart_config (capability_keyword).</t>
         </is>
       </c>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -6789,6 +7752,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Community Scripts.</t>
         </is>
       </c>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -6809,6 +7775,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Broker Comparison.</t>
         </is>
       </c>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -6829,6 +7798,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Paper Trading / Simulation.</t>
         </is>
       </c>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -6849,6 +7821,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Workspace.</t>
         </is>
       </c>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -6869,6 +7844,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Intelligence Screener.</t>
         </is>
       </c>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -6889,6 +7867,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Decision-First Mode.</t>
         </is>
       </c>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -6909,6 +7890,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional L1/L2 Market Data.</t>
         </is>
       </c>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -6929,6 +7913,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Reference Data Registry.</t>
         </is>
       </c>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -6949,6 +7936,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Spot &amp; Derivatives Coverage.</t>
         </is>
       </c>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -6969,6 +7959,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DeFi Market Data.</t>
         </is>
       </c>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -6989,6 +7982,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Depth &amp; Liquidity Intelligence.</t>
         </is>
       </c>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -7009,6 +8005,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Fair Market Value Pricing.</t>
         </is>
       </c>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -7029,6 +8028,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Best Execution Pricing.</t>
         </is>
       </c>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -7049,6 +8051,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=trade_simulator.simulate_spot_trade; production=market_context.probe_price_sources (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -7069,6 +8074,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=ETF Reference Rates / iNAV.</t>
         </is>
       </c>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -7089,6 +8097,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Commodity / TradFi Reference Rates.</t>
         </is>
       </c>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -7109,6 +8120,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Indices.</t>
         </is>
       </c>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -7129,6 +8143,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Risk Analytics.</t>
         </is>
       </c>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -7149,6 +8166,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Derivatives Listing Analytics.</t>
         </is>
       </c>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -7169,6 +8189,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Surveillance.</t>
         </is>
       </c>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -7189,6 +8212,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AML/CFT On-Chain Monitoring.</t>
         </is>
       </c>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -7209,6 +8235,9 @@
           <t>مبني جزئيًا — PRODUCTION-ALIGNED — Option A; PRODUCTION-ALIGNED: explicit_option_a binding verified live via cap646.runtime.execute_capability; backend=cap646.data_spine.data_quality_pipeline_report; surface=data_quality_pipeline; proof=OPTION_A_PRODUCTION_PROOF.json.</t>
         </is>
       </c>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -7229,6 +8258,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.apply_opportunity_filter_70; production=data_provenance_score.compute_data_provenance_score (capability_keyword).</t>
         </is>
       </c>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -7249,6 +8281,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Real-Time REST/gRPC Streaming.</t>
         </is>
       </c>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -7269,6 +8304,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Data Archive.</t>
         </is>
       </c>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -7289,6 +8327,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Venue Quality Ranking.</t>
         </is>
       </c>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -7309,6 +8350,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Execution Quality Analytics.</t>
         </is>
       </c>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -7329,6 +8373,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional SLA Monitoring.</t>
         </is>
       </c>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -7349,6 +8396,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Institutional Decision Layer.</t>
         </is>
       </c>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -7369,6 +8419,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Standardized Financial Metrics.</t>
         </is>
       </c>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -7389,6 +8442,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Fees Intelligence.</t>
         </is>
       </c>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -7409,6 +8465,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Revenue Intelligence.</t>
         </is>
       </c>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -7429,6 +8488,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Token Incentives.</t>
         </is>
       </c>
+      <c r="E350" t="inlineStr"/>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -7449,6 +8511,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Earnings / Economic Profit Proxy.</t>
         </is>
       </c>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -7469,6 +8534,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Active Users.</t>
         </is>
       </c>
+      <c r="E352" t="inlineStr"/>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -7489,6 +8557,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Core Developers.</t>
         </is>
       </c>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -7509,6 +8580,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Code Commits.</t>
         </is>
       </c>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -7529,6 +8603,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=TVL Intelligence.</t>
         </is>
       </c>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -7549,6 +8626,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Borrowed / Loans Outstanding.</t>
         </is>
       </c>
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -7569,6 +8649,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244; production=cap646.fallbacks.resolve_dex_volume_snapshot (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -7589,6 +8672,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Supply.</t>
         </is>
       </c>
+      <c r="E358" t="inlineStr"/>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -7609,6 +8695,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Valuation Multiples.</t>
         </is>
       </c>
+      <c r="E359" t="inlineStr"/>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -7629,6 +8718,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Growth Metrics.</t>
         </is>
       </c>
+      <c r="E360" t="inlineStr"/>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -7649,6 +8741,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Margins / Take Rate.</t>
         </is>
       </c>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -7669,6 +8764,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Project Comparables.</t>
         </is>
       </c>
+      <c r="E362" t="inlineStr"/>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -7689,6 +8787,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Sector Comparables.</t>
         </is>
       </c>
+      <c r="E363" t="inlineStr"/>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -7709,6 +8810,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Tokenized Asset Coverage.</t>
         </is>
       </c>
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -7729,6 +8833,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Fundamental Screener.</t>
         </is>
       </c>
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -7749,6 +8856,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Financial Statement View.</t>
         </is>
       </c>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -7769,6 +8879,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Data Methodology Registry.</t>
         </is>
       </c>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -7789,6 +8902,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Source Data Provenance.</t>
         </is>
       </c>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -7809,6 +8925,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API / Data Export.</t>
         </is>
       </c>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -7829,6 +8948,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Fundamental Decision Intelligence.</t>
         </is>
       </c>
+      <c r="E370" t="inlineStr"/>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -7849,6 +8971,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=SQL On-Chain Query Workspace.</t>
         </is>
       </c>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -7869,6 +8994,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Curated Data Models.</t>
         </is>
       </c>
+      <c r="E372" t="inlineStr"/>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -7889,6 +9017,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Decoded Smart Contract Tables.</t>
         </is>
       </c>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -7909,6 +9040,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Chain Data Warehouse.</t>
         </is>
       </c>
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -7929,6 +9063,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Visualization Builder.</t>
         </is>
       </c>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -7949,6 +9086,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Dashboard Builder.</t>
         </is>
       </c>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -7969,6 +9109,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Public Dashboard Sharing.</t>
         </is>
       </c>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -7989,6 +9132,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Community Discovery.</t>
         </is>
       </c>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -8009,6 +9155,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=exchange_currency_status.deposit_currencies_open; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -8029,6 +9178,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -8049,6 +9201,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=exchange_currency_status.deposit_currencies_open; production=cap646.fallbacks.resolve_gas_usd (capability_keyword).</t>
         </is>
       </c>
+      <c r="E381" t="inlineStr"/>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -8069,6 +9224,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=exchange_currency_status.withdrawal_currencies_closed; production=data_provenance_score.compute_data_provenance_score (track_default).</t>
         </is>
       </c>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -8089,6 +9247,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=heroes_quality.heroes_quality_manifest; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -8109,6 +9270,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=BI Connectors.</t>
         </is>
       </c>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -8129,6 +9293,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=MCP for AI Agents.</t>
         </is>
       </c>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -8149,6 +9316,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Prompt-to-SQL Agent.</t>
         </is>
       </c>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -8169,6 +9339,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Dashboard-from-Prompt.</t>
         </is>
       </c>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -8189,6 +9362,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Scheduled Queries.</t>
         </is>
       </c>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -8209,6 +9385,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Alerts from Query Results.</t>
         </is>
       </c>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -8229,6 +9408,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Data Lineage.</t>
         </is>
       </c>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -8249,6 +9431,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.whales_institutional_layer.build_exchange_health_80; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -8269,6 +9454,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=White-Label Embedded Analytics.</t>
         </is>
       </c>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -8289,6 +9477,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Domain Decision Layer.</t>
         </is>
       </c>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -8309,6 +9500,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=data_sources_registry.registry_summary; production=bd_platform.onchain_hub.dexscreener_pairs (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -8329,6 +9523,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Chain TVL Comparison.</t>
         </is>
       </c>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -8349,6 +9546,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Directory.</t>
         </is>
       </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -8369,6 +9569,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.news_classifier.coindesk_feed; production=cap646.fallbacks.resolve_gas_usd (capability_keyword).</t>
         </is>
       </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -8389,6 +9592,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DEX Volume.</t>
         </is>
       </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -8409,6 +9615,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Perps Volume.</t>
         </is>
       </c>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -8429,6 +9638,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Volume.</t>
         </is>
       </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -8449,6 +9661,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoins Intelligence.</t>
         </is>
       </c>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -8469,6 +9684,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Bridges Intelligence.</t>
         </is>
       </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -8489,6 +9707,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Yields Screener.</t>
         </is>
       </c>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -8509,6 +9730,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Yield History.</t>
         </is>
       </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -8529,6 +9753,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Borrowing Rates.</t>
         </is>
       </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -8549,6 +9776,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquid Staking Intelligence.</t>
         </is>
       </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -8569,6 +9799,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=RWA Intelligence.</t>
         </is>
       </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -8589,6 +9822,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Raises / Funding Rounds.</t>
         </is>
       </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -8609,6 +9845,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Investor Profiles.</t>
         </is>
       </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -8629,6 +9868,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.quicktake_feed.quicktake_feed_status_409; production=bd_platform.token_unlocks.unlock_calendar (capability_keyword).</t>
         </is>
       </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -8649,6 +9891,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Treasury Intelligence.</t>
         </is>
       </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -8669,6 +9914,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Airdrop / Incentive Intelligence.</t>
         </is>
       </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -8689,6 +9937,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Capital Formation Radar.</t>
         </is>
       </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -8709,6 +9960,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DeFi Opportunity Screener.</t>
         </is>
       </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -8729,6 +9983,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DeFi Risk Passport.</t>
         </is>
       </c>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -8749,6 +10006,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Aggregation Layer.</t>
         </is>
       </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -8769,6 +10029,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-DeFi Decision Intelligence.</t>
         </is>
       </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -8789,6 +10052,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Chain Fundamentals.</t>
         </is>
       </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -8809,6 +10075,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Fundamentals.</t>
         </is>
       </c>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -8829,6 +10098,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Intelligence.</t>
         </is>
       </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -8849,6 +10121,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Activity Breakdown.</t>
         </is>
       </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -8869,6 +10144,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Developer Activity.</t>
         </is>
       </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -8889,6 +10167,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Sector/Ecosystem Comparables.</t>
         </is>
       </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -8909,6 +10190,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Equities + Crypto Research.</t>
         </is>
       </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -8929,6 +10213,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Consensus Estimates.</t>
         </is>
       </c>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -8949,6 +10236,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI Analyst.</t>
         </is>
       </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -8969,6 +10259,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Thesis Research Workspace.</t>
         </is>
       </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -8989,6 +10282,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Comparable Company / Protocol Analysis.</t>
         </is>
       </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -9009,6 +10305,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Excel / Sheets Integration.</t>
         </is>
       </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -9029,6 +10328,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Data Platform.</t>
         </is>
       </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -9049,6 +10351,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Research Templates.</t>
         </is>
       </c>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -9069,6 +10374,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Dashboards.</t>
         </is>
       </c>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -9089,6 +10397,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Payment Intelligence.</t>
         </is>
       </c>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -9109,6 +10420,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=On-Chain Usage Intelligence.</t>
         </is>
       </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -9129,6 +10443,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Revenue / Fees / Economic Activity.</t>
         </is>
       </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -9149,6 +10466,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Research Copilot.</t>
         </is>
       </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -9169,6 +10489,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Investment Thesis Scoring.</t>
         </is>
       </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -9189,6 +10512,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.correlation_mindshare.compute_mindshare_correlation_288; production=bd_platform.onchain_hub.defillama_raises (capability_keyword).</t>
         </is>
       </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -9209,6 +10535,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Lending Market Risk.</t>
         </is>
       </c>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -9229,6 +10558,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Collateral Risk.</t>
         </is>
       </c>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -9249,6 +10581,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Risk.</t>
         </is>
       </c>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -9269,6 +10604,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.intelligence_analysis_layer.stat_arb_insight_155; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -9289,6 +10627,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidity Risk.</t>
         </is>
       </c>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -9309,6 +10650,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Exploit Intelligence.</t>
         </is>
       </c>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -9329,6 +10673,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Risk Intelligence.</t>
         </is>
       </c>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -9349,6 +10696,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DeFi Strategy Risk.</t>
         </is>
       </c>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -9369,6 +10719,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Real-Time Risk Alerts.</t>
         </is>
       </c>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -9389,6 +10742,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DAO Treasury Risk.</t>
         </is>
       </c>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -9409,6 +10765,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional Risk API.</t>
         </is>
       </c>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -9429,6 +10788,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Curated On-Chain Dashboards.</t>
         </is>
       </c>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -9449,6 +10811,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Narrative-Driven Research.</t>
         </is>
       </c>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -9469,6 +10834,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Dominance.</t>
         </is>
       </c>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -9489,6 +10857,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Aave Multi-Chain Analytics.</t>
         </is>
       </c>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -9509,6 +10880,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Risk Curation.</t>
         </is>
       </c>
+      <c r="E454" t="inlineStr"/>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -9529,6 +10903,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Capital Protection Controls.</t>
         </is>
       </c>
+      <c r="E455" t="inlineStr"/>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -9549,6 +10926,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stress Testing.</t>
         </is>
       </c>
+      <c r="E456" t="inlineStr"/>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -9569,6 +10949,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Protocol Contagion.</t>
         </is>
       </c>
+      <c r="E457" t="inlineStr"/>
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -9589,6 +10972,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Risk Passport.</t>
         </is>
       </c>
+      <c r="E458" t="inlineStr"/>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -9609,6 +10995,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.whales_institutional_layer.build_methodology_docs_86; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
+      <c r="E459" t="inlineStr"/>
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -9629,6 +11018,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Network Data Pro Metrics.</t>
         </is>
       </c>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -9649,6 +11041,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Atlas Blockchain Search.</t>
         </is>
       </c>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -9669,6 +11064,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Address/Balance Search.</t>
         </is>
       </c>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -9689,6 +11087,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Transaction Search.</t>
         </is>
       </c>
+      <c r="E463" t="inlineStr"/>
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -9709,6 +11110,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Block Search.</t>
         </is>
       </c>
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -9729,6 +11133,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Balance Updates.</t>
         </is>
       </c>
+      <c r="E465" t="inlineStr"/>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -9749,6 +11156,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Network Metrics.</t>
         </is>
       </c>
+      <c r="E466" t="inlineStr"/>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -9769,6 +11179,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Data Feed.</t>
         </is>
       </c>
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -9789,6 +11202,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Data Pro.</t>
         </is>
       </c>
+      <c r="E468" t="inlineStr"/>
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -9809,6 +11225,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Reference Rates.</t>
         </is>
       </c>
+      <c r="E469" t="inlineStr"/>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -9829,6 +11248,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Indexes.</t>
         </is>
       </c>
+      <c r="E470" t="inlineStr"/>
+      <c r="F470" t="inlineStr"/>
+      <c r="G470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -9849,6 +11271,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Realized Metrics.</t>
         </is>
       </c>
+      <c r="E471" t="inlineStr"/>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -9869,6 +11294,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Supply Metrics.</t>
         </is>
       </c>
+      <c r="E472" t="inlineStr"/>
+      <c r="F472" t="inlineStr"/>
+      <c r="G472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -9889,6 +11317,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Mining/Validator Metrics.</t>
         </is>
       </c>
+      <c r="E473" t="inlineStr"/>
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -9909,6 +11340,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Fee Metrics.</t>
         </is>
       </c>
+      <c r="E474" t="inlineStr"/>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -9929,6 +11363,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Activity Metrics.</t>
         </is>
       </c>
+      <c r="E475" t="inlineStr"/>
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -9949,6 +11386,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Metric Workbench.</t>
         </is>
       </c>
+      <c r="E476" t="inlineStr"/>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -9969,6 +11409,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Community Charts/API.</t>
         </is>
       </c>
+      <c r="E477" t="inlineStr"/>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -9989,6 +11432,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market + Network Join.</t>
         </is>
       </c>
+      <c r="E478" t="inlineStr"/>
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -10009,6 +11455,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Data Quality Methodologies.</t>
         </is>
       </c>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -10029,6 +11478,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Research Dataset.</t>
         </is>
       </c>
+      <c r="E480" t="inlineStr"/>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -10049,6 +11501,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional APIs.</t>
         </is>
       </c>
+      <c r="E481" t="inlineStr"/>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -10069,6 +11524,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Network Decision Intelligence.</t>
         </is>
       </c>
+      <c r="E482" t="inlineStr"/>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -10089,6 +11547,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional Trade Data.</t>
         </is>
       </c>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -10109,6 +11570,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Order Book Data.</t>
         </is>
       </c>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -10129,6 +11593,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=OHLCV Data.</t>
         </is>
       </c>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -10149,6 +11616,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Derivatives Data.</t>
         </is>
       </c>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -10169,6 +11639,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Open Interest Data.</t>
         </is>
       </c>
+      <c r="E487" t="inlineStr"/>
+      <c r="F487" t="inlineStr"/>
+      <c r="G487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -10189,6 +11662,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Funding Rate Data.</t>
         </is>
       </c>
+      <c r="E488" t="inlineStr"/>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -10209,6 +11685,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Index Data.</t>
         </is>
       </c>
+      <c r="E489" t="inlineStr"/>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -10229,6 +11708,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Reference Pricing.</t>
         </is>
       </c>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -10249,6 +11731,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Exchange Metadata.</t>
         </is>
       </c>
+      <c r="E491" t="inlineStr"/>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -10269,6 +11754,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Asset Metadata.</t>
         </is>
       </c>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -10289,6 +11777,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Market Archive.</t>
         </is>
       </c>
+      <c r="E493" t="inlineStr"/>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -10309,6 +11800,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Real-Time Streams.</t>
         </is>
       </c>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -10329,6 +11823,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Aggregates.</t>
         </is>
       </c>
+      <c r="E495" t="inlineStr"/>
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -10349,6 +11846,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidity Analytics.</t>
         </is>
       </c>
+      <c r="E496" t="inlineStr"/>
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -10369,6 +11869,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Volatility Analytics.</t>
         </is>
       </c>
+      <c r="E497" t="inlineStr"/>
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -10389,6 +11892,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Cap / Supply.</t>
         </is>
       </c>
+      <c r="E498" t="inlineStr"/>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -10409,6 +11915,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=ETF / ETP Data.</t>
         </is>
       </c>
+      <c r="E499" t="inlineStr"/>
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -10429,6 +11938,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Coverage Registry.</t>
         </is>
       </c>
+      <c r="E500" t="inlineStr"/>
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -10449,6 +11961,9 @@
           <t>مبني جزئيًا — PRODUCTION-ALIGNED — Option A; PRODUCTION-ALIGNED: explicit_option_a binding verified live via cap646.runtime.execute_capability; backend=cap646.data_spine.normalization_report; surface=data_quality_normalization; proof=OPTION_A_PRODUCTION_PROOF.json.</t>
         </is>
       </c>
+      <c r="E501" t="inlineStr"/>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -10469,6 +11984,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional Delivery.</t>
         </is>
       </c>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -10489,6 +12007,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Benchmark Administration Metadata.</t>
         </is>
       </c>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -10509,6 +12030,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Data Intelligence.</t>
         </is>
       </c>
+      <c r="E504" t="inlineStr"/>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -10529,6 +12053,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Unified Exchange Connector Layer.</t>
         </is>
       </c>
+      <c r="E505" t="inlineStr"/>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -10549,6 +12076,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Tick Trade Data.</t>
         </is>
       </c>
+      <c r="E506" t="inlineStr"/>
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -10569,6 +12099,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Quote Data.</t>
         </is>
       </c>
+      <c r="E507" t="inlineStr"/>
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -10589,6 +12122,9 @@
           <t>مبني جزئيًا — PRODUCTION-ALIGNED — Option A; PRODUCTION-ALIGNED: explicit_option_a binding verified live via cap646.runtime.execute_capability; backend=cap646.fallbacks.resolve_ohlcv_closes; surface=ohlcv; proof=OPTION_A_PRODUCTION_PROOF.json.</t>
         </is>
       </c>
+      <c r="E508" t="inlineStr"/>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -10609,6 +12145,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=L1 Order Book.</t>
         </is>
       </c>
+      <c r="E509" t="inlineStr"/>
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -10629,6 +12168,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=L2 Order Book.</t>
         </is>
       </c>
+      <c r="E510" t="inlineStr"/>
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -10649,6 +12191,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=L3 Order Book.</t>
         </is>
       </c>
+      <c r="E511" t="inlineStr"/>
+      <c r="F511" t="inlineStr"/>
+      <c r="G511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -10669,6 +12214,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Market Data.</t>
         </is>
       </c>
+      <c r="E512" t="inlineStr"/>
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -10689,6 +12237,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Funding / OI / Liquidation Metrics.</t>
         </is>
       </c>
+      <c r="E513" t="inlineStr"/>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -10709,6 +12260,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Asset &amp; Symbol Metadata.</t>
         </is>
       </c>
+      <c r="E514" t="inlineStr"/>
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -10729,6 +12283,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Flat Files.</t>
         </is>
       </c>
+      <c r="E515" t="inlineStr"/>
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -10749,6 +12306,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=REST API.</t>
         </is>
       </c>
+      <c r="E516" t="inlineStr"/>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -10769,6 +12329,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=WebSocket Streaming.</t>
         </is>
       </c>
+      <c r="E517" t="inlineStr"/>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -10789,6 +12352,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=comparison_engine.run_comparison_engine; production=data_provenance_score.compute_data_provenance_score (track_default).</t>
         </is>
       </c>
+      <c r="E518" t="inlineStr"/>
+      <c r="F518" t="inlineStr"/>
+      <c r="G518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -10809,6 +12375,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=MCP for AI.</t>
         </is>
       </c>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -10829,6 +12398,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Exchange Rates / VWAP.</t>
         </is>
       </c>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -10849,6 +12421,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Indexes.</t>
         </is>
       </c>
+      <c r="E521" t="inlineStr"/>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -10869,6 +12444,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Volatility Index.</t>
         </is>
       </c>
+      <c r="E522" t="inlineStr"/>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -10889,6 +12467,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=EMS Integration Boundary.</t>
         </is>
       </c>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -10909,6 +12490,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Data Health / SLA Monitoring.</t>
         </is>
       </c>
+      <c r="E524" t="inlineStr"/>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -10929,6 +12513,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Symbol Mapping Engine.</t>
         </is>
       </c>
+      <c r="E525" t="inlineStr"/>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -10949,6 +12536,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.run_backtest_74; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E526" t="inlineStr"/>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -10969,6 +12559,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI Market Data Grounding Layer.</t>
         </is>
       </c>
+      <c r="E527" t="inlineStr"/>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -10989,6 +12582,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Heatmap.</t>
         </is>
       </c>
+      <c r="E528" t="inlineStr"/>
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -11009,6 +12605,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_rankings.market_rankings; production=bd_platform.liquidation_radar.liquidation_radar (capability_keyword).</t>
         </is>
       </c>
+      <c r="E529" t="inlineStr"/>
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -11029,6 +12628,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Cascade Model.</t>
         </is>
       </c>
+      <c r="E530" t="inlineStr"/>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -11049,6 +12651,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Global Liquidation Metrics.</t>
         </is>
       </c>
+      <c r="E531" t="inlineStr"/>
+      <c r="F531" t="inlineStr"/>
+      <c r="G531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -11069,6 +12674,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Open Interest.</t>
         </is>
       </c>
+      <c r="E532" t="inlineStr"/>
+      <c r="F532" t="inlineStr"/>
+      <c r="G532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -11089,6 +12697,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Funding Rates.</t>
         </is>
       </c>
+      <c r="E533" t="inlineStr"/>
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -11109,6 +12720,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Order Flow Intelligence.</t>
         </is>
       </c>
+      <c r="E534" t="inlineStr"/>
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -11129,6 +12743,9 @@
           <t>مبني جزئيًا — PRODUCTION-ALIGNED — Option A; PRODUCTION-ALIGNED: explicit_option_a binding verified live via cap646.runtime.execute_capability; backend=cap646.data_spine.bucketed_cvd_report; surface=bucketed_cvd; proof=OPTION_A_PRODUCTION_PROOF.json.</t>
         </is>
       </c>
+      <c r="E535" t="inlineStr"/>
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -11149,6 +12766,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Whale vs Retail Flow.</t>
         </is>
       </c>
+      <c r="E536" t="inlineStr"/>
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -11169,6 +12789,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Slippage Intelligence.</t>
         </is>
       </c>
+      <c r="E537" t="inlineStr"/>
+      <c r="F537" t="inlineStr"/>
+      <c r="G537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -11189,6 +12812,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Global Order Book Metrics.</t>
         </is>
       </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr"/>
+      <c r="G538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -11209,6 +12835,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Order Book Imbalance.</t>
         </is>
       </c>
+      <c r="E539" t="inlineStr"/>
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -11229,6 +12858,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidity Zones.</t>
         </is>
       </c>
+      <c r="E540" t="inlineStr"/>
+      <c r="F540" t="inlineStr"/>
+      <c r="G540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -11249,6 +12881,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Bot Activity Detection.</t>
         </is>
       </c>
+      <c r="E541" t="inlineStr"/>
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -11269,6 +12904,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Positioning.</t>
         </is>
       </c>
+      <c r="E542" t="inlineStr"/>
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -11289,6 +12927,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Pressure Score.</t>
         </is>
       </c>
+      <c r="E543" t="inlineStr"/>
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -11309,6 +12950,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Orderflow Anomaly Detection.</t>
         </is>
       </c>
+      <c r="E544" t="inlineStr"/>
+      <c r="F544" t="inlineStr"/>
+      <c r="G544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -11329,6 +12973,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Indicator Platform.</t>
         </is>
       </c>
+      <c r="E545" t="inlineStr"/>
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -11349,6 +12996,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Trader Cohort Intelligence.</t>
         </is>
       </c>
+      <c r="E546" t="inlineStr"/>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -11369,6 +13019,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Derivatives Decision Intelligence.</t>
         </is>
       </c>
+      <c r="E547" t="inlineStr"/>
+      <c r="F547" t="inlineStr"/>
+      <c r="G547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -11389,6 +13042,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=High-Resolution Multi-Pane Charts.</t>
         </is>
       </c>
+      <c r="E548" t="inlineStr"/>
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -11409,6 +13065,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Derivatives Dashboard.</t>
         </is>
       </c>
+      <c r="E549" t="inlineStr"/>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -11429,6 +13088,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Funding Rate Intelligence.</t>
         </is>
       </c>
+      <c r="E550" t="inlineStr"/>
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -11449,6 +13111,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Open Interest Intelligence.</t>
         </is>
       </c>
+      <c r="E551" t="inlineStr"/>
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -11469,6 +13134,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Intelligence.</t>
         </is>
       </c>
+      <c r="E552" t="inlineStr"/>
+      <c r="F552" t="inlineStr"/>
+      <c r="G552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -11489,6 +13157,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Futures Volume.</t>
         </is>
       </c>
+      <c r="E553" t="inlineStr"/>
+      <c r="F553" t="inlineStr"/>
+      <c r="G553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -11509,6 +13180,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Basis Intelligence.</t>
         </is>
       </c>
+      <c r="E554" t="inlineStr"/>
+      <c r="F554" t="inlineStr"/>
+      <c r="G554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -11529,6 +13203,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Spot Market Data.</t>
         </is>
       </c>
+      <c r="E555" t="inlineStr"/>
+      <c r="F555" t="inlineStr"/>
+      <c r="G555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -11549,6 +13226,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Analytics.</t>
         </is>
       </c>
+      <c r="E556" t="inlineStr"/>
+      <c r="F556" t="inlineStr"/>
+      <c r="G556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -11569,6 +13249,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options IV Surface.</t>
         </is>
       </c>
+      <c r="E557" t="inlineStr"/>
+      <c r="F557" t="inlineStr"/>
+      <c r="G557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -11589,6 +13272,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Skew.</t>
         </is>
       </c>
+      <c r="E558" t="inlineStr"/>
+      <c r="F558" t="inlineStr"/>
+      <c r="G558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -11609,6 +13295,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Term Structure.</t>
         </is>
       </c>
+      <c r="E559" t="inlineStr"/>
+      <c r="F559" t="inlineStr"/>
+      <c r="G559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -11629,6 +13318,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=TradFi Context.</t>
         </is>
       </c>
+      <c r="E560" t="inlineStr"/>
+      <c r="F560" t="inlineStr"/>
+      <c r="G560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -11649,6 +13341,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Multi-Indicator Workspace.</t>
         </is>
       </c>
+      <c r="E561" t="inlineStr"/>
+      <c r="F561" t="inlineStr"/>
+      <c r="G561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -11669,6 +13364,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Real-Time Prices.</t>
         </is>
       </c>
+      <c r="E562" t="inlineStr"/>
+      <c r="F562" t="inlineStr"/>
+      <c r="G562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -11689,6 +13387,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Data.</t>
         </is>
       </c>
+      <c r="E563" t="inlineStr"/>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -11709,6 +13410,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Data Access.</t>
         </is>
       </c>
+      <c r="E564" t="inlineStr"/>
+      <c r="F564" t="inlineStr"/>
+      <c r="G564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -11729,6 +13433,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=News Context.</t>
         </is>
       </c>
+      <c r="E565" t="inlineStr"/>
+      <c r="F565" t="inlineStr"/>
+      <c r="G565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -11749,6 +13456,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Asset Correlation.</t>
         </is>
       </c>
+      <c r="E566" t="inlineStr"/>
+      <c r="F566" t="inlineStr"/>
+      <c r="G566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -11769,6 +13479,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Derivatives Regime Engine.</t>
         </is>
       </c>
+      <c r="E567" t="inlineStr"/>
+      <c r="F567" t="inlineStr"/>
+      <c r="G567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -11789,6 +13502,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Decision Intelligence.</t>
         </is>
       </c>
+      <c r="E568" t="inlineStr"/>
+      <c r="F568" t="inlineStr"/>
+      <c r="G568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -11809,6 +13525,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Security_First_Architecture.</t>
         </is>
       </c>
+      <c r="E569" t="inlineStr"/>
+      <c r="F569" t="inlineStr"/>
+      <c r="G569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -11829,6 +13548,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API_Security_Encryption.</t>
         </is>
       </c>
+      <c r="E570" t="inlineStr"/>
+      <c r="F570" t="inlineStr"/>
+      <c r="G570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -11849,6 +13571,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=High_Availability_Architecture.</t>
         </is>
       </c>
+      <c r="E571" t="inlineStr"/>
+      <c r="F571" t="inlineStr"/>
+      <c r="G571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -11869,6 +13594,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Infrastructure_Uptime_Shield.</t>
         </is>
       </c>
+      <c r="E572" t="inlineStr"/>
+      <c r="F572" t="inlineStr"/>
+      <c r="G572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -11889,6 +13617,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional_Data_Architecture.</t>
         </is>
       </c>
+      <c r="E573" t="inlineStr"/>
+      <c r="F573" t="inlineStr"/>
+      <c r="G573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -11909,6 +13640,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Flexible_Connector_Microservice.</t>
         </is>
       </c>
+      <c r="E574" t="inlineStr"/>
+      <c r="F574" t="inlineStr"/>
+      <c r="G574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -11929,6 +13663,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional_API_Gateway.</t>
         </is>
       </c>
+      <c r="E575" t="inlineStr"/>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -11949,6 +13686,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API_Data_Pipe.</t>
         </is>
       </c>
+      <c r="E576" t="inlineStr"/>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -11969,6 +13709,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Developer_SDK.</t>
         </is>
       </c>
+      <c r="E577" t="inlineStr"/>
+      <c r="F577" t="inlineStr"/>
+      <c r="G577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -11989,6 +13732,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Pro_Developer_Sandbox.</t>
         </is>
       </c>
+      <c r="E578" t="inlineStr"/>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -12009,6 +13755,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.execution_rejected_layer.whale_behavior_analysis_216; production=bd_platform.portfolio_rebalancer.portfolio_snapshot (capability_keyword).</t>
         </is>
       </c>
+      <c r="E579" t="inlineStr"/>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -12029,6 +13778,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Global_Asset_Tracker.</t>
         </is>
       </c>
+      <c r="E580" t="inlineStr"/>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -12049,6 +13801,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Multi_Account_Sync.</t>
         </is>
       </c>
+      <c r="E581" t="inlineStr"/>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -12069,6 +13824,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=On_Chain_Balance_Monitor.</t>
         </is>
       </c>
+      <c r="E582" t="inlineStr"/>
+      <c r="F582" t="inlineStr"/>
+      <c r="G582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -12089,6 +13847,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Profitability_Analyzer.</t>
         </is>
       </c>
+      <c r="E583" t="inlineStr"/>
+      <c r="F583" t="inlineStr"/>
+      <c r="G583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -12109,6 +13870,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Margin_Risk_Calculator.</t>
         </is>
       </c>
+      <c r="E584" t="inlineStr"/>
+      <c r="F584" t="inlineStr"/>
+      <c r="G584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -12129,6 +13893,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.news_classifier.coindesk_feed; production=risk_manager.risk_status (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E585" t="inlineStr"/>
+      <c r="F585" t="inlineStr"/>
+      <c r="G585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -12149,6 +13916,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Volatility_Scoring_System.</t>
         </is>
       </c>
+      <c r="E586" t="inlineStr"/>
+      <c r="F586" t="inlineStr"/>
+      <c r="G586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -12169,6 +13939,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Volatility_Surface_Analyzer.</t>
         </is>
       </c>
+      <c r="E587" t="inlineStr"/>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -12189,6 +13962,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Delta_Neutral_Calculator.</t>
         </is>
       </c>
+      <c r="E588" t="inlineStr"/>
+      <c r="F588" t="inlineStr"/>
+      <c r="G588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -12209,6 +13985,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=High_Precision_Backtesting.</t>
         </is>
       </c>
+      <c r="E589" t="inlineStr"/>
+      <c r="F589" t="inlineStr"/>
+      <c r="G589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -12229,6 +14008,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Strategy_Vetting_Algorithm.</t>
         </is>
       </c>
+      <c r="E590" t="inlineStr"/>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -12249,6 +14031,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI_Quant_Rating_Engine.</t>
         </is>
       </c>
+      <c r="E591" t="inlineStr"/>
+      <c r="F591" t="inlineStr"/>
+      <c r="G591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -12269,6 +14054,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Sentiment_Analysis_Engine.</t>
         </is>
       </c>
+      <c r="E592" t="inlineStr"/>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -12289,6 +14077,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Social_Sentiment_Engine.</t>
         </is>
       </c>
+      <c r="E593" t="inlineStr"/>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -12309,6 +14100,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Social_Hype_Analyzer.</t>
         </is>
       </c>
+      <c r="E594" t="inlineStr"/>
+      <c r="F594" t="inlineStr"/>
+      <c r="G594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -12329,6 +14123,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Narrative_Alert_System.</t>
         </is>
       </c>
+      <c r="E595" t="inlineStr"/>
+      <c r="F595" t="inlineStr"/>
+      <c r="G595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -12349,6 +14146,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI_Digest_Generator.</t>
         </is>
       </c>
+      <c r="E596" t="inlineStr"/>
+      <c r="F596" t="inlineStr"/>
+      <c r="G596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -12369,6 +14169,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI_Agent_Consultant.</t>
         </is>
       </c>
+      <c r="E597" t="inlineStr"/>
+      <c r="F597" t="inlineStr"/>
+      <c r="G597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -12389,6 +14192,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Natural_Language_Interpreter.</t>
         </is>
       </c>
+      <c r="E598" t="inlineStr"/>
+      <c r="F598" t="inlineStr"/>
+      <c r="G598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -12409,6 +14215,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Wallet_Shadowing.</t>
         </is>
       </c>
+      <c r="E599" t="inlineStr"/>
+      <c r="F599" t="inlineStr"/>
+      <c r="G599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -12429,6 +14238,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Entity_Tagging_System.</t>
         </is>
       </c>
+      <c r="E600" t="inlineStr"/>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -12449,6 +14261,9 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Whale_Clustering_Engine.</t>
         </is>
       </c>
+      <c r="E601" t="inlineStr"/>
+      <c r="F601" t="inlineStr"/>
+      <c r="G601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -12469,6 +14284,9 @@
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
+      <c r="E602" t="inlineStr"/>
+      <c r="F602" t="inlineStr"/>
+      <c r="G602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -12489,6 +14307,9 @@
           <t>مبني وشغال فعليًا — acquirer_evidence_pack.build_acquirer_evidence_pack</t>
         </is>
       </c>
+      <c r="E603" t="inlineStr"/>
+      <c r="F603" t="inlineStr"/>
+      <c r="G603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -12509,6 +14330,9 @@
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.continuous_learning_status_186 via platform_api/intelligence/continuous-learning-status</t>
         </is>
       </c>
+      <c r="E604" t="inlineStr"/>
+      <c r="F604" t="inlineStr"/>
+      <c r="G604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -12529,6 +14353,9 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
+      <c r="E605" t="inlineStr"/>
+      <c r="F605" t="inlineStr"/>
+      <c r="G605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -12549,6 +14376,9 @@
           <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
       </c>
+      <c r="E606" t="inlineStr"/>
+      <c r="F606" t="inlineStr"/>
+      <c r="G606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -12569,6 +14399,9 @@
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.withdrawal_suspension_alert_191</t>
         </is>
       </c>
+      <c r="E607" t="inlineStr"/>
+      <c r="F607" t="inlineStr"/>
+      <c r="G607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -12589,6 +14422,9 @@
           <t>مبني وشغال فعليًا — bd_platform/infra_intelligence_layer.py</t>
         </is>
       </c>
+      <c r="E608" t="inlineStr"/>
+      <c r="F608" t="inlineStr"/>
+      <c r="G608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -12609,6 +14445,9 @@
           <t>مبني وشغال فعليًا — bd_platform/derivatives_ta_research_layer.py</t>
         </is>
       </c>
+      <c r="E609" t="inlineStr"/>
+      <c r="F609" t="inlineStr"/>
+      <c r="G609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -12629,6 +14468,9 @@
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
+      <c r="E610" t="inlineStr"/>
+      <c r="F610" t="inlineStr"/>
+      <c r="G610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -12649,6 +14491,9 @@
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
+      <c r="E611" t="inlineStr"/>
+      <c r="F611" t="inlineStr"/>
+      <c r="G611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -12669,6 +14514,9 @@
           <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_glassnode_metrics_205 via platform_api/oracle/on-chain/sources/glassnode</t>
         </is>
       </c>
+      <c r="E612" t="inlineStr"/>
+      <c r="F612" t="inlineStr"/>
+      <c r="G612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -12689,6 +14537,9 @@
           <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
+      <c r="E613" t="inlineStr"/>
+      <c r="F613" t="inlineStr"/>
+      <c r="G613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -12709,6 +14560,9 @@
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
+      <c r="E614" t="inlineStr"/>
+      <c r="F614" t="inlineStr"/>
+      <c r="G614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -12729,6 +14583,9 @@
           <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
         </is>
       </c>
+      <c r="E615" t="inlineStr"/>
+      <c r="F615" t="inlineStr"/>
+      <c r="G615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -12749,6 +14606,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E616" t="inlineStr"/>
+      <c r="F616" t="inlineStr"/>
+      <c r="G616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -12769,6 +14629,9 @@
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
+      <c r="E617" t="inlineStr"/>
+      <c r="F617" t="inlineStr"/>
+      <c r="G617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -12789,6 +14652,9 @@
           <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132</t>
         </is>
       </c>
+      <c r="E618" t="inlineStr"/>
+      <c r="F618" t="inlineStr"/>
+      <c r="G618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -12809,6 +14675,9 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
+      <c r="E619" t="inlineStr"/>
+      <c r="F619" t="inlineStr"/>
+      <c r="G619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -12829,6 +14698,9 @@
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
+      <c r="E620" t="inlineStr"/>
+      <c r="F620" t="inlineStr"/>
+      <c r="G620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -12849,6 +14721,9 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
+      <c r="E621" t="inlineStr"/>
+      <c r="F621" t="inlineStr"/>
+      <c r="G621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -12869,6 +14744,9 @@
           <t>مبني وشغال فعليًا — bd_platform/intelligence_market_extensions_layer.py</t>
         </is>
       </c>
+      <c r="E622" t="inlineStr"/>
+      <c r="F622" t="inlineStr"/>
+      <c r="G622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -12889,6 +14767,9 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
+      <c r="E623" t="inlineStr"/>
+      <c r="F623" t="inlineStr"/>
+      <c r="G623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -12909,6 +14790,9 @@
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
+      <c r="E624" t="inlineStr"/>
+      <c r="F624" t="inlineStr"/>
+      <c r="G624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -12929,6 +14813,9 @@
           <t>مبني وشغال فعليًا — bd_platform.free_tier_capabilities.free_tier_live_ready</t>
         </is>
       </c>
+      <c r="E625" t="inlineStr"/>
+      <c r="F625" t="inlineStr"/>
+      <c r="G625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -12949,6 +14836,9 @@
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
+      <c r="E626" t="inlineStr"/>
+      <c r="F626" t="inlineStr"/>
+      <c r="G626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -12969,6 +14859,9 @@
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
+      <c r="E627" t="inlineStr"/>
+      <c r="F627" t="inlineStr"/>
+      <c r="G627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -12989,6 +14882,9 @@
           <t>مبني وشغال فعليًا — comparison_engine.py:run_comparison_engine + route /api/platform/intelligence/comparison-engine</t>
         </is>
       </c>
+      <c r="E628" t="inlineStr"/>
+      <c r="F628" t="inlineStr"/>
+      <c r="G628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -13009,6 +14905,9 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233 via platform_api/radar/heatmap</t>
         </is>
       </c>
+      <c r="E629" t="inlineStr"/>
+      <c r="F629" t="inlineStr"/>
+      <c r="G629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -13029,6 +14928,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=regulatory_compliance_guard.compliant_oracle_sentence; production=instant_alert_engine.engine_stats (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E630" t="inlineStr"/>
+      <c r="F630" t="inlineStr"/>
+      <c r="G630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -13049,6 +14951,9 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.scan_market_opportunities_238</t>
         </is>
       </c>
+      <c r="E631" t="inlineStr"/>
+      <c r="F631" t="inlineStr"/>
+      <c r="G631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -13069,6 +14974,9 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
+      <c r="E632" t="inlineStr"/>
+      <c r="F632" t="inlineStr"/>
+      <c r="G632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -13089,6 +14997,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E633" t="inlineStr"/>
+      <c r="F633" t="inlineStr"/>
+      <c r="G633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -13109,6 +15020,9 @@
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244 via platform_api/radar/news/cointelegraph</t>
         </is>
       </c>
+      <c r="E634" t="inlineStr"/>
+      <c r="F634" t="inlineStr"/>
+      <c r="G634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -13129,6 +15043,9 @@
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.list_etherscan_watchlist_246 via platform_api/oracle/on-chain/watch</t>
         </is>
       </c>
+      <c r="E635" t="inlineStr"/>
+      <c r="F635" t="inlineStr"/>
+      <c r="G635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -13149,6 +15066,9 @@
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.trad_simulator_635 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
       </c>
+      <c r="E636" t="inlineStr"/>
+      <c r="F636" t="inlineStr"/>
+      <c r="G636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -13169,6 +15089,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E637" t="inlineStr"/>
+      <c r="F637" t="inlineStr"/>
+      <c r="G637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -13189,6 +15112,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.build_kill_rate_widget_253; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
+      <c r="E638" t="inlineStr"/>
+      <c r="F638" t="inlineStr"/>
+      <c r="G638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -13209,6 +15135,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.build_contradiction_replay_254; production=oracle_track_record.public_track_record (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E639" t="inlineStr"/>
+      <c r="F639" t="inlineStr"/>
+      <c r="G639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -13229,6 +15158,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.committee_one_pager_status_255; production=net_edge_truth.compute_net_edge_truth (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E640" t="inlineStr"/>
+      <c r="F640" t="inlineStr"/>
+      <c r="G640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -13249,6 +15181,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.compute_half_life_clock_256; production=oracle_track_record.public_track_record (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E641" t="inlineStr"/>
+      <c r="F641" t="inlineStr"/>
+      <c r="G641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -13269,6 +15204,9 @@
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.proof_arena_lite_641 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
       </c>
+      <c r="E642" t="inlineStr"/>
+      <c r="F642" t="inlineStr"/>
+      <c r="G642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -13289,6 +15227,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.since_you_left_top3_258; production=data_provenance_score.compute_data_provenance_score (capability_keyword).</t>
         </is>
       </c>
+      <c r="E643" t="inlineStr"/>
+      <c r="F643" t="inlineStr"/>
+      <c r="G643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -13309,6 +15250,9 @@
           <t>مبني وشغال فعليًا — kill_rate_board.py + anti_hype_mode.py + proof_arena.py</t>
         </is>
       </c>
+      <c r="E644" t="inlineStr"/>
+      <c r="F644" t="inlineStr"/>
+      <c r="G644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -13329,6 +15273,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.corpus_passport_status_260; production=scale_readiness.scale_readiness_report (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E645" t="inlineStr"/>
+      <c r="F645" t="inlineStr"/>
+      <c r="G645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -13349,6 +15296,9 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.data_sources_layer.compute_opportunity_score_150; production=security_posture.security_posture_report (gap_matrix_component).</t>
         </is>
       </c>
+      <c r="E646" t="inlineStr"/>
+      <c r="F646" t="inlineStr"/>
+      <c r="G646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -13369,6 +15319,9 @@
           <t>مبني وشغال فعليًا — bd_platform.auto_keys.parse_keys_file</t>
         </is>
       </c>
+      <c r="E647" t="inlineStr"/>
+      <c r="F647" t="inlineStr"/>
+      <c r="G647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -13389,6 +15342,9 @@
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
+      <c r="E648" t="inlineStr"/>
+      <c r="F648" t="inlineStr"/>
+      <c r="G648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -13409,6 +15365,9 @@
           <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
+      <c r="E649" t="inlineStr"/>
+      <c r="F649" t="inlineStr"/>
+      <c r="G649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -13429,6 +15388,9 @@
           <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
+      <c r="E650" t="inlineStr"/>
+      <c r="F650" t="inlineStr"/>
+      <c r="G650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -13449,6 +15411,9 @@
           <t>مبني وشغال فعليًا — audit_registry.py + security_trust_data_layer audit_log_id_242</t>
         </is>
       </c>
+      <c r="E651" t="inlineStr"/>
+      <c r="F651" t="inlineStr"/>
+      <c r="G651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -13469,6 +15434,9 @@
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
+      <c r="E652" t="inlineStr"/>
+      <c r="F652" t="inlineStr"/>
+      <c r="G652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -13489,6 +15457,9 @@
           <t>مبني وشغال فعليًا — persona_clarity.build_persona_clarity</t>
         </is>
       </c>
+      <c r="E653" t="inlineStr"/>
+      <c r="F653" t="inlineStr"/>
+      <c r="G653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -13509,6 +15480,9 @@
           <t>مبني وشغال فعليًا — dashboard.py</t>
         </is>
       </c>
+      <c r="E654" t="inlineStr"/>
+      <c r="F654" t="inlineStr"/>
+      <c r="G654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -13529,6 +15503,9 @@
           <t>مبني وشغال فعليًا — gas_oracle.py + cap646/fallbacks resolve_gas_usd</t>
         </is>
       </c>
+      <c r="E655" t="inlineStr"/>
+      <c r="F655" t="inlineStr"/>
+      <c r="G655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -13549,6 +15526,9 @@
           <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
       </c>
+      <c r="E656" t="inlineStr"/>
+      <c r="F656" t="inlineStr"/>
+      <c r="G656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -13569,6 +15549,9 @@
           <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
       </c>
+      <c r="E657" t="inlineStr"/>
+      <c r="F657" t="inlineStr"/>
+      <c r="G657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -13589,6 +15572,9 @@
           <t>مبني وشغال فعليًا — hot_storage.py — تحقق عميق (كان: إشارات فقط)</t>
         </is>
       </c>
+      <c r="E658" t="inlineStr"/>
+      <c r="F658" t="inlineStr"/>
+      <c r="G658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -13609,6 +15595,9 @@
           <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
+      <c r="E659" t="inlineStr"/>
+      <c r="F659" t="inlineStr"/>
+      <c r="G659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="n">
@@ -13629,6 +15618,9 @@
           <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
+      <c r="E660" t="inlineStr"/>
+      <c r="F660" t="inlineStr"/>
+      <c r="G660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="n">
@@ -13649,6 +15641,9 @@
           <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
+      <c r="E661" t="inlineStr"/>
+      <c r="F661" t="inlineStr"/>
+      <c r="G661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="n">
@@ -13669,6 +15664,9 @@
           <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 via platform_api/data-engine/streaming/status</t>
         </is>
       </c>
+      <c r="E662" t="inlineStr"/>
+      <c r="F662" t="inlineStr"/>
+      <c r="G662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="n">
@@ -13689,6 +15687,9 @@
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
         </is>
       </c>
+      <c r="E663" t="inlineStr"/>
+      <c r="F663" t="inlineStr"/>
+      <c r="G663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="n">
@@ -13709,6 +15710,9 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
+      <c r="E664" t="inlineStr"/>
+      <c r="F664" t="inlineStr"/>
+      <c r="G664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="n">
@@ -13729,6 +15733,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E665" t="inlineStr"/>
+      <c r="F665" t="inlineStr"/>
+      <c r="G665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -13749,6 +15756,9 @@
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
+      <c r="E666" t="inlineStr"/>
+      <c r="F666" t="inlineStr"/>
+      <c r="G666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="n">
@@ -13769,6 +15779,9 @@
           <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.health_score_from_holdings_67 via platform_api/portfolio/health-score</t>
         </is>
       </c>
+      <c r="E667" t="inlineStr"/>
+      <c r="F667" t="inlineStr"/>
+      <c r="G667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="n">
@@ -13789,6 +15802,9 @@
           <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
+      <c r="E668" t="inlineStr"/>
+      <c r="F668" t="inlineStr"/>
+      <c r="G668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="n">
@@ -13809,6 +15825,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E669" t="inlineStr"/>
+      <c r="F669" t="inlineStr"/>
+      <c r="G669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="n">
@@ -13829,6 +15848,9 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
+      <c r="E670" t="inlineStr"/>
+      <c r="F670" t="inlineStr"/>
+      <c r="G670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="n">
@@ -13849,6 +15871,9 @@
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
+      <c r="E671" t="inlineStr"/>
+      <c r="F671" t="inlineStr"/>
+      <c r="G671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -13869,6 +15894,9 @@
           <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
+      <c r="E672" t="inlineStr"/>
+      <c r="F672" t="inlineStr"/>
+      <c r="G672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="n">
@@ -13889,6 +15917,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E673" t="inlineStr"/>
+      <c r="F673" t="inlineStr"/>
+      <c r="G673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -13909,6 +15940,9 @@
           <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 via platform_api/data-engine/streaming/status</t>
         </is>
       </c>
+      <c r="E674" t="inlineStr"/>
+      <c r="F674" t="inlineStr"/>
+      <c r="G674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="n">
@@ -13929,6 +15963,9 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
+      <c r="E675" t="inlineStr"/>
+      <c r="F675" t="inlineStr"/>
+      <c r="G675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" t="n">
@@ -13949,6 +15986,9 @@
           <t>مبني وشغال فعليًا — oracle_unified.build_full_market_context</t>
         </is>
       </c>
+      <c r="E676" t="inlineStr"/>
+      <c r="F676" t="inlineStr"/>
+      <c r="G676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="n">
@@ -13969,6 +16009,9 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.build_institutional_insight_report_163</t>
         </is>
       </c>
+      <c r="E677" t="inlineStr"/>
+      <c r="F677" t="inlineStr"/>
+      <c r="G677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="n">
@@ -13989,6 +16032,9 @@
           <t>مبني وشغال فعليًا — sentiment_manipulation_guard spoof detection</t>
         </is>
       </c>
+      <c r="E678" t="inlineStr"/>
+      <c r="F678" t="inlineStr"/>
+      <c r="G678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="n">
@@ -14009,6 +16055,9 @@
           <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.run_risk_infrastructure_e2e_164_176 via platform_api/infrastructure/resilience-status</t>
         </is>
       </c>
+      <c r="E679" t="inlineStr"/>
+      <c r="F679" t="inlineStr"/>
+      <c r="G679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="n">
@@ -14029,6 +16078,9 @@
           <t>مبني وشغال فعليًا — sentiment_manipulation_guard spoof detection</t>
         </is>
       </c>
+      <c r="E680" t="inlineStr"/>
+      <c r="F680" t="inlineStr"/>
+      <c r="G680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" t="n">
@@ -14049,6 +16101,9 @@
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
+      <c r="E681" t="inlineStr"/>
+      <c r="F681" t="inlineStr"/>
+      <c r="G681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -14069,6 +16124,9 @@
           <t>مبني وشغال فعليًا — bd_platform/whales_institutional_layer.py</t>
         </is>
       </c>
+      <c r="E682" t="inlineStr"/>
+      <c r="F682" t="inlineStr"/>
+      <c r="G682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="n">
@@ -14089,6 +16147,9 @@
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
+      <c r="E683" t="inlineStr"/>
+      <c r="F683" t="inlineStr"/>
+      <c r="G683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="n">
@@ -14109,6 +16170,9 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
+      <c r="E684" t="inlineStr"/>
+      <c r="F684" t="inlineStr"/>
+      <c r="G684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="n">
@@ -14129,6 +16193,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E685" t="inlineStr"/>
+      <c r="F685" t="inlineStr"/>
+      <c r="G685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="n">
@@ -14149,6 +16216,9 @@
           <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
+      <c r="E686" t="inlineStr"/>
+      <c r="F686" t="inlineStr"/>
+      <c r="G686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="n">
@@ -14169,6 +16239,9 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
+      <c r="E687" t="inlineStr"/>
+      <c r="F687" t="inlineStr"/>
+      <c r="G687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="n">
@@ -14189,6 +16262,9 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
+      <c r="E688" t="inlineStr"/>
+      <c r="F688" t="inlineStr"/>
+      <c r="G688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="n">
@@ -14209,6 +16285,9 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
+      <c r="E689" t="inlineStr"/>
+      <c r="F689" t="inlineStr"/>
+      <c r="G689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="n">
@@ -14229,6 +16308,9 @@
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.list_etherscan_watchlist_246 via platform_api/oracle/on-chain/watch</t>
         </is>
       </c>
+      <c r="E690" t="inlineStr"/>
+      <c r="F690" t="inlineStr"/>
+      <c r="G690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="n">
@@ -14249,6 +16331,9 @@
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
+      <c r="E691" t="inlineStr"/>
+      <c r="F691" t="inlineStr"/>
+      <c r="G691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="n">
@@ -14269,6 +16354,9 @@
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
+      <c r="E692" t="inlineStr"/>
+      <c r="F692" t="inlineStr"/>
+      <c r="G692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="n">
@@ -14289,6 +16377,9 @@
           <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
+      <c r="E693" t="inlineStr"/>
+      <c r="F693" t="inlineStr"/>
+      <c r="G693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="n">
@@ -14309,6 +16400,9 @@
           <t>مبني جزئيًا — EXTERNAL_BLOCKED — Polygon.io API license requires human vendor contract; proxy: bd_platform/oneinch_connector.py</t>
         </is>
       </c>
+      <c r="E694" t="inlineStr"/>
+      <c r="F694" t="inlineStr"/>
+      <c r="G694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="n">
@@ -14329,6 +16423,9 @@
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
+      <c r="E695" t="inlineStr"/>
+      <c r="F695" t="inlineStr"/>
+      <c r="G695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="n">
@@ -14349,6 +16446,9 @@
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
+      <c r="E696" t="inlineStr"/>
+      <c r="F696" t="inlineStr"/>
+      <c r="G696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="n">
@@ -14369,6 +16469,9 @@
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
+      <c r="E697" t="inlineStr"/>
+      <c r="F697" t="inlineStr"/>
+      <c r="G697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="n">
@@ -14389,6 +16492,9 @@
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
+      <c r="E698" t="inlineStr"/>
+      <c r="F698" t="inlineStr"/>
+      <c r="G698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="n">
@@ -14409,6 +16515,9 @@
           <t>مبني وشغال فعليًا — onchain_tracker.build_onchain_context_safe</t>
         </is>
       </c>
+      <c r="E699" t="inlineStr"/>
+      <c r="F699" t="inlineStr"/>
+      <c r="G699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="n">
@@ -14429,6 +16538,9 @@
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
       </c>
+      <c r="E700" t="inlineStr"/>
+      <c r="F700" t="inlineStr"/>
+      <c r="G700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="n">
@@ -14449,6 +16561,9 @@
           <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
       </c>
+      <c r="E701" t="inlineStr"/>
+      <c r="F701" t="inlineStr"/>
+      <c r="G701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="n">
@@ -14469,6 +16584,9 @@
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
       </c>
+      <c r="E702" t="inlineStr"/>
+      <c r="F702" t="inlineStr"/>
+      <c r="G702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="n">
@@ -14489,6 +16607,9 @@
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
+      <c r="E703" t="inlineStr"/>
+      <c r="F703" t="inlineStr"/>
+      <c r="G703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="n">
@@ -14509,6 +16630,9 @@
           <t>مبني وشغال فعليًا — platform_api.py + public_api_docs.py REST surfaces</t>
         </is>
       </c>
+      <c r="E704" t="inlineStr"/>
+      <c r="F704" t="inlineStr"/>
+      <c r="G704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="n">
@@ -14529,6 +16653,9 @@
           <t>مبني جزئيًا — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978 catalog and batch-01 evidence but absent from cap646.backend_registry (binding_for KeyError). Requires cap646 registration or dedicated CAP978 extension verification track — not auditable via /api/cap646/{id} today.</t>
         </is>
       </c>
+      <c r="E705" t="inlineStr"/>
+      <c r="F705" t="inlineStr"/>
+      <c r="G705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="n">
@@ -14549,6 +16676,9 @@
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
+      <c r="E706" t="inlineStr"/>
+      <c r="F706" t="inlineStr"/>
+      <c r="G706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="n">
@@ -14569,6 +16699,9 @@
           <t>مبني وشغال فعليًا — dbt_connector.get_run_evidence</t>
         </is>
       </c>
+      <c r="E707" t="inlineStr"/>
+      <c r="F707" t="inlineStr"/>
+      <c r="G707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="n">
@@ -14589,6 +16722,9 @@
           <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
+      <c r="E708" t="inlineStr"/>
+      <c r="F708" t="inlineStr"/>
+      <c r="G708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="n">
@@ -14609,6 +16745,9 @@
           <t>مبني جزئيًا — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978 catalog and batch-01 evidence but absent from cap646.backend_registry (binding_for KeyError). Requires cap646 registration or dedicated CAP978 extension verification track — not auditable via /api/cap646/{id} today.</t>
         </is>
       </c>
+      <c r="E709" t="inlineStr"/>
+      <c r="F709" t="inlineStr"/>
+      <c r="G709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="n">
@@ -14629,6 +16768,9 @@
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
       </c>
+      <c r="E710" t="inlineStr"/>
+      <c r="F710" t="inlineStr"/>
+      <c r="G710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="n">
@@ -14649,6 +16791,9 @@
           <t>مبني وشغال فعليًا — bd_platform/telegram_agent.py + intelligence_analysis_layer #161</t>
         </is>
       </c>
+      <c r="E711" t="inlineStr"/>
+      <c r="F711" t="inlineStr"/>
+      <c r="G711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="n">
@@ -14669,6 +16814,9 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.analyze_token_dcf_224 via platform_api/intelligence/valuation/dcf-token</t>
         </is>
       </c>
+      <c r="E712" t="inlineStr"/>
+      <c r="F712" t="inlineStr"/>
+      <c r="G712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="n">
@@ -14689,6 +16837,9 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
+      <c r="E713" t="inlineStr"/>
+      <c r="F713" t="inlineStr"/>
+      <c r="G713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="n">
@@ -14709,6 +16860,9 @@
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
+      <c r="E714" t="inlineStr"/>
+      <c r="F714" t="inlineStr"/>
+      <c r="G714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="n">
@@ -14729,6 +16883,9 @@
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
+      <c r="E715" t="inlineStr"/>
+      <c r="F715" t="inlineStr"/>
+      <c r="G715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="n">
@@ -14749,6 +16906,9 @@
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
+      <c r="E716" t="inlineStr"/>
+      <c r="F716" t="inlineStr"/>
+      <c r="G716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="n">
@@ -14769,6 +16929,9 @@
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
+      <c r="E717" t="inlineStr"/>
+      <c r="F717" t="inlineStr"/>
+      <c r="G717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="n">
@@ -14789,6 +16952,9 @@
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
+      <c r="E718" t="inlineStr"/>
+      <c r="F718" t="inlineStr"/>
+      <c r="G718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="n">
@@ -14809,6 +16975,9 @@
           <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
+      <c r="E719" t="inlineStr"/>
+      <c r="F719" t="inlineStr"/>
+      <c r="G719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="n">
@@ -14829,6 +16998,9 @@
           <t>مبني وشغال فعليًا — market_event_library.event_library_stats</t>
         </is>
       </c>
+      <c r="E720" t="inlineStr"/>
+      <c r="F720" t="inlineStr"/>
+      <c r="G720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="n">
@@ -14849,6 +17021,9 @@
           <t>مبني وشغال فعليًا — bd_platform/whale_story.py + whale_tracker.py</t>
         </is>
       </c>
+      <c r="E721" t="inlineStr"/>
+      <c r="F721" t="inlineStr"/>
+      <c r="G721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="n">
@@ -14869,6 +17044,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E722" t="inlineStr"/>
+      <c r="F722" t="inlineStr"/>
+      <c r="G722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="n">
@@ -14889,6 +17067,9 @@
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
+      <c r="E723" t="inlineStr"/>
+      <c r="F723" t="inlineStr"/>
+      <c r="G723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="n">
@@ -14909,6 +17090,9 @@
           <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_blockchain_com_148 via platform_api/oracle/on-chain/sources/blockchain-com</t>
         </is>
       </c>
+      <c r="E724" t="inlineStr"/>
+      <c r="F724" t="inlineStr"/>
+      <c r="G724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="n">
@@ -14929,6 +17113,9 @@
           <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
+      <c r="E725" t="inlineStr"/>
+      <c r="F725" t="inlineStr"/>
+      <c r="G725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="n">
@@ -14949,6 +17136,9 @@
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.white_label_api_brokerage_725 + tests/test_hero_batch_01_capabilities.py — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978/heroes evidence but absent from cap646.backend_registry (binding_for KeyError). Historical quad-evidence used pdf_capability_registry — apparent success did NOT prove production /api/cap646 path. Requires cap646 registration or dedicated CAP978 extension verification track.</t>
         </is>
       </c>
+      <c r="E726" t="inlineStr"/>
+      <c r="F726" t="inlineStr"/>
+      <c r="G726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="n">
@@ -14969,6 +17159,9 @@
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
+      <c r="E727" t="inlineStr"/>
+      <c r="F727" t="inlineStr"/>
+      <c r="G727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="n">
@@ -14989,6 +17182,9 @@
           <t>مبني وشغال فعليًا — bd_platform/grid_bot.py</t>
         </is>
       </c>
+      <c r="E728" t="inlineStr"/>
+      <c r="F728" t="inlineStr"/>
+      <c r="G728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="n">
@@ -15009,6 +17205,9 @@
           <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.ingest_yahoo_finance_macro_196 via platform_api/intelligence/multi-dim/macro/yahoo</t>
         </is>
       </c>
+      <c r="E729" t="inlineStr"/>
+      <c r="F729" t="inlineStr"/>
+      <c r="G729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="n">
@@ -15029,6 +17228,9 @@
           <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.attach_macro_research_sources_196_197 via platform_api/intelligence/multi-dim/macro/alpha-vantage</t>
         </is>
       </c>
+      <c r="E730" t="inlineStr"/>
+      <c r="F730" t="inlineStr"/>
+      <c r="G730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" t="n">
@@ -15049,6 +17251,9 @@
           <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.run_derivatives_ta_research_e2e_192_203 via platform_api/oracle/sources/cryptocompare</t>
         </is>
       </c>
+      <c r="E731" t="inlineStr"/>
+      <c r="F731" t="inlineStr"/>
+      <c r="G731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" t="n">
@@ -15069,6 +17274,9 @@
           <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_bscscan_204 via platform_api/oracle/on-chain/bsc</t>
         </is>
       </c>
+      <c r="E732" t="inlineStr"/>
+      <c r="F732" t="inlineStr"/>
+      <c r="G732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" t="n">
@@ -15089,6 +17297,9 @@
           <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
+      <c r="E733" t="inlineStr"/>
+      <c r="F733" t="inlineStr"/>
+      <c r="G733" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" t="n">
@@ -15109,6 +17320,9 @@
           <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_reddit_sentiment_208 via platform_api/radar/sentiment/social/reddit</t>
         </is>
       </c>
+      <c r="E734" t="inlineStr"/>
+      <c r="F734" t="inlineStr"/>
+      <c r="G734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" t="n">
@@ -15129,6 +17343,9 @@
           <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.ingest_blockchain_com_148 via platform_api/oracle/on-chain/sources/blockchain-com</t>
         </is>
       </c>
+      <c r="E735" t="inlineStr"/>
+      <c r="F735" t="inlineStr"/>
+      <c r="G735" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" t="n">
@@ -15149,6 +17366,9 @@
           <t>مبني وشغال فعليًا — bd_platform.onchain_hub.dexscreener_pairs</t>
         </is>
       </c>
+      <c r="E736" t="inlineStr"/>
+      <c r="F736" t="inlineStr"/>
+      <c r="G736" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" t="n">
@@ -15169,6 +17389,9 @@
           <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
+      <c r="E737" t="inlineStr"/>
+      <c r="F737" t="inlineStr"/>
+      <c r="G737" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" t="n">
@@ -15189,6 +17412,9 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
+      <c r="E738" t="inlineStr"/>
+      <c r="F738" t="inlineStr"/>
+      <c r="G738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="n">
@@ -15209,6 +17435,9 @@
           <t>مبني وشغال فعليًا — platform_api.py</t>
         </is>
       </c>
+      <c r="E739" t="inlineStr"/>
+      <c r="F739" t="inlineStr"/>
+      <c r="G739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" t="n">
@@ -15229,6 +17458,9 @@
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
+      <c r="E740" t="inlineStr"/>
+      <c r="F740" t="inlineStr"/>
+      <c r="G740" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" t="n">
@@ -15249,6 +17481,9 @@
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
+      <c r="E741" t="inlineStr"/>
+      <c r="F741" t="inlineStr"/>
+      <c r="G741" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" t="n">
@@ -15269,6 +17504,9 @@
           <t>مبني وشغال فعليًا — gdpr_service.gdpr_compliance_status</t>
         </is>
       </c>
+      <c r="E742" t="inlineStr"/>
+      <c r="F742" t="inlineStr"/>
+      <c r="G742" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" t="n">
@@ -15289,6 +17527,9 @@
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
+      <c r="E743" t="inlineStr"/>
+      <c r="F743" t="inlineStr"/>
+      <c r="G743" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" t="n">
@@ -15309,6 +17550,9 @@
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
+      <c r="E744" t="inlineStr"/>
+      <c r="F744" t="inlineStr"/>
+      <c r="G744" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" t="n">
@@ -15329,6 +17573,9 @@
           <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.evaluate_aml_gate_59</t>
         </is>
       </c>
+      <c r="E745" t="inlineStr"/>
+      <c r="F745" t="inlineStr"/>
+      <c r="G745" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" t="n">
@@ -15349,6 +17596,9 @@
           <t>مبني وشغال فعليًا — subscription_analytics.subscription_analytics_status_745</t>
         </is>
       </c>
+      <c r="E746" t="inlineStr"/>
+      <c r="F746" t="inlineStr"/>
+      <c r="G746" t="inlineStr"/>
     </row>
     <row r="747">
       <c r="A747" t="n">
@@ -15369,6 +17619,9 @@
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
+      <c r="E747" t="inlineStr"/>
+      <c r="F747" t="inlineStr"/>
+      <c r="G747" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" t="n">
@@ -15389,6 +17642,9 @@
           <t>مبني وشغال فعليًا — billing_service.billing_status</t>
         </is>
       </c>
+      <c r="E748" t="inlineStr"/>
+      <c r="F748" t="inlineStr"/>
+      <c r="G748" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" t="n">
@@ -15409,6 +17665,9 @@
           <t>مبني وشغال فعليًا — trust_compounding.build_evidence_pack</t>
         </is>
       </c>
+      <c r="E749" t="inlineStr"/>
+      <c r="F749" t="inlineStr"/>
+      <c r="G749" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" t="n">
@@ -15429,6 +17688,9 @@
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
+      <c r="E750" t="inlineStr"/>
+      <c r="F750" t="inlineStr"/>
+      <c r="G750" t="inlineStr"/>
     </row>
     <row r="751">
       <c r="A751" t="n">
@@ -15449,6 +17711,9 @@
           <t>مبني وشغال فعليًا — kill_rate_board.py + anti_hype_mode.py + proof_arena.py</t>
         </is>
       </c>
+      <c r="E751" t="inlineStr"/>
+      <c r="F751" t="inlineStr"/>
+      <c r="G751" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" t="n">
@@ -15469,6 +17734,9 @@
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
+      <c r="E752" t="inlineStr"/>
+      <c r="F752" t="inlineStr"/>
+      <c r="G752" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" t="n">
@@ -15489,6 +17757,9 @@
           <t>مبني وشغال فعليًا — institutional_assurance.backup_status</t>
         </is>
       </c>
+      <c r="E753" t="inlineStr"/>
+      <c r="F753" t="inlineStr"/>
+      <c r="G753" t="inlineStr"/>
     </row>
     <row r="754">
       <c r="A754" t="n">
@@ -15509,6 +17780,9 @@
           <t>مبني وشغال فعليًا — institutional_assurance.ir_program</t>
         </is>
       </c>
+      <c r="E754" t="inlineStr"/>
+      <c r="F754" t="inlineStr"/>
+      <c r="G754" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" t="n">
@@ -15529,6 +17803,9 @@
           <t>مبني وشغال فعليًا — docs/ops/INCIDENT_RESPONSE.md + institutional_assurance/incident_response.json</t>
         </is>
       </c>
+      <c r="E755" t="inlineStr"/>
+      <c r="F755" t="inlineStr"/>
+      <c r="G755" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" t="n">
@@ -15549,6 +17826,9 @@
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
+      <c r="E756" t="inlineStr"/>
+      <c r="F756" t="inlineStr"/>
+      <c r="G756" t="inlineStr"/>
     </row>
     <row r="757">
       <c r="A757" t="n">
@@ -15569,6 +17849,9 @@
           <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
         </is>
       </c>
+      <c r="E757" t="inlineStr"/>
+      <c r="F757" t="inlineStr"/>
+      <c r="G757" t="inlineStr"/>
     </row>
     <row r="758">
       <c r="A758" t="n">
@@ -15589,6 +17872,9 @@
           <t>مبني وشغال فعليًا — institutional_assurance.get_signed_capacity</t>
         </is>
       </c>
+      <c r="E758" t="inlineStr"/>
+      <c r="F758" t="inlineStr"/>
+      <c r="G758" t="inlineStr"/>
     </row>
     <row r="759">
       <c r="A759" t="n">
@@ -15609,6 +17895,9 @@
           <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
+      <c r="E759" t="inlineStr"/>
+      <c r="F759" t="inlineStr"/>
+      <c r="G759" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" t="n">
@@ -15629,6 +17918,9 @@
           <t>مبني وشغال فعليًا — bd_platform/infra_intelligence_layer.py</t>
         </is>
       </c>
+      <c r="E760" t="inlineStr"/>
+      <c r="F760" t="inlineStr"/>
+      <c r="G760" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" t="n">
@@ -15649,6 +17941,9 @@
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
+      <c r="E761" t="inlineStr"/>
+      <c r="F761" t="inlineStr"/>
+      <c r="G761" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" t="n">
@@ -15669,6 +17964,9 @@
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
+      <c r="E762" t="inlineStr"/>
+      <c r="F762" t="inlineStr"/>
+      <c r="G762" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" t="n">
@@ -15689,6 +17987,9 @@
           <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.run_onchain_platform_e2e_129_139 via platform_api/portfolio/stress-alert</t>
         </is>
       </c>
+      <c r="E763" t="inlineStr"/>
+      <c r="F763" t="inlineStr"/>
+      <c r="G763" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" t="n">
@@ -15709,6 +18010,9 @@
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
+      <c r="E764" t="inlineStr"/>
+      <c r="F764" t="inlineStr"/>
+      <c r="G764" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" t="n">
@@ -15729,6 +18033,9 @@
           <t>مبني وشغال فعليًا — sentiment_manipulation_guard.py — spoofed/manipulated signal detection</t>
         </is>
       </c>
+      <c r="E765" t="inlineStr"/>
+      <c r="F765" t="inlineStr"/>
+      <c r="G765" t="inlineStr"/>
     </row>
     <row r="766">
       <c r="A766" t="n">
@@ -15749,6 +18056,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E766" t="inlineStr"/>
+      <c r="F766" t="inlineStr"/>
+      <c r="G766" t="inlineStr"/>
     </row>
     <row r="767">
       <c r="A767" t="n">
@@ -15769,6 +18079,9 @@
           <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
       </c>
+      <c r="E767" t="inlineStr"/>
+      <c r="F767" t="inlineStr"/>
+      <c r="G767" t="inlineStr"/>
     </row>
     <row r="768">
       <c r="A768" t="n">
@@ -15789,6 +18102,9 @@
           <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
       </c>
+      <c r="E768" t="inlineStr"/>
+      <c r="F768" t="inlineStr"/>
+      <c r="G768" t="inlineStr"/>
     </row>
     <row r="769">
       <c r="A769" t="n">
@@ -15809,6 +18125,9 @@
           <t>مبني وشغال فعليًا — tests/test_i18n_25_locales.py</t>
         </is>
       </c>
+      <c r="E769" t="inlineStr"/>
+      <c r="F769" t="inlineStr"/>
+      <c r="G769" t="inlineStr"/>
     </row>
     <row r="770">
       <c r="A770" t="n">
@@ -15829,6 +18148,9 @@
           <t>مبني وشغال فعليًا — tests/test_i18n_25_locales.py</t>
         </is>
       </c>
+      <c r="E770" t="inlineStr"/>
+      <c r="F770" t="inlineStr"/>
+      <c r="G770" t="inlineStr"/>
     </row>
     <row r="771">
       <c r="A771" t="n">
@@ -15849,6 +18171,9 @@
           <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
       </c>
+      <c r="E771" t="inlineStr"/>
+      <c r="F771" t="inlineStr"/>
+      <c r="G771" t="inlineStr"/>
     </row>
     <row r="772">
       <c r="A772" t="n">
@@ -15869,6 +18194,9 @@
           <t>مبني وشغال فعليًا — bd_platform.market_analysis_layer.compute_whale_retail_ratio_107</t>
         </is>
       </c>
+      <c r="E772" t="inlineStr"/>
+      <c r="F772" t="inlineStr"/>
+      <c r="G772" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" t="n">
@@ -15889,6 +18217,9 @@
           <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
+      <c r="E773" t="inlineStr"/>
+      <c r="F773" t="inlineStr"/>
+      <c r="G773" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" t="n">
@@ -15909,6 +18240,9 @@
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
+      <c r="E774" t="inlineStr"/>
+      <c r="F774" t="inlineStr"/>
+      <c r="G774" t="inlineStr"/>
     </row>
     <row r="775">
       <c r="A775" t="n">
@@ -15929,6 +18263,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E775" t="inlineStr"/>
+      <c r="F775" t="inlineStr"/>
+      <c r="G775" t="inlineStr"/>
     </row>
     <row r="776">
       <c r="A776" t="n">
@@ -15949,6 +18286,9 @@
           <t>مبني وشغال فعليًا — bd_platform/roadmap_audit.py</t>
         </is>
       </c>
+      <c r="E776" t="inlineStr"/>
+      <c r="F776" t="inlineStr"/>
+      <c r="G776" t="inlineStr"/>
     </row>
     <row r="777">
       <c r="A777" t="n">
@@ -15969,6 +18309,9 @@
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
+      <c r="E777" t="inlineStr"/>
+      <c r="F777" t="inlineStr"/>
+      <c r="G777" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" t="n">
@@ -15989,6 +18332,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E778" t="inlineStr"/>
+      <c r="F778" t="inlineStr"/>
+      <c r="G778" t="inlineStr"/>
     </row>
     <row r="779">
       <c r="A779" t="n">
@@ -16009,6 +18355,9 @@
           <t>مبني وشغال فعليًا — bd_platform/pro_trader_layer.py</t>
         </is>
       </c>
+      <c r="E779" t="inlineStr"/>
+      <c r="F779" t="inlineStr"/>
+      <c r="G779" t="inlineStr"/>
     </row>
     <row r="780">
       <c r="A780" t="n">
@@ -16029,6 +18378,9 @@
           <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216</t>
         </is>
       </c>
+      <c r="E780" t="inlineStr"/>
+      <c r="F780" t="inlineStr"/>
+      <c r="G780" t="inlineStr"/>
     </row>
     <row r="781">
       <c r="A781" t="n">
@@ -16049,6 +18401,9 @@
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
+      <c r="E781" t="inlineStr"/>
+      <c r="F781" t="inlineStr"/>
+      <c r="G781" t="inlineStr"/>
     </row>
     <row r="782">
       <c r="A782" t="n">
@@ -16069,6 +18424,9 @@
           <t>مبني وشغال فعليًا — tests/test_english_ui_rule.py</t>
         </is>
       </c>
+      <c r="E782" t="inlineStr"/>
+      <c r="F782" t="inlineStr"/>
+      <c r="G782" t="inlineStr"/>
     </row>
     <row r="783">
       <c r="A783" t="n">
@@ -16089,6 +18447,9 @@
           <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170</t>
         </is>
       </c>
+      <c r="E783" t="inlineStr"/>
+      <c r="F783" t="inlineStr"/>
+      <c r="G783" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" t="n">
@@ -16109,6 +18470,9 @@
           <t>مبني وشغال فعليًا — sentiment_manipulation_guard spoof detection</t>
         </is>
       </c>
+      <c r="E784" t="inlineStr"/>
+      <c r="F784" t="inlineStr"/>
+      <c r="G784" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" t="n">
@@ -16129,6 +18493,9 @@
           <t>مبني وشغال فعليًا — secrets_vault.get_vault_key</t>
         </is>
       </c>
+      <c r="E785" t="inlineStr"/>
+      <c r="F785" t="inlineStr"/>
+      <c r="G785" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" t="n">
@@ -16149,6 +18516,9 @@
           <t>مبني وشغال فعليًا — secrets_vault.get_vault_key</t>
         </is>
       </c>
+      <c r="E786" t="inlineStr"/>
+      <c r="F786" t="inlineStr"/>
+      <c r="G786" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" t="n">
@@ -16169,6 +18539,9 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
+      <c r="E787" t="inlineStr"/>
+      <c r="F787" t="inlineStr"/>
+      <c r="G787" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" t="n">
@@ -16189,6 +18562,9 @@
           <t>مبني وشغال فعليًا — pentest_attestation.get_pentest_attestation</t>
         </is>
       </c>
+      <c r="E788" t="inlineStr"/>
+      <c r="F788" t="inlineStr"/>
+      <c r="G788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" t="n">
@@ -16209,6 +18585,9 @@
           <t>مبني وشغال فعليًا — cap646.handlers.institutional.handle_institutional_capability</t>
         </is>
       </c>
+      <c r="E789" t="inlineStr"/>
+      <c r="F789" t="inlineStr"/>
+      <c r="G789" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" t="n">
@@ -16229,6 +18608,9 @@
           <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.capital_allocation_insight_213 via platform_api/portfolio/capital-allocation</t>
         </is>
       </c>
+      <c r="E790" t="inlineStr"/>
+      <c r="F790" t="inlineStr"/>
+      <c r="G790" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" t="n">
@@ -16249,6 +18631,9 @@
           <t>مبني وشغال فعليًا — stale_price_guard.py + exchange health scrapers</t>
         </is>
       </c>
+      <c r="E791" t="inlineStr"/>
+      <c r="F791" t="inlineStr"/>
+      <c r="G791" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" t="n">
@@ -16269,6 +18654,9 @@
           <t>مبني وشغال فعليًا — bd_platform/tradingview_bridge.py chart_config</t>
         </is>
       </c>
+      <c r="E792" t="inlineStr"/>
+      <c r="F792" t="inlineStr"/>
+      <c r="G792" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" t="n">
@@ -16289,6 +18677,9 @@
           <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
+      <c r="E793" t="inlineStr"/>
+      <c r="F793" t="inlineStr"/>
+      <c r="G793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="n">
@@ -16309,6 +18700,9 @@
           <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.evaluate_aml_gate_59</t>
         </is>
       </c>
+      <c r="E794" t="inlineStr"/>
+      <c r="F794" t="inlineStr"/>
+      <c r="G794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" t="n">
@@ -16329,6 +18723,9 @@
           <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
+      <c r="E795" t="inlineStr"/>
+      <c r="F795" t="inlineStr"/>
+      <c r="G795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" t="n">
@@ -16349,6 +18746,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E796" t="inlineStr"/>
+      <c r="F796" t="inlineStr"/>
+      <c r="G796" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" t="n">
@@ -16369,6 +18769,9 @@
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.analyze_wallet_surveillance_79 via platform_api/oracle/on-chain/surveillance</t>
         </is>
       </c>
+      <c r="E797" t="inlineStr"/>
+      <c r="F797" t="inlineStr"/>
+      <c r="G797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" t="n">
@@ -16389,6 +18792,9 @@
           <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.build_admin_analytics_dashboard_95</t>
         </is>
       </c>
+      <c r="E798" t="inlineStr"/>
+      <c r="F798" t="inlineStr"/>
+      <c r="G798" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" t="n">
@@ -16409,6 +18815,9 @@
           <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 via platform_api/oracle/on-chain/security/flash-loan-scan</t>
         </is>
       </c>
+      <c r="E799" t="inlineStr"/>
+      <c r="F799" t="inlineStr"/>
+      <c r="G799" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" t="n">
@@ -16429,6 +18838,9 @@
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_performance_ledger_view_84 via platform_api/transparency/performance</t>
         </is>
       </c>
+      <c r="E800" t="inlineStr"/>
+      <c r="F800" t="inlineStr"/>
+      <c r="G800" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" t="n">
@@ -16449,6 +18861,9 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
+      <c r="E801" t="inlineStr"/>
+      <c r="F801" t="inlineStr"/>
+      <c r="G801" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" t="n">
@@ -16469,6 +18884,9 @@
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
+      <c r="E802" t="inlineStr"/>
+      <c r="F802" t="inlineStr"/>
+      <c r="G802" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" t="n">
@@ -16489,6 +18907,9 @@
           <t>مبني وشغال فعليًا — aggregator.py + live_book_hub.py + cap646/handlers/market.py</t>
         </is>
       </c>
+      <c r="E803" t="inlineStr"/>
+      <c r="F803" t="inlineStr"/>
+      <c r="G803" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" t="n">
@@ -16509,6 +18930,9 @@
           <t>مبني وشغال فعليًا — audit_registry.py + security_trust_data_layer audit_log_id_242</t>
         </is>
       </c>
+      <c r="E804" t="inlineStr"/>
+      <c r="F804" t="inlineStr"/>
+      <c r="G804" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" t="n">
@@ -16529,6 +18953,9 @@
           <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194</t>
         </is>
       </c>
+      <c r="E805" t="inlineStr"/>
+      <c r="F805" t="inlineStr"/>
+      <c r="G805" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" t="n">
@@ -16549,6 +18976,9 @@
           <t>مبني وشغال فعليًا — docs/ops/INCIDENT_RESPONSE.md + institutional_assurance/incident_response.json</t>
         </is>
       </c>
+      <c r="E806" t="inlineStr"/>
+      <c r="F806" t="inlineStr"/>
+      <c r="G806" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" t="n">
@@ -16569,6 +18999,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E807" t="inlineStr"/>
+      <c r="F807" t="inlineStr"/>
+      <c r="G807" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" t="n">
@@ -16589,6 +19022,9 @@
           <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
       </c>
+      <c r="E808" t="inlineStr"/>
+      <c r="F808" t="inlineStr"/>
+      <c r="G808" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" t="n">
@@ -16609,6 +19045,9 @@
           <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
       </c>
+      <c r="E809" t="inlineStr"/>
+      <c r="F809" t="inlineStr"/>
+      <c r="G809" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" t="n">
@@ -16629,6 +19068,9 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
+      <c r="E810" t="inlineStr"/>
+      <c r="F810" t="inlineStr"/>
+      <c r="G810" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" t="n">
@@ -16649,6 +19091,9 @@
           <t>مبني وشغال فعليًا — enterprise_sso.build_sso_authorize_url_async</t>
         </is>
       </c>
+      <c r="E811" t="inlineStr"/>
+      <c r="F811" t="inlineStr"/>
+      <c r="G811" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" t="n">
@@ -16669,6 +19114,9 @@
           <t>مبني وشغال فعليًا — bd_platform.legal_commercial_layer.gdpr_compliance_status_58</t>
         </is>
       </c>
+      <c r="E812" t="inlineStr"/>
+      <c r="F812" t="inlineStr"/>
+      <c r="G812" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" t="n">
@@ -16689,6 +19137,9 @@
           <t>مبني جزئيًا — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978 catalog and batch-01 evidence but absent from cap646.backend_registry (binding_for KeyError). Requires cap646 registration or dedicated CAP978 extension verification track — not auditable via /api/cap646/{id} today.</t>
         </is>
       </c>
+      <c r="E813" t="inlineStr"/>
+      <c r="F813" t="inlineStr"/>
+      <c r="G813" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" t="n">
@@ -16709,6 +19160,9 @@
           <t>مبني وشغال فعليًا — constitution_gates.ensure_execution_gates — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978/heroes evidence but absent from cap646.backend_registry (binding_for KeyError). Historical quad-evidence used pdf_capability_registry — apparent success did NOT prove production /api/cap646 path. Requires cap646 registration or dedicated CAP978 extension verification track.</t>
         </is>
       </c>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="inlineStr"/>
+      <c r="G814" t="inlineStr"/>
     </row>
     <row r="815">
       <c r="A815" t="n">
@@ -16729,6 +19183,9 @@
           <t>مبني جزئيًا — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978 catalog and batch-01 evidence but absent from cap646.backend_registry (binding_for KeyError). Requires cap646 registration or dedicated CAP978 extension verification track — not auditable via /api/cap646/{id} today.</t>
         </is>
       </c>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="inlineStr"/>
+      <c r="G815" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" t="n">
@@ -16749,6 +19206,9 @@
           <t>مبني جزئيًا — EXTENSION-PENDING-CAP646; EXTENSION-PENDING-CAP646: ID present in CAP978 catalog and batch-01 evidence but absent from cap646.backend_registry (binding_for KeyError). Requires cap646 registration or dedicated CAP978 extension verification track — not auditable via /api/cap646/{id} today.</t>
         </is>
       </c>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="inlineStr"/>
+      <c r="G816" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" t="n">
@@ -16769,6 +19229,9 @@
           <t>مبني وشغال فعليًا — dimension_conflict_guard.dimension_conflict_status</t>
         </is>
       </c>
+      <c r="E817" t="inlineStr"/>
+      <c r="F817" t="inlineStr"/>
+      <c r="G817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" t="n">
@@ -16789,6 +19252,9 @@
           <t>مبني وشغال فعليًا — bd_platform/cex_dex_arbitrage.py</t>
         </is>
       </c>
+      <c r="E818" t="inlineStr"/>
+      <c r="F818" t="inlineStr"/>
+      <c r="G818" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" t="n">
@@ -16809,6 +19275,9 @@
           <t>مبني وشغال فعليًا — coverage_honesty.py</t>
         </is>
       </c>
+      <c r="E819" t="inlineStr"/>
+      <c r="F819" t="inlineStr"/>
+      <c r="G819" t="inlineStr"/>
     </row>
     <row r="820">
       <c r="A820" t="n">
@@ -16829,6 +19298,9 @@
           <t>مبني وشغال فعليًا — blackdark.data.db.data_engine_available</t>
         </is>
       </c>
+      <c r="E820" t="inlineStr"/>
+      <c r="F820" t="inlineStr"/>
+      <c r="G820" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" t="n">
@@ -16849,6 +19321,9 @@
           <t>مبني وشغال فعليًا — b2b_websocket_hub.py</t>
         </is>
       </c>
+      <c r="E821" t="inlineStr"/>
+      <c r="F821" t="inlineStr"/>
+      <c r="G821" t="inlineStr"/>
     </row>
     <row r="822">
       <c r="A822" t="n">
@@ -16869,6 +19344,9 @@
           <t>مبني وشغال فعليًا — didit_kyc.didit_status</t>
         </is>
       </c>
+      <c r="E822" t="inlineStr"/>
+      <c r="F822" t="inlineStr"/>
+      <c r="G822" t="inlineStr"/>
     </row>
     <row r="823">
       <c r="A823" t="n">
@@ -16889,6 +19367,9 @@
           <t>مبني وشغال فعليًا — bd_platform.finbert_sentiment.analyze_text</t>
         </is>
       </c>
+      <c r="E823" t="inlineStr"/>
+      <c r="F823" t="inlineStr"/>
+      <c r="G823" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" t="n">
@@ -16909,6 +19390,9 @@
           <t>مبني وشغال فعليًا — regulatory_compliance_guard.py</t>
         </is>
       </c>
+      <c r="E824" t="inlineStr"/>
+      <c r="F824" t="inlineStr"/>
+      <c r="G824" t="inlineStr"/>
     </row>
     <row r="825">
       <c r="A825" t="n">
@@ -16929,6 +19413,9 @@
           <t>مبني وشغال فعليًا — constitution_gates.py</t>
         </is>
       </c>
+      <c r="E825" t="inlineStr"/>
+      <c r="F825" t="inlineStr"/>
+      <c r="G825" t="inlineStr"/>
     </row>
     <row r="826">
       <c r="A826" t="n">
@@ -16949,6 +19436,9 @@
           <t>مبني وشغال فعليًا — lp_il_simulator.compute_impermanent_loss_pct</t>
         </is>
       </c>
+      <c r="E826" t="inlineStr"/>
+      <c r="F826" t="inlineStr"/>
+      <c r="G826" t="inlineStr"/>
     </row>
     <row r="827">
       <c r="A827" t="n">
@@ -16969,6 +19459,9 @@
           <t>مبني وشغال فعليًا — glass_box_challenge.build_glass_box_operator_pack</t>
         </is>
       </c>
+      <c r="E827" t="inlineStr"/>
+      <c r="F827" t="inlineStr"/>
+      <c r="G827" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/capabilities_checklist.xlsx
+++ b/capabilities_checklist.xlsx
@@ -55,10 +55,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,9 +487,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=bd_platform.footprint_analytics.footprint_snapshot; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -507,9 +507,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=trade_simulator.simulate_spot_trade; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -530,9 +527,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.free_tier_capabilities.wallet_profiler_for_token; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -553,9 +547,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.free_tier_capabilities.smart_money_tracking; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -576,9 +567,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=bd_platform.onchain_hub.dexscreener_pairs (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -599,9 +587,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -622,9 +607,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -645,9 +627,6 @@
           <t>مبني وشغال فعليًا — cap646.institutional_controls._sec_8</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -668,9 +647,6 @@
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.execution_risk_score_9 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -691,9 +667,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=instant_alert_engine.engine_stats; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -714,9 +687,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=arbitrage_service.scan_arbitrage_opportunities; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -737,9 +707,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.whales_institutional_layer.evaluate_liquidation_alert_82; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -760,9 +727,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -783,9 +747,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=market_context.whale_alert_message; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -806,9 +767,6 @@
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.flash_loan_attack_proximity_15 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -829,9 +787,6 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -852,9 +807,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=alert_service.subscribe_alerts; production=instant_alert_engine.engine_stats (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -875,9 +827,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.alert_orchestration.alert_orchestration_status_18; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -898,9 +847,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.get_alert_policy_75; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -921,9 +867,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.append_audit_event_242; production=bd_platform.portfolio_rebalancer.portfolio_snapshot (capability_keyword).</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -944,9 +887,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.alert_orchestration.alert_orchestration_status_18; production=scale_readiness.scale_readiness_report (track_default).</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -967,9 +907,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.list_etherscan_watchlist_246; production=bd_platform.onchain_hub.debank_wallet (capability_keyword).</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -990,9 +927,6 @@
           <t>مبني وشغال فعليًا — aggregator.py + live_book_hub.py + cap646/handlers/market.py</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1013,9 +947,6 @@
           <t>مبني وشغال فعليًا — aggregator.py + live_book_hub.py + cap646/handlers/market.py</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1036,9 +967,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_GENERIC_HANDLER; audit=bd_platform.footprint_analytics.footprint_snapshot; production=trust_pulse.build_trust_pulse (track_default).</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1059,9 +987,6 @@
           <t>مبني وشغال فعليًا — bd_platform.derivatives_hub.derivatives_overview</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1082,9 +1007,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1105,9 +1027,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.retail_intelligence_layer.evaluate_contextual_alert_65; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1128,9 +1047,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.retail_intelligence_layer.compare_discipline_66; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1151,9 +1067,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1174,9 +1087,6 @@
           <t>مبني وشغال فعليًا — bd_platform.retail_intelligence_layer.build_discipline_tab_66</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1197,9 +1107,6 @@
           <t>مبني وشغال فعليًا — bd_platform.derivatives_ta_research_layer.compute_cvd_194</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1220,9 +1127,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.retail_intelligence_layer.build_one_clear_answer_63; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1243,9 +1147,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1266,9 +1167,6 @@
           <t>مبني وشغال فعليًا — bd_platform/footprint_analytics.py + market_analysis_layer</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1289,9 +1187,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=risk_manager.is_trading_frozen; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1312,9 +1207,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.evaluate_flexible_alert_75; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1335,9 +1227,6 @@
           <t>مبني وشغال فعليًا — bd_platform/telegram_agent.py + intelligence_analysis_layer #161</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1358,9 +1247,6 @@
           <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1381,9 +1267,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189; production=bd_platform.onchain_hub.lookintobitcoin_macro (capability_keyword).</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1404,9 +1287,6 @@
           <t>مبني وشغال فعليًا — execution_engine.get_execution_status</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1427,9 +1307,6 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1450,9 +1327,6 @@
           <t>مبني وشغال فعليًا — bd_platform/mvrv_realignment.py compute_mvrv_realignment</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1473,9 +1347,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153; production=bd_platform.portfolio_rebalancer.portfolio_snapshot (capability_keyword).</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1496,9 +1367,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.free_tier_capabilities.smart_money_leaderboard; production=market_context.probe_price_sources (track_default).</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1519,9 +1387,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_GENERIC_HANDLER; audit=bd_platform.slippage_tolerance_optimizer.optimize_slippage_tolerance; production=market_context.probe_price_sources (track_default).</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1542,9 +1407,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.whales_institutional_layer.build_exchange_health_80; production=market_context.probe_price_sources (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1565,9 +1427,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.ingest_bybit_price_243; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1588,9 +1447,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.flash_crash_protection.flash_crash_protection_status_49; production=options_fetcher.fetch_options_overview (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1611,9 +1467,6 @@
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.mvrv_z_score_50 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1634,9 +1487,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1657,9 +1507,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1680,9 +1527,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1703,9 +1547,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1726,9 +1567,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1749,9 +1587,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1772,9 +1607,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1795,9 +1627,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1818,9 +1647,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1841,9 +1667,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1864,9 +1687,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1887,9 +1707,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1910,9 +1727,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1933,9 +1747,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1956,9 +1767,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1979,9 +1787,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2002,9 +1807,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2025,9 +1827,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2048,9 +1847,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2071,9 +1867,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2094,9 +1887,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2117,9 +1907,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2140,9 +1927,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2163,9 +1947,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2186,9 +1967,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2209,9 +1987,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2232,9 +2007,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2255,9 +2027,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2278,9 +2047,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2301,9 +2067,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2324,9 +2087,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2347,9 +2107,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2370,9 +2127,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2393,9 +2147,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2416,9 +2167,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2439,9 +2187,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2462,9 +2207,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2485,9 +2227,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2508,9 +2247,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2531,9 +2267,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2554,9 +2287,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2577,9 +2307,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2600,9 +2327,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2623,9 +2347,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2646,9 +2367,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2669,9 +2387,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2692,9 +2407,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2715,9 +2427,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2738,9 +2447,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2761,9 +2467,6 @@
           <t>PRODUCTION-ALIGNED (official batch02)</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2784,9 +2487,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.infra_intelligence_layer.validate_oracle_freshness_101; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2807,9 +2507,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.infra_intelligence_layer.compute_il_vulnerability_102; production=trust_pulse.build_trust_pulse (track_default).</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2830,9 +2527,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.whales_institutional_layer._compute_drawdown_duration_103; production=hot_storage.get_hot_storage_stats (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2853,9 +2547,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.infra_intelligence_layer.run_infra_intelligence_e2e_95_104 + tests/test_hero_batch_02_capabilities.py | proof=04b6f48520e87a33 (deferred)</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2876,9 +2567,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.attach_tail_risk_to_backtest_105; production=data_provenance_score.compute_data_provenance_score (track_default).</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2899,9 +2587,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_contagion_vector_106; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2922,9 +2607,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_whale_retail_ratio_107; production=signal_registry.registry_stats (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2945,9 +2627,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_orderbook_skew_108; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2968,9 +2647,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.attach_liquidation_anchors_109; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2991,9 +2667,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.attach_whale_extensions_107_110; production=ai_oracle.evaluate_opportunity (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3014,9 +2687,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.market_analysis_layer.compute_spx_correlation_111; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3037,9 +2707,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_gcli_112; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3060,9 +2727,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_imbalance_delta_113; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -3083,9 +2747,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.attach_market_health_bundle_106_112_114; production=due_diligence_bundle.build_full_due_diligence_bundle (capability_keyword).</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -3106,9 +2767,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.compute_volume_velocity_115; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3129,9 +2787,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_analysis_layer.run_market_analysis_e2e_105_116; production=bd_platform.onchain_hub.dexscreener_pairs (capability_keyword).</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3152,9 +2807,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.compute_liquidity_vacuum_117; production=data_provenance_score.compute_data_provenance_score (capability_keyword).</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -3175,9 +2827,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.attach_risk_distribution_118; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -3198,9 +2847,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.gas_spike_alert_119 + tests/test_hero_batch_02_capabilities.py | proof=94c9046b8987c79f (deferred)</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -3221,9 +2867,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.attach_leverage_risk_120 + tests/test_hero_batch_02_capabilities.py | proof=fb767a8fb1d81fc5 (deferred)</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -3244,9 +2887,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.attach_journal_attribution_121; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3267,9 +2907,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.compute_structural_break_122 + tests/test_hero_batch_02_capabilities.py | proof=8219e7cbbb4af67e (deferred)</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3290,9 +2927,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3313,9 +2947,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.advanced_ta_risk_layer.detect_fair_value_gaps_124; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3336,9 +2967,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.custody_tracking_status_125 + tests/test_hero_batch_02_capabilities.py | proof=ef2d5b8e047cfe12 (deferred)</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3359,9 +2987,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.dex_front_running_risk_126 + tests/test_hero_batch_01_capabilities.py | proof=f358382e13507bd6 (deferred)</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3382,9 +3007,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.orderbook_inefficiency_insight_127 + tests/test_hero_batch_02_capabilities.py | proof=88def6faccb782cc (deferred)</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3405,9 +3027,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.advanced_ta_risk_layer.run_advanced_ta_risk_e2e_117_128 + tests/test_hero_batch_02_capabilities.py | proof=39b021e04931808a (deferred)</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3428,9 +3047,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_platform_layer.attach_sybil_clustering_129; production=sentiment_gate.fetch_asset_sentiment (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3451,9 +3067,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.transaction_risk_insight_130 + tests/test_hero_batch_02_capabilities.py | proof=140846bc87832d7a (deferred)</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3474,9 +3087,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.analyze_dust_assets_131 + tests/test_hero_batch_02_capabilities.py | proof=c2de62f8049cebf9 (deferred)</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3497,9 +3107,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132 + tests/test_hero_batch_02_capabilities.py | proof=44ded9a4f1dbcaef (deferred)</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3520,9 +3127,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_platform_layer.attach_macro_nexus_to_multi_dim_133; production=bd_platform.news_classifier.coindesk_feed (capability_keyword).</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3543,9 +3147,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_platform_layer.compute_delta_convergence_134; production=bd_platform.news_classifier.coindesk_feed (capability_keyword).</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3566,9 +3167,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.locate_liquidity_vortex_135 + tests/test_hero_batch_02_capabilities.py | proof=a25a44a234d04ca4 (deferred)</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3589,9 +3187,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.support_chat_response_136 + tests/test_hero_batch_02_capabilities.py | proof=043a8ec1ca42c2ea (deferred)</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3612,9 +3207,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.b2b_relationships_status_137 + tests/test_hero_batch_02_capabilities.py | proof=3453565f15e4b18d (deferred)</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3635,9 +3227,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.institution_features_status_138 + tests/test_hero_batch_02_capabilities.py | proof=db89ec286186839d (deferred)</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -3658,9 +3247,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_platform_layer.run_onchain_platform_e2e_129_139 + tests/test_hero_batch_02_capabilities.py | proof=7469f8a938c9efc8 (deferred)</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3681,9 +3267,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.white_label_status_140 + tests/test_hero_batch_02_capabilities.py | proof=0d5f9eb47b907fa4 (deferred)</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -3704,9 +3287,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_coindesk_feed_141; production=bd_platform.token_unlocks.unlock_calendar (capability_keyword).</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -3727,9 +3307,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_santiment_metrics_142; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -3750,9 +3327,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_event_calendar_143; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -3773,9 +3347,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_whale_alert_144; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -3796,9 +3367,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_cmc_price_145; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -3819,9 +3387,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.validate_oracle_consensus_145_146; production=bd_platform.derivatives_hub.derivatives_overview (capability_keyword).</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -3842,9 +3407,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.signal_engine_status_147 + tests/test_hero_batch_02_capabilities.py | proof=ddc516bdba67fe96 (deferred)</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -3865,9 +3427,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_blockchain_com_148; production=due_diligence_bundle.build_full_due_diligence_bundle (capability_keyword).</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -3888,9 +3447,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.ingest_defillama_149; production=risk_manager.risk_status (capability_keyword).</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -3911,9 +3467,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.data_sources_layer.attach_opportunity_to_daily_top3_150; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -3934,9 +3487,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.explain_opportunity_151 + tests/test_hero_batch_02_capabilities.py | proof=6a1f7649399cddc9 (deferred)</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -3957,9 +3507,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.data_sources_layer.run_data_sources_e2e_140_152 + tests/test_hero_batch_02_capabilities.py | proof=0bc1db8886bcdad8 (deferred)</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -3980,9 +3527,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.intelligence_analysis_layer.analyze_arbitrage_opportunity_153 + tests/test_hero_batch_02_capabilities.py | proof=721755483b2945dc (deferred)</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -4003,9 +3547,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -4026,9 +3567,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.intelligence_analysis_layer.stat_arb_insight_155 + tests/test_hero_batch_02_capabilities.py | proof=7fa98659e3dadcb4 (deferred)</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -4049,9 +3587,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.asset_registry_105_coins_156; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -4072,9 +3607,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -4095,9 +3627,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.multi_venue_websocket_status_158; production=cap646.fallbacks.resolve_gas_usd (capability_keyword).</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -4118,9 +3647,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.compute_gas_volatility_profile_159; production=hot_storage.get_hot_storage_stats (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -4141,9 +3667,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.detect_volatility_squeeze_160; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -4164,9 +3687,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.alert_delivery_status_161; production=org_tenant.org_isolation_status (track_default).</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -4187,9 +3707,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.data_grid_ui_status_162; production=data_provenance_score.compute_data_provenance_score (capability_keyword).</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -4210,9 +3727,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_analysis_layer.run_intelligence_analysis_e2e_153_163; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -4233,9 +3747,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.liquidity_impact_warning_164 + tests/test_hero_batch_01_capabilities.py | proof=808b7e3033384b16 (deferred)</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -4256,9 +3767,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.hashrate_capitulation_forecast_165; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -4279,9 +3787,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.brokerage_rejected_status_166 + tests/test_hero_batch_02_capabilities.py | proof=2ed11344777da646 (deferred)</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -4302,9 +3807,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.validate_time_sync_167; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -4325,9 +3827,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.attach_cluster_index_168; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -4348,9 +3847,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.attach_correlation_decay_169; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -4371,9 +3867,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.compute_oi_momentum_delta_170; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -4394,9 +3887,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.risk_infrastructure_layer.attach_m2_macro_flow_171; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -4417,9 +3907,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -4440,9 +3927,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -4463,9 +3947,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.full_white_label_status_174 + tests/test_hero_batch_02_capabilities.py | proof=db8bc694743b83cc (deferred)</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -4486,9 +3967,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -4509,9 +3987,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.risk_infrastructure_layer.run_risk_infrastructure_e2e_164_176 + tests/test_hero_batch_02_capabilities.py | proof=a84a3a72b074edab (deferred)</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -4532,9 +4007,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.analyze_arbitrage_cost_177; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -4555,9 +4027,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.attach_scenarios_178; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -4578,9 +4047,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.build_command_center_dashboard_179; production=market_context.probe_price_sources (track_default).</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -4601,9 +4067,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.attach_whale_visualization_180; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -4624,9 +4087,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -4647,9 +4107,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.white_label_infrastructure_status_182; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -4670,9 +4127,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.heroes_capability_layer.onchain_usage_intelligence_183 + tests/test_hero_batch_01_capabilities.py | proof=b7369963edda8686 (deferred)</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -4693,9 +4147,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.fund_reporting_status_184; production=whale_tracker.get_latest_whale_alerts (capability_keyword).</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -4716,9 +4167,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.acquisition_evidence_package_185 + tests/test_hero_batch_02_capabilities.py | proof=db9e7a683209d837 (deferred)</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -4739,9 +4187,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.continuous_learning_status_186 + tests/test_hero_batch_02_capabilities.py | proof=5cfc751f4b2a31ef (deferred)</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -4762,9 +4207,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.latency_monitoring_status_187; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -4785,9 +4227,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.risk_alert_user_confirmation_188 + tests/test_hero_batch_02_capabilities.py | proof=127dde368dd13a82 (deferred)</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -4808,9 +4247,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189; production=market_context.probe_price_sources (track_default).</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -4831,9 +4267,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.attach_arbitrage_extensions_177_189_190 + tests/test_hero_batch_02_capabilities.py | proof=09ff0255054c9fff (deferred)</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -4854,9 +4287,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.arbitrage_portfolio_ux_layer.run_arbitrage_portfolio_ux_e2e_177_191 + tests/test_hero_batch_02_capabilities.py | proof=1f1aa38c1c805843 (deferred)</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -4877,9 +4307,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.analyze_funding_rate_192; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -4900,9 +4327,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.derivatives_ta_research_layer.auto_arbitrage_rejected_status_193 + tests/test_hero_batch_02_capabilities.py | proof=56673bf309232b01 (deferred)</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -4923,9 +4347,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.compute_cvd_194; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -4946,9 +4367,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.derivatives_ta_research_layer.strategy_simulator_195 + tests/test_hero_batch_02_capabilities.py | proof=52632db04722442b (deferred)</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -4969,9 +4387,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.ingest_yahoo_finance_macro_196; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -4992,9 +4407,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.attach_macro_research_sources_196_197; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -5015,9 +4427,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.ingest_binance_research_198; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -5038,9 +4447,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.ingest_messari_research_199; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -5061,9 +4467,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.ingest_coingecko_reports_200; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -5084,9 +4487,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.quantitative_analysis_framework_201; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -5107,9 +4507,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.discover_hidden_opportunities_202; production=scale_readiness.scale_readiness_report (track_default).</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -5130,9 +4527,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_ta_research_layer.run_derivatives_ta_research_e2e_192_203; production=bd_platform.onchain_hub.dexscreener_pairs (capability_keyword).</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -5153,9 +4547,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_bscscan_204; production=bd_platform.onchain_hub.defillama_raises (capability_keyword).</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -5176,9 +4567,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_glassnode_metrics_205; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -5199,9 +4587,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_uniswap_subgraph_206; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -5222,9 +4607,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_aave_data_207; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -5245,9 +4627,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.ingest_reddit_sentiment_208; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -5268,9 +4647,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -5291,9 +4667,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.analyze_predictive_arbitrage_210; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -5314,9 +4687,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.cross_margin_risk_alert_211; production=org_tenant.org_isolation_status (track_default).</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -5337,9 +4707,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.hedge_effectiveness_analysis_212; production=instant_alert_engine.engine_stats (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -5360,9 +4727,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.capital_allocation_insight_213; production=instant_alert_engine.engine_stats (capability_keyword).</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -5383,9 +4747,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.build_whale_narrative_71; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -5406,9 +4767,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.onchain_defi_sources_layer.flash_loan_gas_rejected_status_215 + tests/test_onchain_defi_sources_batch204_216.py | proof=faa17c104ae759de (deferred)</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -5429,9 +4787,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.onchain_defi_sources_layer.run_onchain_defi_sources_e2e_204_216; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -5452,9 +4807,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.analyze_best_venue_217; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -5475,9 +4827,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.attach_order_journal_218; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -5498,9 +4847,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.analyze_nlp_sentiment_219; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -5521,9 +4867,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.attach_pattern_outcome_220; production=data_provenance_score.compute_data_provenance_score (track_default).</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -5544,9 +4887,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.market_slippage_analysis_221; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -5567,9 +4907,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.monitor_exchange_latency_222; production=signal_registry.registry_stats (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -5590,9 +4927,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.analyze_defi_fundamentals_223; production=sentiment_engine.build_sentiment_context_safe (capability_keyword).</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -5613,9 +4947,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -5636,9 +4967,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.pwa_strategy_status_225; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -5659,9 +4987,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.analyze_launch_event_226; production=ai_oracle.evaluate_opportunity (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -5682,9 +5007,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -5705,9 +5027,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.simulate_drawdown_hedge_228; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -5728,9 +5047,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.attach_reasoning_explanation_229; production=arbitrage_service.scan_arbitrage_opportunities (capability_keyword).</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -5751,9 +5067,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.analyze_cross_exchange_divergence_230; production=arbitrage_service.scan_arbitrage_opportunities (capability_keyword).</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -5774,9 +5087,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.intelligence_ux_extensions_layer.triangular_arbitrage_status_231 + tests/test_intelligence_ux_extensions_batch228_241.py | proof=75574418a6a8ca4b (deferred)</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -5797,9 +5107,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.attach_arbitrage_comparison_230_232; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -5820,9 +5127,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233; production=bd_platform.liquidation_radar.liquidation_radar (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -5843,9 +5147,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -5866,9 +5167,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -5889,9 +5187,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -5912,9 +5207,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.generate_market_summary_237; production=risk_manager.risk_status (capability_keyword).</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -5935,9 +5227,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.scan_market_opportunities_238; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -5958,9 +5247,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -5981,9 +5267,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.compute_s2f_240; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -6004,9 +5287,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.intelligence_ux_extensions_layer.run_intelligence_ux_extensions_e2e_228_241; production=sentiment_gate.fetch_asset_sentiment (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -6027,9 +5307,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.attach_audit_log_id_242; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -6050,9 +5327,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.ingest_bybit_price_243; production=bd_platform.derivatives_hub.derivatives_overview (track_default).</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -6073,9 +5347,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -6096,9 +5367,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -6119,9 +5387,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.list_etherscan_watchlist_246; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -6142,9 +5407,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.generate_weekly_digest_247; production=product_honesty_api.build_public_readiness (track_default).</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -6165,9 +5427,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.manual_performance_tracker_248; production=bd_platform.telegram_agent.handle_agent_message (capability_keyword).</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -6188,9 +5447,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.security_trust_data_layer.trad_simulator_rejected_status_249 + tests/test_security_trust_data_batch242_261.py | proof=d60108f2983f98a4 (deferred)</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -6211,9 +5467,6 @@
           <t>مبني جزئيًا — [deferred] bd_platform.security_trust_data_layer.execution_speed_rejected_status_250 + tests/test_security_trust_data_batch242_261.py | proof=4ca762095f9b06d2 (deferred)</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -6234,9 +5487,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.compute_token_velocity_251; production=ai_oracle.evaluate_opportunity (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -6257,9 +5507,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.ingest_google_trends_252; production=bd_platform.liquidation_radar.liquidation_radar (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -6280,9 +5527,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.build_kill_rate_widget_253; production=bd_platform.liquidation_radar.liquidation_radar (capability_keyword).</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -6303,9 +5547,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.build_contradiction_replay_254; production=bd_platform.liquidation_radar.liquidation_radar (capability_keyword).</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -6326,9 +5567,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.committee_one_pager_status_255; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -6349,9 +5587,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.compute_half_life_clock_256; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -6372,9 +5607,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.proof_arena_lite_status_257; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -6395,9 +5627,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.since_you_left_top3_258; production=bd_platform.onchain_hub.defillama_raises (track_default).</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -6418,9 +5647,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.apply_anti_hype_mode_259; production=bd_platform.derivatives_hub.derivatives_overview (capability_keyword).</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -6441,9 +5667,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.corpus_passport_status_260; production=bd_platform.derivatives_hub.derivatives_overview (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -6464,9 +5687,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.security_trust_data_layer.run_security_trust_data_e2e_242_261; production=bd_platform.derivatives_hub.derivatives_overview (capability_keyword).</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -6487,9 +5707,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Open Interest.</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -6510,9 +5727,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Volume.</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -6533,9 +5747,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options IV / Skew.</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -6556,9 +5767,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Max Pain / Gamma Context.</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -6579,9 +5787,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Spot Market Intelligence.</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -6602,9 +5807,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Order Book / Market Depth.</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -6625,9 +5827,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Derivatives Data.</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -6648,9 +5847,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Exchange Comparison.</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -6671,9 +5867,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Cascade Proximity.</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -6694,9 +5887,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Leverage Pressure Score.</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -6717,9 +5907,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_onchain_intelligence_layer.api_data_platform_status_272; production=hot_storage.get_hot_storage_stats (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -6740,9 +5927,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Multi-Model Liquidation Comparison.</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -6763,9 +5947,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_onchain_intelligence_layer.derivatives_alerts_status_274; production=instant_alert_engine.engine_stats (capability_keyword).</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -6786,9 +5967,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Domain Decision Intelligence.</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -6809,9 +5987,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Entity Resolution Engine.</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -6832,9 +6007,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Address Labeling System.</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -6855,9 +6027,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Entity Profiles.</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -6878,9 +6047,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.build_share_card_68; production=onchain_tracker.build_onchain_context_safe (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -6901,9 +6067,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Portfolio Holdings.</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -6924,9 +6087,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Balance History.</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -6947,9 +6107,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Entity PnL.</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -6970,9 +6127,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Exchange Usage Intelligence.</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -6993,9 +6147,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Top Counterparties.</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -7016,9 +6167,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Visualizer / Network Graph.</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -7039,9 +6187,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Automated Trace / Path Finding.</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -7062,9 +6207,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Chain Trace.</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -7085,9 +6227,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.correlation_mindshare.compute_mindshare_correlation_288; production=oracle_track_record.public_track_record (track_default).</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -7108,9 +6247,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Token Exchange Flows.</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -7131,9 +6267,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Token Transaction Explorer.</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -7154,9 +6287,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Dashboards.</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -7177,9 +6307,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Alerts.</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr"/>
-      <c r="F293" t="inlineStr"/>
-      <c r="G293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -7200,9 +6327,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Private Labels.</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr"/>
-      <c r="F294" t="inlineStr"/>
-      <c r="G294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -7223,9 +6347,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Archive / Historical Portfolio Snapshot.</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr"/>
-      <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -7246,9 +6367,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI Market Insights.</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -7269,9 +6387,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Whale Movement Intelligence.</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -7292,9 +6407,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_onchain_intelligence_layer.fraud_suspicious_activity_297; production=onchain_tracker.build_onchain_context_safe (track_default).</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -7315,9 +6427,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API On-Chain Intelligence.</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -7338,9 +6447,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_GENERIC_HANDLER; audit=bd_platform.news_classifier.classify_headlines; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -7361,9 +6467,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.derivatives_onchain_intelligence_layer.run_derivatives_onchain_intelligence_e2e_262_300; production=bd_platform.tradingview_bridge.chart_config (capability_keyword).</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -7384,9 +6487,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Multi-Chart Layouts.</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr"/>
-      <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -7407,9 +6507,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Technical Indicator Library.</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
-      <c r="G303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -7430,9 +6527,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Indicator Scripting.</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -7453,9 +6547,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Strategy Backtesting.</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -7476,9 +6567,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Screener.</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -7499,9 +6587,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Pine-Style Screener.</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr"/>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -7522,9 +6607,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Smart Alerts.</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -7545,9 +6627,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Watchlists.</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr"/>
-      <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -7568,9 +6647,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Economic Calendar.</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr"/>
-      <c r="F310" t="inlineStr"/>
-      <c r="G310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -7591,9 +6667,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Crypto Calendar / Events.</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr"/>
-      <c r="F311" t="inlineStr"/>
-      <c r="G311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -7614,9 +6687,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=News Integration.</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
-      <c r="G312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -7637,9 +6707,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Heatmaps.</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr"/>
-      <c r="F313" t="inlineStr"/>
-      <c r="G313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -7660,9 +6727,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Technical Ratings.</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr"/>
-      <c r="F314" t="inlineStr"/>
-      <c r="G314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -7683,9 +6747,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Drawing Tools.</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr"/>
-      <c r="F315" t="inlineStr"/>
-      <c r="G315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -7706,9 +6767,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Replay Mode.</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -7729,9 +6787,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.sse_stream.sse_digest_status_316; production=bd_platform.tradingview_bridge.chart_config (capability_keyword).</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr"/>
-      <c r="F317" t="inlineStr"/>
-      <c r="G317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -7752,9 +6807,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Community Scripts.</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr"/>
-      <c r="F318" t="inlineStr"/>
-      <c r="G318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -7775,9 +6827,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Broker Comparison.</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr"/>
-      <c r="F319" t="inlineStr"/>
-      <c r="G319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -7798,9 +6847,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Paper Trading / Simulation.</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -7821,9 +6867,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Workspace.</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr"/>
-      <c r="F321" t="inlineStr"/>
-      <c r="G321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -7844,9 +6887,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Intelligence Screener.</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr"/>
-      <c r="G322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -7867,9 +6907,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Decision-First Mode.</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr"/>
-      <c r="F323" t="inlineStr"/>
-      <c r="G323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -7890,9 +6927,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional L1/L2 Market Data.</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -7913,9 +6947,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Reference Data Registry.</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr"/>
-      <c r="F325" t="inlineStr"/>
-      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -7936,9 +6967,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Spot &amp; Derivatives Coverage.</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr"/>
-      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -7959,9 +6987,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DeFi Market Data.</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -7982,9 +7007,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Depth &amp; Liquidity Intelligence.</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -8005,9 +7027,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Fair Market Value Pricing.</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr"/>
-      <c r="G329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -8028,9 +7047,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Best Execution Pricing.</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
-      <c r="G330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -8051,9 +7067,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=trade_simulator.simulate_spot_trade; production=market_context.probe_price_sources (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr"/>
-      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -8074,9 +7087,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=ETF Reference Rates / iNAV.</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
-      <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -8097,9 +7107,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Commodity / TradFi Reference Rates.</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
-      <c r="G333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -8120,9 +7127,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Indices.</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
-      <c r="G334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -8143,9 +7147,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Risk Analytics.</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr"/>
-      <c r="G335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -8166,9 +7167,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Derivatives Listing Analytics.</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -8189,9 +7187,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Surveillance.</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr"/>
-      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -8212,9 +7207,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AML/CFT On-Chain Monitoring.</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
-      <c r="G338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -8235,9 +7227,6 @@
           <t>مبني جزئيًا — PRODUCTION-ALIGNED — Option A; PRODUCTION-ALIGNED: explicit_option_a binding verified live via cap646.runtime.execute_capability; backend=cap646.data_spine.data_quality_pipeline_report; surface=data_quality_pipeline; proof=OPTION_A_PRODUCTION_PROOF.json.</t>
         </is>
       </c>
-      <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
-      <c r="G339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -8258,9 +7247,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.apply_opportunity_filter_70; production=data_provenance_score.compute_data_provenance_score (capability_keyword).</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -8281,9 +7267,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Real-Time REST/gRPC Streaming.</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr"/>
-      <c r="G341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -8304,9 +7287,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Data Archive.</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
-      <c r="G342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -8327,9 +7307,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Venue Quality Ranking.</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
-      <c r="G343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -8350,9 +7327,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Execution Quality Analytics.</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -8373,9 +7347,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional SLA Monitoring.</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
-      <c r="G345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -8396,9 +7367,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Institutional Decision Layer.</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
-      <c r="G346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -8419,9 +7387,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Standardized Financial Metrics.</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr"/>
-      <c r="G347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -8442,9 +7407,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Fees Intelligence.</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -8465,9 +7427,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Revenue Intelligence.</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr"/>
-      <c r="G349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -8488,9 +7447,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Token Incentives.</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
-      <c r="G350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -8511,9 +7467,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Earnings / Economic Profit Proxy.</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
-      <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -8534,9 +7487,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Active Users.</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
-      <c r="G352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -8557,9 +7507,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Core Developers.</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
-      <c r="G353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -8580,9 +7527,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Code Commits.</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
-      <c r="G354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -8603,9 +7547,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=TVL Intelligence.</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr"/>
-      <c r="G355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -8626,9 +7567,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Borrowed / Loans Outstanding.</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -8649,9 +7587,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244; production=cap646.fallbacks.resolve_dex_volume_snapshot (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
-      <c r="G357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -8672,9 +7607,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Supply.</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
-      <c r="G358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -8695,9 +7627,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Valuation Multiples.</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
-      <c r="G359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -8718,9 +7647,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Growth Metrics.</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
-      <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -8741,9 +7667,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Margins / Take Rate.</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr"/>
-      <c r="G361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -8764,9 +7687,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Project Comparables.</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -8787,9 +7707,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Sector Comparables.</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -8810,9 +7727,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Tokenized Asset Coverage.</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
-      <c r="G364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -8833,9 +7747,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Fundamental Screener.</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr"/>
-      <c r="G365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -8856,9 +7767,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Financial Statement View.</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
-      <c r="G366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -8879,9 +7787,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Data Methodology Registry.</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
-      <c r="G367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -8902,9 +7807,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Source Data Provenance.</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -8925,9 +7827,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API / Data Export.</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
-      <c r="G369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -8948,9 +7847,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Fundamental Decision Intelligence.</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr"/>
-      <c r="F370" t="inlineStr"/>
-      <c r="G370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -8971,9 +7867,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=SQL On-Chain Query Workspace.</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr"/>
-      <c r="F371" t="inlineStr"/>
-      <c r="G371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -8994,9 +7887,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Curated Data Models.</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -9017,9 +7907,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Decoded Smart Contract Tables.</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -9040,9 +7927,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Chain Data Warehouse.</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr"/>
-      <c r="G374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -9063,9 +7947,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Visualization Builder.</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
-      <c r="G375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -9086,9 +7967,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Dashboard Builder.</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -9109,9 +7987,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Public Dashboard Sharing.</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr"/>
-      <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -9132,9 +8007,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Community Discovery.</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr"/>
-      <c r="G378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -9155,9 +8027,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=exchange_currency_status.deposit_currencies_open; production=security_posture.security_posture_report (track_default).</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -9178,9 +8047,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.arbitrage_portfolio_ux_layer.analyze_liquidity_capacity_189; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
-      <c r="G380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -9201,9 +8067,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=exchange_currency_status.deposit_currencies_open; production=cap646.fallbacks.resolve_gas_usd (capability_keyword).</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr"/>
-      <c r="G381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -9224,9 +8087,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=exchange_currency_status.withdrawal_currencies_closed; production=data_provenance_score.compute_data_provenance_score (track_default).</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
-      <c r="G382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -9247,9 +8107,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=heroes_quality.heroes_quality_manifest; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
-      <c r="G383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -9270,9 +8127,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=BI Connectors.</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr"/>
-      <c r="G384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -9293,9 +8147,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=MCP for AI Agents.</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr"/>
-      <c r="F385" t="inlineStr"/>
-      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -9316,9 +8167,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Prompt-to-SQL Agent.</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr"/>
-      <c r="G386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -9339,9 +8187,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Dashboard-from-Prompt.</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -9362,9 +8207,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Scheduled Queries.</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -9385,9 +8227,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Alerts from Query Results.</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr"/>
-      <c r="G389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -9408,9 +8247,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Data Lineage.</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -9431,9 +8267,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.whales_institutional_layer.build_exchange_health_80; production=blackdark.canonical.layer.get_canonical_layer (track_default).</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr"/>
-      <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -9454,9 +8287,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=White-Label Embedded Analytics.</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr"/>
-      <c r="F392" t="inlineStr"/>
-      <c r="G392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -9477,9 +8307,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Domain Decision Layer.</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -9500,9 +8327,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=data_sources_registry.registry_summary; production=bd_platform.onchain_hub.dexscreener_pairs (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
-      <c r="G394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -9523,9 +8347,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Chain TVL Comparison.</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr"/>
-      <c r="G395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -9546,9 +8367,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Directory.</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr"/>
-      <c r="G396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -9569,9 +8387,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.news_classifier.coindesk_feed; production=cap646.fallbacks.resolve_gas_usd (capability_keyword).</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
-      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -9592,9 +8407,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DEX Volume.</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -9615,9 +8427,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Perps Volume.</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
-      <c r="G399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -9638,9 +8447,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Volume.</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
-      <c r="G400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -9661,9 +8467,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoins Intelligence.</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr"/>
-      <c r="F401" t="inlineStr"/>
-      <c r="G401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -9679,14 +8482,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Bridges Intelligence.</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr"/>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -9702,14 +8502,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Yields Screener.</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr"/>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -9725,14 +8522,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Yield History.</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
-      <c r="G404" t="inlineStr"/>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -9748,14 +8542,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Borrowing Rates.</t>
-        </is>
-      </c>
-      <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr"/>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -9771,14 +8562,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquid Staking Intelligence.</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr"/>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -9794,14 +8582,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=RWA Intelligence.</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr"/>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr"/>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -9817,14 +8602,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Raises / Funding Rounds.</t>
-        </is>
-      </c>
-      <c r="E408" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
-      <c r="G408" t="inlineStr"/>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -9840,14 +8622,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Investor Profiles.</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
-      <c r="G409" t="inlineStr"/>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -9863,14 +8642,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.quicktake_feed.quicktake_feed_status_409; production=bd_platform.token_unlocks.unlock_calendar (capability_keyword).</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
-      <c r="G410" t="inlineStr"/>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -9886,14 +8662,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Treasury Intelligence.</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr"/>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -9909,14 +8682,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Airdrop / Incentive Intelligence.</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr"/>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -9932,14 +8702,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Capital Formation Radar.</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr"/>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -9955,14 +8722,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DeFi Opportunity Screener.</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr"/>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -9978,14 +8742,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DeFi Risk Passport.</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr"/>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -10001,14 +8762,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Aggregation Layer.</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr"/>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -10024,14 +8782,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-DeFi Decision Intelligence.</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr"/>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -10047,14 +8802,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Chain Fundamentals.</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr"/>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -10070,14 +8822,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Fundamentals.</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr"/>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -10093,14 +8842,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Intelligence.</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr"/>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -10116,14 +8862,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Activity Breakdown.</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr"/>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -10139,14 +8882,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Developer Activity.</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr"/>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -10162,14 +8902,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Sector/Ecosystem Comparables.</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr"/>
-      <c r="G423" t="inlineStr"/>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -10185,14 +8922,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Equities + Crypto Research.</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr"/>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -10208,14 +8942,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Consensus Estimates.</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr"/>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -10231,14 +8962,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI Analyst.</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr"/>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -10254,14 +8982,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Thesis Research Workspace.</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
-      <c r="G427" t="inlineStr"/>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -10277,14 +9002,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Comparable Company / Protocol Analysis.</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
-      <c r="G428" t="inlineStr"/>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -10300,14 +9022,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Excel / Sheets Integration.</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr"/>
-      <c r="F429" t="inlineStr"/>
-      <c r="G429" t="inlineStr"/>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -10323,14 +9042,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Data Platform.</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
-      <c r="G430" t="inlineStr"/>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -10346,14 +9062,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Research Templates.</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -10369,14 +9082,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Dashboards.</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr"/>
-      <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr"/>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -10392,14 +9102,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Payment Intelligence.</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr"/>
-      <c r="G433" t="inlineStr"/>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -10415,14 +9122,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=On-Chain Usage Intelligence.</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr"/>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -10438,14 +9142,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Revenue / Fees / Economic Activity.</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr"/>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -10461,14 +9162,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Research Copilot.</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr"/>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr"/>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -10484,14 +9182,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Investment Thesis Scoring.</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr"/>
-      <c r="F437" t="inlineStr"/>
-      <c r="G437" t="inlineStr"/>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -10507,14 +9202,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.correlation_mindshare.compute_mindshare_correlation_288; production=bd_platform.onchain_hub.defillama_raises (capability_keyword).</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr"/>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -10530,14 +9222,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Lending Market Risk.</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr"/>
-      <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr"/>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -10553,14 +9242,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Collateral Risk.</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr"/>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -10576,14 +9262,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Risk.</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -10599,14 +9282,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.intelligence_analysis_layer.stat_arb_insight_155; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr"/>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -10622,14 +9302,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidity Risk.</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
-      <c r="G443" t="inlineStr"/>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -10645,14 +9322,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Exploit Intelligence.</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
-      <c r="G444" t="inlineStr"/>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -10668,14 +9342,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Risk Intelligence.</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr"/>
-      <c r="G445" t="inlineStr"/>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -10691,14 +9362,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DeFi Strategy Risk.</t>
-        </is>
-      </c>
-      <c r="E446" t="inlineStr"/>
-      <c r="F446" t="inlineStr"/>
-      <c r="G446" t="inlineStr"/>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -10714,14 +9382,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Real-Time Risk Alerts.</t>
-        </is>
-      </c>
-      <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr"/>
-      <c r="G447" t="inlineStr"/>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -10737,14 +9402,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=DAO Treasury Risk.</t>
-        </is>
-      </c>
-      <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
-      <c r="G448" t="inlineStr"/>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -10760,14 +9422,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional Risk API.</t>
-        </is>
-      </c>
-      <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr"/>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -10783,14 +9442,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Curated On-Chain Dashboards.</t>
-        </is>
-      </c>
-      <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -10806,14 +9462,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Narrative-Driven Research.</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr"/>
-      <c r="F451" t="inlineStr"/>
-      <c r="G451" t="inlineStr"/>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -10829,14 +9482,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Dominance.</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
-      <c r="G452" t="inlineStr"/>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -10852,14 +9502,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Aave Multi-Chain Analytics.</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr"/>
-      <c r="F453" t="inlineStr"/>
-      <c r="G453" t="inlineStr"/>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -10875,14 +9522,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Risk Curation.</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr"/>
-      <c r="F454" t="inlineStr"/>
-      <c r="G454" t="inlineStr"/>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -10898,14 +9542,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Capital Protection Controls.</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr"/>
-      <c r="F455" t="inlineStr"/>
-      <c r="G455" t="inlineStr"/>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -10921,14 +9562,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stress Testing.</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr"/>
-      <c r="G456" t="inlineStr"/>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -10944,14 +9582,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Protocol Contagion.</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr"/>
-      <c r="F457" t="inlineStr"/>
-      <c r="G457" t="inlineStr"/>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -10967,14 +9602,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Protocol Risk Passport.</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr"/>
-      <c r="F458" t="inlineStr"/>
-      <c r="G458" t="inlineStr"/>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -10990,14 +9622,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.whales_institutional_layer.build_methodology_docs_86; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr"/>
-      <c r="F459" t="inlineStr"/>
-      <c r="G459" t="inlineStr"/>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -11013,14 +9642,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Network Data Pro Metrics.</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr"/>
-      <c r="F460" t="inlineStr"/>
-      <c r="G460" t="inlineStr"/>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -11036,14 +9662,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Atlas Blockchain Search.</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr"/>
-      <c r="F461" t="inlineStr"/>
-      <c r="G461" t="inlineStr"/>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -11059,14 +9682,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Address/Balance Search.</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr"/>
-      <c r="F462" t="inlineStr"/>
-      <c r="G462" t="inlineStr"/>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -11082,14 +9702,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Transaction Search.</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr"/>
-      <c r="F463" t="inlineStr"/>
-      <c r="G463" t="inlineStr"/>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -11105,14 +9722,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Block Search.</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr"/>
-      <c r="F464" t="inlineStr"/>
-      <c r="G464" t="inlineStr"/>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -11128,14 +9742,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Balance Updates.</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr"/>
-      <c r="F465" t="inlineStr"/>
-      <c r="G465" t="inlineStr"/>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -11151,14 +9762,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Stablecoin Network Metrics.</t>
-        </is>
-      </c>
-      <c r="E466" t="inlineStr"/>
-      <c r="F466" t="inlineStr"/>
-      <c r="G466" t="inlineStr"/>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -11174,14 +9782,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Data Feed.</t>
-        </is>
-      </c>
-      <c r="E467" t="inlineStr"/>
-      <c r="F467" t="inlineStr"/>
-      <c r="G467" t="inlineStr"/>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -11197,14 +9802,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Data Pro.</t>
-        </is>
-      </c>
-      <c r="E468" t="inlineStr"/>
-      <c r="F468" t="inlineStr"/>
-      <c r="G468" t="inlineStr"/>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -11220,14 +9822,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Reference Rates.</t>
-        </is>
-      </c>
-      <c r="E469" t="inlineStr"/>
-      <c r="F469" t="inlineStr"/>
-      <c r="G469" t="inlineStr"/>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -11243,14 +9842,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Indexes.</t>
-        </is>
-      </c>
-      <c r="E470" t="inlineStr"/>
-      <c r="F470" t="inlineStr"/>
-      <c r="G470" t="inlineStr"/>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -11266,14 +9862,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Realized Metrics.</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr"/>
-      <c r="F471" t="inlineStr"/>
-      <c r="G471" t="inlineStr"/>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -11289,14 +9882,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Supply Metrics.</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr"/>
-      <c r="F472" t="inlineStr"/>
-      <c r="G472" t="inlineStr"/>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -11312,14 +9902,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Mining/Validator Metrics.</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr"/>
-      <c r="F473" t="inlineStr"/>
-      <c r="G473" t="inlineStr"/>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -11335,14 +9922,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Fee Metrics.</t>
-        </is>
-      </c>
-      <c r="E474" t="inlineStr"/>
-      <c r="F474" t="inlineStr"/>
-      <c r="G474" t="inlineStr"/>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -11358,14 +9942,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Activity Metrics.</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr"/>
-      <c r="F475" t="inlineStr"/>
-      <c r="G475" t="inlineStr"/>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -11381,14 +9962,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Custom Metric Workbench.</t>
-        </is>
-      </c>
-      <c r="E476" t="inlineStr"/>
-      <c r="F476" t="inlineStr"/>
-      <c r="G476" t="inlineStr"/>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -11404,14 +9982,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Community Charts/API.</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr"/>
-      <c r="F477" t="inlineStr"/>
-      <c r="G477" t="inlineStr"/>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -11427,14 +10002,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market + Network Join.</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr"/>
-      <c r="F478" t="inlineStr"/>
-      <c r="G478" t="inlineStr"/>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -11450,14 +10022,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Data Quality Methodologies.</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr"/>
-      <c r="F479" t="inlineStr"/>
-      <c r="G479" t="inlineStr"/>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -11473,14 +10042,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Research Dataset.</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
-      <c r="G480" t="inlineStr"/>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -11496,14 +10062,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional APIs.</t>
-        </is>
-      </c>
-      <c r="E481" t="inlineStr"/>
-      <c r="F481" t="inlineStr"/>
-      <c r="G481" t="inlineStr"/>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -11519,14 +10082,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Network Decision Intelligence.</t>
-        </is>
-      </c>
-      <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
-      <c r="G482" t="inlineStr"/>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -11542,14 +10102,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional Trade Data.</t>
-        </is>
-      </c>
-      <c r="E483" t="inlineStr"/>
-      <c r="F483" t="inlineStr"/>
-      <c r="G483" t="inlineStr"/>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -11565,14 +10122,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Order Book Data.</t>
-        </is>
-      </c>
-      <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
-      <c r="G484" t="inlineStr"/>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -11588,14 +10142,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=OHLCV Data.</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
-      <c r="G485" t="inlineStr"/>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -11611,14 +10162,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Derivatives Data.</t>
-        </is>
-      </c>
-      <c r="E486" t="inlineStr"/>
-      <c r="F486" t="inlineStr"/>
-      <c r="G486" t="inlineStr"/>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -11634,14 +10182,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Open Interest Data.</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr"/>
-      <c r="F487" t="inlineStr"/>
-      <c r="G487" t="inlineStr"/>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -11657,14 +10202,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Funding Rate Data.</t>
-        </is>
-      </c>
-      <c r="E488" t="inlineStr"/>
-      <c r="F488" t="inlineStr"/>
-      <c r="G488" t="inlineStr"/>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -11680,14 +10222,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Index Data.</t>
-        </is>
-      </c>
-      <c r="E489" t="inlineStr"/>
-      <c r="F489" t="inlineStr"/>
-      <c r="G489" t="inlineStr"/>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -11703,14 +10242,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Reference Pricing.</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr"/>
-      <c r="F490" t="inlineStr"/>
-      <c r="G490" t="inlineStr"/>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -11726,14 +10262,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Exchange Metadata.</t>
-        </is>
-      </c>
-      <c r="E491" t="inlineStr"/>
-      <c r="F491" t="inlineStr"/>
-      <c r="G491" t="inlineStr"/>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -11749,14 +10282,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Asset Metadata.</t>
-        </is>
-      </c>
-      <c r="E492" t="inlineStr"/>
-      <c r="F492" t="inlineStr"/>
-      <c r="G492" t="inlineStr"/>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -11772,14 +10302,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Market Archive.</t>
-        </is>
-      </c>
-      <c r="E493" t="inlineStr"/>
-      <c r="F493" t="inlineStr"/>
-      <c r="G493" t="inlineStr"/>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -11795,14 +10322,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Real-Time Streams.</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr"/>
-      <c r="F494" t="inlineStr"/>
-      <c r="G494" t="inlineStr"/>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -11818,14 +10342,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Aggregates.</t>
-        </is>
-      </c>
-      <c r="E495" t="inlineStr"/>
-      <c r="F495" t="inlineStr"/>
-      <c r="G495" t="inlineStr"/>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -11841,14 +10362,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidity Analytics.</t>
-        </is>
-      </c>
-      <c r="E496" t="inlineStr"/>
-      <c r="F496" t="inlineStr"/>
-      <c r="G496" t="inlineStr"/>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -11864,14 +10382,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Volatility Analytics.</t>
-        </is>
-      </c>
-      <c r="E497" t="inlineStr"/>
-      <c r="F497" t="inlineStr"/>
-      <c r="G497" t="inlineStr"/>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -11887,14 +10402,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Cap / Supply.</t>
-        </is>
-      </c>
-      <c r="E498" t="inlineStr"/>
-      <c r="F498" t="inlineStr"/>
-      <c r="G498" t="inlineStr"/>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -11910,14 +10422,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=ETF / ETP Data.</t>
-        </is>
-      </c>
-      <c r="E499" t="inlineStr"/>
-      <c r="F499" t="inlineStr"/>
-      <c r="G499" t="inlineStr"/>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -11933,14 +10442,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Coverage Registry.</t>
-        </is>
-      </c>
-      <c r="E500" t="inlineStr"/>
-      <c r="F500" t="inlineStr"/>
-      <c r="G500" t="inlineStr"/>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -11956,14 +10462,11 @@
           <t>قدرة داخلية</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>مبني جزئيًا — PRODUCTION-ALIGNED — Option A; PRODUCTION-ALIGNED: explicit_option_a binding verified live via cap646.runtime.execute_capability; backend=cap646.data_spine.normalization_report; surface=data_quality_normalization; proof=OPTION_A_PRODUCTION_PROOF.json.</t>
-        </is>
-      </c>
-      <c r="E501" t="inlineStr"/>
-      <c r="F501" t="inlineStr"/>
-      <c r="G501" t="inlineStr"/>
+      <c r="D501" s="2" t="inlineStr">
+        <is>
+          <t>مبني جزئيًا</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -11984,9 +10487,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional Delivery.</t>
         </is>
       </c>
-      <c r="E502" t="inlineStr"/>
-      <c r="F502" t="inlineStr"/>
-      <c r="G502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -12007,9 +10507,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Benchmark Administration Metadata.</t>
         </is>
       </c>
-      <c r="E503" t="inlineStr"/>
-      <c r="F503" t="inlineStr"/>
-      <c r="G503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -12030,9 +10527,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Data Intelligence.</t>
         </is>
       </c>
-      <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr"/>
-      <c r="G504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -12053,9 +10547,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Unified Exchange Connector Layer.</t>
         </is>
       </c>
-      <c r="E505" t="inlineStr"/>
-      <c r="F505" t="inlineStr"/>
-      <c r="G505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -12076,9 +10567,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Tick Trade Data.</t>
         </is>
       </c>
-      <c r="E506" t="inlineStr"/>
-      <c r="F506" t="inlineStr"/>
-      <c r="G506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -12099,9 +10587,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Quote Data.</t>
         </is>
       </c>
-      <c r="E507" t="inlineStr"/>
-      <c r="F507" t="inlineStr"/>
-      <c r="G507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -12122,9 +10607,6 @@
           <t>مبني جزئيًا — PRODUCTION-ALIGNED — Option A; PRODUCTION-ALIGNED: explicit_option_a binding verified live via cap646.runtime.execute_capability; backend=cap646.fallbacks.resolve_ohlcv_closes; surface=ohlcv; proof=OPTION_A_PRODUCTION_PROOF.json.</t>
         </is>
       </c>
-      <c r="E508" t="inlineStr"/>
-      <c r="F508" t="inlineStr"/>
-      <c r="G508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -12145,9 +10627,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=L1 Order Book.</t>
         </is>
       </c>
-      <c r="E509" t="inlineStr"/>
-      <c r="F509" t="inlineStr"/>
-      <c r="G509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -12168,9 +10647,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=L2 Order Book.</t>
         </is>
       </c>
-      <c r="E510" t="inlineStr"/>
-      <c r="F510" t="inlineStr"/>
-      <c r="G510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -12191,9 +10667,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=L3 Order Book.</t>
         </is>
       </c>
-      <c r="E511" t="inlineStr"/>
-      <c r="F511" t="inlineStr"/>
-      <c r="G511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -12214,9 +10687,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Market Data.</t>
         </is>
       </c>
-      <c r="E512" t="inlineStr"/>
-      <c r="F512" t="inlineStr"/>
-      <c r="G512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -12237,9 +10707,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Funding / OI / Liquidation Metrics.</t>
         </is>
       </c>
-      <c r="E513" t="inlineStr"/>
-      <c r="F513" t="inlineStr"/>
-      <c r="G513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -12260,9 +10727,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Asset &amp; Symbol Metadata.</t>
         </is>
       </c>
-      <c r="E514" t="inlineStr"/>
-      <c r="F514" t="inlineStr"/>
-      <c r="G514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -12283,9 +10747,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Flat Files.</t>
         </is>
       </c>
-      <c r="E515" t="inlineStr"/>
-      <c r="F515" t="inlineStr"/>
-      <c r="G515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -12306,9 +10767,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=REST API.</t>
         </is>
       </c>
-      <c r="E516" t="inlineStr"/>
-      <c r="F516" t="inlineStr"/>
-      <c r="G516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -12329,9 +10787,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=WebSocket Streaming.</t>
         </is>
       </c>
-      <c r="E517" t="inlineStr"/>
-      <c r="F517" t="inlineStr"/>
-      <c r="G517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -12352,9 +10807,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=comparison_engine.run_comparison_engine; production=data_provenance_score.compute_data_provenance_score (track_default).</t>
         </is>
       </c>
-      <c r="E518" t="inlineStr"/>
-      <c r="F518" t="inlineStr"/>
-      <c r="G518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -12375,9 +10827,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=MCP for AI.</t>
         </is>
       </c>
-      <c r="E519" t="inlineStr"/>
-      <c r="F519" t="inlineStr"/>
-      <c r="G519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -12398,9 +10847,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Exchange Rates / VWAP.</t>
         </is>
       </c>
-      <c r="E520" t="inlineStr"/>
-      <c r="F520" t="inlineStr"/>
-      <c r="G520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -12421,9 +10867,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Indexes.</t>
         </is>
       </c>
-      <c r="E521" t="inlineStr"/>
-      <c r="F521" t="inlineStr"/>
-      <c r="G521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -12444,9 +10887,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Volatility Index.</t>
         </is>
       </c>
-      <c r="E522" t="inlineStr"/>
-      <c r="F522" t="inlineStr"/>
-      <c r="G522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -12467,9 +10907,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=EMS Integration Boundary.</t>
         </is>
       </c>
-      <c r="E523" t="inlineStr"/>
-      <c r="F523" t="inlineStr"/>
-      <c r="G523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -12490,9 +10927,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Data Health / SLA Monitoring.</t>
         </is>
       </c>
-      <c r="E524" t="inlineStr"/>
-      <c r="F524" t="inlineStr"/>
-      <c r="G524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -12513,9 +10947,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Symbol Mapping Engine.</t>
         </is>
       </c>
-      <c r="E525" t="inlineStr"/>
-      <c r="F525" t="inlineStr"/>
-      <c r="G525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -12536,9 +10967,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.pro_trader_layer.run_backtest_74; production=data_provenance_score.compute_data_provenance_score (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E526" t="inlineStr"/>
-      <c r="F526" t="inlineStr"/>
-      <c r="G526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -12559,9 +10987,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI Market Data Grounding Layer.</t>
         </is>
       </c>
-      <c r="E527" t="inlineStr"/>
-      <c r="F527" t="inlineStr"/>
-      <c r="G527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -12582,9 +11007,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Heatmap.</t>
         </is>
       </c>
-      <c r="E528" t="inlineStr"/>
-      <c r="F528" t="inlineStr"/>
-      <c r="G528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -12605,9 +11027,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — SPLIT_BRAIN_ROUTING; SPLIT-BRAIN-UNVERIFIED: pdf_registry/audit binding ≠ production backend_registry; audit function not executed on production path GET /api/cap646/{id}; production serves alternate backend — VERIFIED-DEEP claim suspended pending explicit registry wiring. audit=bd_platform.market_rankings.market_rankings; production=bd_platform.liquidation_radar.liquidation_radar (capability_keyword).</t>
         </is>
       </c>
-      <c r="E529" t="inlineStr"/>
-      <c r="F529" t="inlineStr"/>
-      <c r="G529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -12628,9 +11047,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Cascade Model.</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr"/>
-      <c r="F530" t="inlineStr"/>
-      <c r="G530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -12651,9 +11067,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Global Liquidation Metrics.</t>
         </is>
       </c>
-      <c r="E531" t="inlineStr"/>
-      <c r="F531" t="inlineStr"/>
-      <c r="G531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -12674,9 +11087,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Open Interest.</t>
         </is>
       </c>
-      <c r="E532" t="inlineStr"/>
-      <c r="F532" t="inlineStr"/>
-      <c r="G532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -12697,9 +11107,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Funding Rates.</t>
         </is>
       </c>
-      <c r="E533" t="inlineStr"/>
-      <c r="F533" t="inlineStr"/>
-      <c r="G533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -12720,9 +11127,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Order Flow Intelligence.</t>
         </is>
       </c>
-      <c r="E534" t="inlineStr"/>
-      <c r="F534" t="inlineStr"/>
-      <c r="G534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -12743,9 +11147,6 @@
           <t>مبني جزئيًا — PRODUCTION-ALIGNED — Option A; PRODUCTION-ALIGNED: explicit_option_a binding verified live via cap646.runtime.execute_capability; backend=cap646.data_spine.bucketed_cvd_report; surface=bucketed_cvd; proof=OPTION_A_PRODUCTION_PROOF.json.</t>
         </is>
       </c>
-      <c r="E535" t="inlineStr"/>
-      <c r="F535" t="inlineStr"/>
-      <c r="G535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -12766,9 +11167,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Whale vs Retail Flow.</t>
         </is>
       </c>
-      <c r="E536" t="inlineStr"/>
-      <c r="F536" t="inlineStr"/>
-      <c r="G536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -12789,9 +11187,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Slippage Intelligence.</t>
         </is>
       </c>
-      <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr"/>
-      <c r="G537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -12812,9 +11207,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Global Order Book Metrics.</t>
         </is>
       </c>
-      <c r="E538" t="inlineStr"/>
-      <c r="F538" t="inlineStr"/>
-      <c r="G538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -12835,9 +11227,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Order Book Imbalance.</t>
         </is>
       </c>
-      <c r="E539" t="inlineStr"/>
-      <c r="F539" t="inlineStr"/>
-      <c r="G539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -12858,9 +11247,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidity Zones.</t>
         </is>
       </c>
-      <c r="E540" t="inlineStr"/>
-      <c r="F540" t="inlineStr"/>
-      <c r="G540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -12881,9 +11267,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Bot Activity Detection.</t>
         </is>
       </c>
-      <c r="E541" t="inlineStr"/>
-      <c r="F541" t="inlineStr"/>
-      <c r="G541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -12904,9 +11287,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Market Positioning.</t>
         </is>
       </c>
-      <c r="E542" t="inlineStr"/>
-      <c r="F542" t="inlineStr"/>
-      <c r="G542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -12927,9 +11307,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Pressure Score.</t>
         </is>
       </c>
-      <c r="E543" t="inlineStr"/>
-      <c r="F543" t="inlineStr"/>
-      <c r="G543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -12950,9 +11327,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Orderflow Anomaly Detection.</t>
         </is>
       </c>
-      <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr"/>
-      <c r="G544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -12973,9 +11347,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Indicator Platform.</t>
         </is>
       </c>
-      <c r="E545" t="inlineStr"/>
-      <c r="F545" t="inlineStr"/>
-      <c r="G545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -12996,9 +11367,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Trader Cohort Intelligence.</t>
         </is>
       </c>
-      <c r="E546" t="inlineStr"/>
-      <c r="F546" t="inlineStr"/>
-      <c r="G546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -13019,9 +11387,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Derivatives Decision Intelligence.</t>
         </is>
       </c>
-      <c r="E547" t="inlineStr"/>
-      <c r="F547" t="inlineStr"/>
-      <c r="G547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -13042,9 +11407,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=High-Resolution Multi-Pane Charts.</t>
         </is>
       </c>
-      <c r="E548" t="inlineStr"/>
-      <c r="F548" t="inlineStr"/>
-      <c r="G548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -13065,9 +11427,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Derivatives Dashboard.</t>
         </is>
       </c>
-      <c r="E549" t="inlineStr"/>
-      <c r="F549" t="inlineStr"/>
-      <c r="G549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -13088,9 +11447,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Funding Rate Intelligence.</t>
         </is>
       </c>
-      <c r="E550" t="inlineStr"/>
-      <c r="F550" t="inlineStr"/>
-      <c r="G550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -13111,9 +11467,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Open Interest Intelligence.</t>
         </is>
       </c>
-      <c r="E551" t="inlineStr"/>
-      <c r="F551" t="inlineStr"/>
-      <c r="G551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -13134,9 +11487,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Liquidation Intelligence.</t>
         </is>
       </c>
-      <c r="E552" t="inlineStr"/>
-      <c r="F552" t="inlineStr"/>
-      <c r="G552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -13157,9 +11507,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Futures Volume.</t>
         </is>
       </c>
-      <c r="E553" t="inlineStr"/>
-      <c r="F553" t="inlineStr"/>
-      <c r="G553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -13180,9 +11527,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Basis Intelligence.</t>
         </is>
       </c>
-      <c r="E554" t="inlineStr"/>
-      <c r="F554" t="inlineStr"/>
-      <c r="G554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -13203,9 +11547,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Spot Market Data.</t>
         </is>
       </c>
-      <c r="E555" t="inlineStr"/>
-      <c r="F555" t="inlineStr"/>
-      <c r="G555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -13226,9 +11567,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Analytics.</t>
         </is>
       </c>
-      <c r="E556" t="inlineStr"/>
-      <c r="F556" t="inlineStr"/>
-      <c r="G556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -13249,9 +11587,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options IV Surface.</t>
         </is>
       </c>
-      <c r="E557" t="inlineStr"/>
-      <c r="F557" t="inlineStr"/>
-      <c r="G557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -13272,9 +11607,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Skew.</t>
         </is>
       </c>
-      <c r="E558" t="inlineStr"/>
-      <c r="F558" t="inlineStr"/>
-      <c r="G558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -13295,9 +11627,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Options Term Structure.</t>
         </is>
       </c>
-      <c r="E559" t="inlineStr"/>
-      <c r="F559" t="inlineStr"/>
-      <c r="G559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -13318,9 +11647,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=TradFi Context.</t>
         </is>
       </c>
-      <c r="E560" t="inlineStr"/>
-      <c r="F560" t="inlineStr"/>
-      <c r="G560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -13341,9 +11667,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Multi-Indicator Workspace.</t>
         </is>
       </c>
-      <c r="E561" t="inlineStr"/>
-      <c r="F561" t="inlineStr"/>
-      <c r="G561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -13364,9 +11687,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Real-Time Prices.</t>
         </is>
       </c>
-      <c r="E562" t="inlineStr"/>
-      <c r="F562" t="inlineStr"/>
-      <c r="G562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -13387,9 +11707,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Historical Data.</t>
         </is>
       </c>
-      <c r="E563" t="inlineStr"/>
-      <c r="F563" t="inlineStr"/>
-      <c r="G563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -13410,9 +11727,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API Data Access.</t>
         </is>
       </c>
-      <c r="E564" t="inlineStr"/>
-      <c r="F564" t="inlineStr"/>
-      <c r="G564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -13433,9 +11747,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=News Context.</t>
         </is>
       </c>
-      <c r="E565" t="inlineStr"/>
-      <c r="F565" t="inlineStr"/>
-      <c r="G565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -13456,9 +11767,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Asset Correlation.</t>
         </is>
       </c>
-      <c r="E566" t="inlineStr"/>
-      <c r="F566" t="inlineStr"/>
-      <c r="G566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -13479,9 +11787,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Derivatives Regime Engine.</t>
         </is>
       </c>
-      <c r="E567" t="inlineStr"/>
-      <c r="F567" t="inlineStr"/>
-      <c r="G567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -13502,9 +11807,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Cross-Market Decision Intelligence.</t>
         </is>
       </c>
-      <c r="E568" t="inlineStr"/>
-      <c r="F568" t="inlineStr"/>
-      <c r="G568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -13525,9 +11827,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Security_First_Architecture.</t>
         </is>
       </c>
-      <c r="E569" t="inlineStr"/>
-      <c r="F569" t="inlineStr"/>
-      <c r="G569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -13548,9 +11847,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API_Security_Encryption.</t>
         </is>
       </c>
-      <c r="E570" t="inlineStr"/>
-      <c r="F570" t="inlineStr"/>
-      <c r="G570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -13571,9 +11867,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=High_Availability_Architecture.</t>
         </is>
       </c>
-      <c r="E571" t="inlineStr"/>
-      <c r="F571" t="inlineStr"/>
-      <c r="G571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -13594,9 +11887,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Infrastructure_Uptime_Shield.</t>
         </is>
       </c>
-      <c r="E572" t="inlineStr"/>
-      <c r="F572" t="inlineStr"/>
-      <c r="G572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -13617,9 +11907,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional_Data_Architecture.</t>
         </is>
       </c>
-      <c r="E573" t="inlineStr"/>
-      <c r="F573" t="inlineStr"/>
-      <c r="G573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -13640,9 +11927,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Flexible_Connector_Microservice.</t>
         </is>
       </c>
-      <c r="E574" t="inlineStr"/>
-      <c r="F574" t="inlineStr"/>
-      <c r="G574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -13663,9 +11947,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Institutional_API_Gateway.</t>
         </is>
       </c>
-      <c r="E575" t="inlineStr"/>
-      <c r="F575" t="inlineStr"/>
-      <c r="G575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -13686,9 +11967,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=API_Data_Pipe.</t>
         </is>
       </c>
-      <c r="E576" t="inlineStr"/>
-      <c r="F576" t="inlineStr"/>
-      <c r="G576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -13709,9 +11987,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Developer_SDK.</t>
         </is>
       </c>
-      <c r="E577" t="inlineStr"/>
-      <c r="F577" t="inlineStr"/>
-      <c r="G577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -13732,9 +12007,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Pro_Developer_Sandbox.</t>
         </is>
       </c>
-      <c r="E578" t="inlineStr"/>
-      <c r="F578" t="inlineStr"/>
-      <c r="G578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -13755,9 +12027,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.execution_rejected_layer.whale_behavior_analysis_216; production=bd_platform.portfolio_rebalancer.portfolio_snapshot (capability_keyword).</t>
         </is>
       </c>
-      <c r="E579" t="inlineStr"/>
-      <c r="F579" t="inlineStr"/>
-      <c r="G579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -13778,9 +12047,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Global_Asset_Tracker.</t>
         </is>
       </c>
-      <c r="E580" t="inlineStr"/>
-      <c r="F580" t="inlineStr"/>
-      <c r="G580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -13801,9 +12067,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Multi_Account_Sync.</t>
         </is>
       </c>
-      <c r="E581" t="inlineStr"/>
-      <c r="F581" t="inlineStr"/>
-      <c r="G581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -13824,9 +12087,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=On_Chain_Balance_Monitor.</t>
         </is>
       </c>
-      <c r="E582" t="inlineStr"/>
-      <c r="F582" t="inlineStr"/>
-      <c r="G582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -13847,9 +12107,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Profitability_Analyzer.</t>
         </is>
       </c>
-      <c r="E583" t="inlineStr"/>
-      <c r="F583" t="inlineStr"/>
-      <c r="G583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -13870,9 +12127,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Margin_Risk_Calculator.</t>
         </is>
       </c>
-      <c r="E584" t="inlineStr"/>
-      <c r="F584" t="inlineStr"/>
-      <c r="G584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -13893,9 +12147,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.news_classifier.coindesk_feed; production=risk_manager.risk_status (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E585" t="inlineStr"/>
-      <c r="F585" t="inlineStr"/>
-      <c r="G585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -13916,9 +12167,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Volatility_Scoring_System.</t>
         </is>
       </c>
-      <c r="E586" t="inlineStr"/>
-      <c r="F586" t="inlineStr"/>
-      <c r="G586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -13939,9 +12187,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Volatility_Surface_Analyzer.</t>
         </is>
       </c>
-      <c r="E587" t="inlineStr"/>
-      <c r="F587" t="inlineStr"/>
-      <c r="G587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -13962,9 +12207,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Delta_Neutral_Calculator.</t>
         </is>
       </c>
-      <c r="E588" t="inlineStr"/>
-      <c r="F588" t="inlineStr"/>
-      <c r="G588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -13985,9 +12227,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=High_Precision_Backtesting.</t>
         </is>
       </c>
-      <c r="E589" t="inlineStr"/>
-      <c r="F589" t="inlineStr"/>
-      <c r="G589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -14008,9 +12247,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Strategy_Vetting_Algorithm.</t>
         </is>
       </c>
-      <c r="E590" t="inlineStr"/>
-      <c r="F590" t="inlineStr"/>
-      <c r="G590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -14031,9 +12267,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI_Quant_Rating_Engine.</t>
         </is>
       </c>
-      <c r="E591" t="inlineStr"/>
-      <c r="F591" t="inlineStr"/>
-      <c r="G591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -14054,9 +12287,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Sentiment_Analysis_Engine.</t>
         </is>
       </c>
-      <c r="E592" t="inlineStr"/>
-      <c r="F592" t="inlineStr"/>
-      <c r="G592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -14077,9 +12307,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Social_Sentiment_Engine.</t>
         </is>
       </c>
-      <c r="E593" t="inlineStr"/>
-      <c r="F593" t="inlineStr"/>
-      <c r="G593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -14100,9 +12327,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Social_Hype_Analyzer.</t>
         </is>
       </c>
-      <c r="E594" t="inlineStr"/>
-      <c r="F594" t="inlineStr"/>
-      <c r="G594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -14123,9 +12347,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Narrative_Alert_System.</t>
         </is>
       </c>
-      <c r="E595" t="inlineStr"/>
-      <c r="F595" t="inlineStr"/>
-      <c r="G595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -14146,9 +12367,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI_Digest_Generator.</t>
         </is>
       </c>
-      <c r="E596" t="inlineStr"/>
-      <c r="F596" t="inlineStr"/>
-      <c r="G596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -14169,9 +12387,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=AI_Agent_Consultant.</t>
         </is>
       </c>
-      <c r="E597" t="inlineStr"/>
-      <c r="F597" t="inlineStr"/>
-      <c r="G597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -14192,9 +12407,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Natural_Language_Interpreter.</t>
         </is>
       </c>
-      <c r="E598" t="inlineStr"/>
-      <c r="F598" t="inlineStr"/>
-      <c r="G598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -14215,9 +12427,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Wallet_Shadowing.</t>
         </is>
       </c>
-      <c r="E599" t="inlineStr"/>
-      <c r="F599" t="inlineStr"/>
-      <c r="G599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -14238,9 +12447,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Entity_Tagging_System.</t>
         </is>
       </c>
-      <c r="E600" t="inlineStr"/>
-      <c r="F600" t="inlineStr"/>
-      <c r="G600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -14261,9 +12467,6 @@
           <t>مبني جزئيًا — DEFERRED/TEMPLATE-STUB — Option B; DEFERRED/TEMPLATE-STUB: TEMPLATE-SEED-STUB has no unique domain implementation; production already serves a generic cap646 handler. Defer until product owner assigns domain spec + acceptance tests. blocked_by=missing_domain_spec; allowed_interim=generic cap646 handler only — no VERIFIED-DEEP claim; catalog=Whale_Clustering_Engine.</t>
         </is>
       </c>
-      <c r="E601" t="inlineStr"/>
-      <c r="F601" t="inlineStr"/>
-      <c r="G601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -14284,9 +12487,6 @@
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
-      <c r="E602" t="inlineStr"/>
-      <c r="F602" t="inlineStr"/>
-      <c r="G602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -14307,9 +12507,6 @@
           <t>مبني وشغال فعليًا — acquirer_evidence_pack.build_acquirer_evidence_pack</t>
         </is>
       </c>
-      <c r="E603" t="inlineStr"/>
-      <c r="F603" t="inlineStr"/>
-      <c r="G603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -14330,9 +12527,6 @@
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.continuous_learning_status_186 via platform_api/intelligence/continuous-learning-status</t>
         </is>
       </c>
-      <c r="E604" t="inlineStr"/>
-      <c r="F604" t="inlineStr"/>
-      <c r="G604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -14353,9 +12547,6 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
-      <c r="E605" t="inlineStr"/>
-      <c r="F605" t="inlineStr"/>
-      <c r="G605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -14376,9 +12567,6 @@
           <t>مبني وشغال فعليًا — arbitrage_catalog.get_catalog</t>
         </is>
       </c>
-      <c r="E606" t="inlineStr"/>
-      <c r="F606" t="inlineStr"/>
-      <c r="G606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -14399,9 +12587,6 @@
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.withdrawal_suspension_alert_191</t>
         </is>
       </c>
-      <c r="E607" t="inlineStr"/>
-      <c r="F607" t="inlineStr"/>
-      <c r="G607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -14422,9 +12607,6 @@
           <t>مبني وشغال فعليًا — bd_platform/infra_intelligence_layer.py</t>
         </is>
       </c>
-      <c r="E608" t="inlineStr"/>
-      <c r="F608" t="inlineStr"/>
-      <c r="G608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -14445,9 +12627,6 @@
           <t>مبني وشغال فعليًا — bd_platform/derivatives_ta_research_layer.py</t>
         </is>
       </c>
-      <c r="E609" t="inlineStr"/>
-      <c r="F609" t="inlineStr"/>
-      <c r="G609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -14468,9 +12647,6 @@
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
-      <c r="E610" t="inlineStr"/>
-      <c r="F610" t="inlineStr"/>
-      <c r="G610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -14491,9 +12667,6 @@
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.build_whale_flow_visualization_180</t>
         </is>
       </c>
-      <c r="E611" t="inlineStr"/>
-      <c r="F611" t="inlineStr"/>
-      <c r="G611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -14514,9 +12687,6 @@
           <t>مبني وشغال فعليًا — bd_platform.onchain_defi_sources_layer.ingest_glassnode_metrics_205 via platform_api/oracle/on-chain/sources/glassnode</t>
         </is>
       </c>
-      <c r="E612" t="inlineStr"/>
-      <c r="F612" t="inlineStr"/>
-      <c r="G612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -14537,9 +12707,6 @@
           <t>مبني وشغال فعليًا — defi_arbitrage_engine.defi_engine_stats</t>
         </is>
       </c>
-      <c r="E613" t="inlineStr"/>
-      <c r="F613" t="inlineStr"/>
-      <c r="G613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -14560,9 +12727,6 @@
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
-      <c r="E614" t="inlineStr"/>
-      <c r="F614" t="inlineStr"/>
-      <c r="G614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -14583,9 +12747,6 @@
           <t>مبني وشغال فعليًا — bd_platform/derivatives_hub.py + liquidation_radar.py</t>
         </is>
       </c>
-      <c r="E615" t="inlineStr"/>
-      <c r="F615" t="inlineStr"/>
-      <c r="G615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -14606,9 +12767,6 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
-      <c r="E616" t="inlineStr"/>
-      <c r="F616" t="inlineStr"/>
-      <c r="G616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -14629,9 +12787,6 @@
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
-      <c r="E617" t="inlineStr"/>
-      <c r="F617" t="inlineStr"/>
-      <c r="G617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -14652,9 +12807,6 @@
           <t>مبني وشغال فعليًا — bd_platform.onchain_platform_layer.scan_flash_loan_vulnerabilities_132</t>
         </is>
       </c>
-      <c r="E618" t="inlineStr"/>
-      <c r="F618" t="inlineStr"/>
-      <c r="G618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -14675,9 +12827,6 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
-      <c r="E619" t="inlineStr"/>
-      <c r="F619" t="inlineStr"/>
-      <c r="G619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -14698,9 +12847,6 @@
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.build_kill_rate_widget_253</t>
         </is>
       </c>
-      <c r="E620" t="inlineStr"/>
-      <c r="F620" t="inlineStr"/>
-      <c r="G620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -14721,9 +12867,6 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
-      <c r="E621" t="inlineStr"/>
-      <c r="F621" t="inlineStr"/>
-      <c r="G621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -14744,9 +12887,6 @@
           <t>مبني وشغال فعليًا — bd_platform/intelligence_market_extensions_layer.py</t>
         </is>
       </c>
-      <c r="E622" t="inlineStr"/>
-      <c r="F622" t="inlineStr"/>
-      <c r="G622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -14767,9 +12907,6 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
-      <c r="E623" t="inlineStr"/>
-      <c r="F623" t="inlineStr"/>
-      <c r="G623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -14790,9 +12927,6 @@
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
-      <c r="E624" t="inlineStr"/>
-      <c r="F624" t="inlineStr"/>
-      <c r="G624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -14813,9 +12947,6 @@
           <t>مبني وشغال فعليًا — bd_platform.free_tier_capabilities.free_tier_live_ready</t>
         </is>
       </c>
-      <c r="E625" t="inlineStr"/>
-      <c r="F625" t="inlineStr"/>
-      <c r="G625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -14836,9 +12967,6 @@
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
-      <c r="E626" t="inlineStr"/>
-      <c r="F626" t="inlineStr"/>
-      <c r="G626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -14859,9 +12987,6 @@
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
-      <c r="E627" t="inlineStr"/>
-      <c r="F627" t="inlineStr"/>
-      <c r="G627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -14882,9 +13007,6 @@
           <t>مبني وشغال فعليًا — comparison_engine.py:run_comparison_engine + route /api/platform/intelligence/comparison-engine</t>
         </is>
       </c>
-      <c r="E628" t="inlineStr"/>
-      <c r="F628" t="inlineStr"/>
-      <c r="G628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -14905,9 +13027,6 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.build_heatmap_component_233 via platform_api/radar/heatmap</t>
         </is>
       </c>
-      <c r="E629" t="inlineStr"/>
-      <c r="F629" t="inlineStr"/>
-      <c r="G629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -14928,9 +13047,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_OTHER; audit=regulatory_compliance_guard.compliant_oracle_sentence; production=instant_alert_engine.engine_stats (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E630" t="inlineStr"/>
-      <c r="F630" t="inlineStr"/>
-      <c r="G630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -14951,9 +13067,6 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_ux_extensions_layer.scan_market_opportunities_238</t>
         </is>
       </c>
-      <c r="E631" t="inlineStr"/>
-      <c r="F631" t="inlineStr"/>
-      <c r="G631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -14974,9 +13087,6 @@
           <t>مبني جزئيًا</t>
         </is>
       </c>
-      <c r="E632" t="inlineStr"/>
-      <c r="F632" t="inlineStr"/>
-      <c r="G632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -14997,9 +13107,6 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
-      <c r="E633" t="inlineStr"/>
-      <c r="F633" t="inlineStr"/>
-      <c r="G633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -15020,9 +13127,6 @@
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.ingest_cointelegraph_rss_244 via platform_api/radar/news/cointelegraph</t>
         </is>
       </c>
-      <c r="E634" t="inlineStr"/>
-      <c r="F634" t="inlineStr"/>
-      <c r="G634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -15043,9 +13147,6 @@
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.list_etherscan_watchlist_246 via platform_api/oracle/on-chain/watch</t>
         </is>
       </c>
-      <c r="E635" t="inlineStr"/>
-      <c r="F635" t="inlineStr"/>
-      <c r="G635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -15066,9 +13167,6 @@
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.trad_simulator_635 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
       </c>
-      <c r="E636" t="inlineStr"/>
-      <c r="F636" t="inlineStr"/>
-      <c r="G636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -15089,9 +13187,6 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
-      <c r="E637" t="inlineStr"/>
-      <c r="F637" t="inlineStr"/>
-      <c r="G637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -15112,9 +13207,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.build_kill_rate_widget_253; production=trust_pulse.build_trust_pulse (capability_keyword).</t>
         </is>
       </c>
-      <c r="E638" t="inlineStr"/>
-      <c r="F638" t="inlineStr"/>
-      <c r="G638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -15135,9 +13227,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.build_contradiction_replay_254; production=oracle_track_record.public_track_record (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E639" t="inlineStr"/>
-      <c r="F639" t="inlineStr"/>
-      <c r="G639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -15158,9 +13247,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.committee_one_pager_status_255; production=net_edge_truth.compute_net_edge_truth (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E640" t="inlineStr"/>
-      <c r="F640" t="inlineStr"/>
-      <c r="G640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -15181,9 +13267,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.compute_half_life_clock_256; production=oracle_track_record.public_track_record (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E641" t="inlineStr"/>
-      <c r="F641" t="inlineStr"/>
-      <c r="G641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -15204,9 +13287,6 @@
           <t>مبني وشغال فعليًا — bd_platform.heroes_capability_layer.proof_arena_lite_641 + tests/test_hero_batch_01_capabilities.py</t>
         </is>
       </c>
-      <c r="E642" t="inlineStr"/>
-      <c r="F642" t="inlineStr"/>
-      <c r="G642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -15227,9 +13307,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.since_you_left_top3_258; production=data_provenance_score.compute_data_provenance_score (capability_keyword).</t>
         </is>
       </c>
-      <c r="E643" t="inlineStr"/>
-      <c r="F643" t="inlineStr"/>
-      <c r="G643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -15250,9 +13327,6 @@
           <t>مبني وشغال فعليًا — kill_rate_board.py + anti_hype_mode.py + proof_arena.py</t>
         </is>
       </c>
-      <c r="E644" t="inlineStr"/>
-      <c r="F644" t="inlineStr"/>
-      <c r="G644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -15273,9 +13347,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.security_trust_data_layer.corpus_passport_status_260; production=scale_readiness.scale_readiness_report (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E645" t="inlineStr"/>
-      <c r="F645" t="inlineStr"/>
-      <c r="G645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -15296,9 +13367,6 @@
           <t>مبني جزئيًا — SPLIT-BRAIN-UNVERIFIED — B/C/D; SPLIT-BRAIN-UNVERIFIED: REUSED/OTHER/GENERIC_HANDLER — audit binding not executed on production path; live execute_capability uses alternate backend_registry binding; VERIFIED-DEEP/REUSED-LINK claim suspended. category=SPLIT_BRAIN_REUSED; audit=bd_platform.data_sources_layer.compute_opportunity_score_150; production=security_posture.security_posture_report (gap_matrix_component).</t>
         </is>
       </c>
-      <c r="E646" t="inlineStr"/>
-      <c r="F646" t="inlineStr"/>
-      <c r="G646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -15319,9 +13387,6 @@
           <t>مبني وشغال فعليًا — bd_platform.auto_keys.parse_keys_file</t>
         </is>
       </c>
-      <c r="E647" t="inlineStr"/>
-      <c r="F647" t="inlineStr"/>
-      <c r="G647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -15342,9 +13407,6 @@
           <t>مبني وشغال فعليًا — bd_platform.advanced_ta_risk_layer.compute_volume_profile_poc_123</t>
         </is>
       </c>
-      <c r="E648" t="inlineStr"/>
-      <c r="F648" t="inlineStr"/>
-      <c r="G648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -15365,9 +13427,6 @@
           <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
-      <c r="E649" t="inlineStr"/>
-      <c r="F649" t="inlineStr"/>
-      <c r="G649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -15388,9 +13447,6 @@
           <t>مبني وشغال فعليًا — bd_platform.data_sources_layer.compute_opportunity_score_150</t>
         </is>
       </c>
-      <c r="E650" t="inlineStr"/>
-      <c r="F650" t="inlineStr"/>
-      <c r="G650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -15411,9 +13467,6 @@
           <t>مبني وشغال فعليًا — audit_registry.py + security_trust_data_layer audit_log_id_242</t>
         </is>
       </c>
-      <c r="E651" t="inlineStr"/>
-      <c r="F651" t="inlineStr"/>
-      <c r="G651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -15434,9 +13487,6 @@
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
-      <c r="E652" t="inlineStr"/>
-      <c r="F652" t="inlineStr"/>
-      <c r="G652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -15457,9 +13507,6 @@
           <t>مبني وشغال فعليًا — persona_clarity.build_persona_clarity</t>
         </is>
       </c>
-      <c r="E653" t="inlineStr"/>
-      <c r="F653" t="inlineStr"/>
-      <c r="G653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -15480,9 +13527,6 @@
           <t>مبني وشغال فعليًا — dashboard.py</t>
         </is>
       </c>
-      <c r="E654" t="inlineStr"/>
-      <c r="F654" t="inlineStr"/>
-      <c r="G654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -15503,9 +13547,6 @@
           <t>مبني وشغال فعليًا — gas_oracle.py + cap646/fallbacks resolve_gas_usd</t>
         </is>
       </c>
-      <c r="E655" t="inlineStr"/>
-      <c r="F655" t="inlineStr"/>
-      <c r="G655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -15526,9 +13567,6 @@
           <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
       </c>
-      <c r="E656" t="inlineStr"/>
-      <c r="F656" t="inlineStr"/>
-      <c r="G656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -15549,9 +13587,6 @@
           <t>مبني وشغال فعليًا — scale_readiness.scale_readiness_report</t>
         </is>
       </c>
-      <c r="E657" t="inlineStr"/>
-      <c r="F657" t="inlineStr"/>
-      <c r="G657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -15572,9 +13607,6 @@
           <t>مبني وشغال فعليًا — hot_storage.py — تحقق عميق (كان: إشارات فقط)</t>
         </is>
       </c>
-      <c r="E658" t="inlineStr"/>
-      <c r="F658" t="inlineStr"/>
-      <c r="G658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -15595,9 +13627,6 @@
           <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
-      <c r="E659" t="inlineStr"/>
-      <c r="F659" t="inlineStr"/>
-      <c r="G659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="n">
@@ -15618,9 +13647,6 @@
           <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
-      <c r="E660" t="inlineStr"/>
-      <c r="F660" t="inlineStr"/>
-      <c r="G660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="n">
@@ -15641,9 +13667,6 @@
           <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
-      <c r="E661" t="inlineStr"/>
-      <c r="F661" t="inlineStr"/>
-      <c r="G661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="n">
@@ -15664,9 +13687,6 @@
           <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 via platform_api/data-engine/streaming/status</t>
         </is>
       </c>
-      <c r="E662" t="inlineStr"/>
-      <c r="F662" t="inlineStr"/>
-      <c r="G662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="n">
@@ -15687,9 +13707,6 @@
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_exchange_health_with_counterparty_92 via platform_api/radar/exchange-health/full</t>
         </is>
       </c>
-      <c r="E663" t="inlineStr"/>
-      <c r="F663" t="inlineStr"/>
-      <c r="G663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="n">
@@ -15710,9 +13727,6 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
-      <c r="E664" t="inlineStr"/>
-      <c r="F664" t="inlineStr"/>
-      <c r="G664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="n">
@@ -15733,9 +13747,6 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
-      <c r="E665" t="inlineStr"/>
-      <c r="F665" t="inlineStr"/>
-      <c r="G665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -15756,9 +13767,6 @@
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
-      <c r="E666" t="inlineStr"/>
-      <c r="F666" t="inlineStr"/>
-      <c r="G666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="n">
@@ -15779,9 +13787,6 @@
           <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.health_score_from_holdings_67 via platform_api/portfolio/health-score</t>
         </is>
       </c>
-      <c r="E667" t="inlineStr"/>
-      <c r="F667" t="inlineStr"/>
-      <c r="G667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="n">
@@ -15802,9 +13807,6 @@
           <t>مبني وشغال فعليًا — data_provenance_score.compute_data_provenance_score</t>
         </is>
       </c>
-      <c r="E668" t="inlineStr"/>
-      <c r="F668" t="inlineStr"/>
-      <c r="G668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="n">
@@ -15825,9 +13827,6 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
-      <c r="E669" t="inlineStr"/>
-      <c r="F669" t="inlineStr"/>
-      <c r="G669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="n">
@@ -15848,9 +13847,6 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
-      <c r="E670" t="inlineStr"/>
-      <c r="F670" t="inlineStr"/>
-      <c r="G670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="n">
@@ -15871,9 +13867,6 @@
           <t>مبني وشغال فعليًا — bd_platform.institutional_b2b_layer.build_ic_report_87</t>
         </is>
       </c>
-      <c r="E671" t="inlineStr"/>
-      <c r="F671" t="inlineStr"/>
-      <c r="G671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -15894,9 +13887,6 @@
           <t>مبني وشغال فعليًا — service_bus.bus_stats</t>
         </is>
       </c>
-      <c r="E672" t="inlineStr"/>
-      <c r="F672" t="inlineStr"/>
-      <c r="G672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="n">
@@ -15917,9 +13907,6 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
-      <c r="E673" t="inlineStr"/>
-      <c r="F673" t="inlineStr"/>
-      <c r="G673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -15940,9 +13927,6 @@
           <t>مبني وشغال فعليًا — bd_platform.infra_intelligence_layer.enqueue_stream_event_96 via platform_api/data-engine/streaming/status</t>
         </is>
       </c>
-      <c r="E674" t="inlineStr"/>
-      <c r="F674" t="inlineStr"/>
-      <c r="G674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="n">
@@ -15963,9 +13947,6 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_market_extensions_layer.run_intelligence_market_extensions_e2e_217_227</t>
         </is>
       </c>
-      <c r="E675" t="inlineStr"/>
-      <c r="F675" t="inlineStr"/>
-      <c r="G675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" t="n">
@@ -15986,9 +13967,6 @@
           <t>مبني وشغال فعليًا — oracle_unified.build_full_market_context</t>
         </is>
       </c>
-      <c r="E676" t="inlineStr"/>
-      <c r="F676" t="inlineStr"/>
-      <c r="G676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="n">
@@ -16009,9 +13987,6 @@
           <t>مبني وشغال فعليًا — bd_platform.intelligence_analysis_layer.build_institutional_insight_report_163</t>
         </is>
       </c>
-      <c r="E677" t="inlineStr"/>
-      <c r="F677" t="inlineStr"/>
-      <c r="G677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="n">
@@ -16032,9 +14007,6 @@
           <t>مبني وشغال فعليًا — sentiment_manipulation_guard spoof detection</t>
         </is>
       </c>
-      <c r="E678" t="inlineStr"/>
-      <c r="F678" t="inlineStr"/>
-      <c r="G678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="n">
@@ -16055,9 +14027,6 @@
           <t>مبني وشغال فعليًا — bd_platform.risk_infrastructure_layer.run_risk_infrastructure_e2e_164_176 via platform_api/infrastructure/resilience-status</t>
         </is>
       </c>
-      <c r="E679" t="inlineStr"/>
-      <c r="F679" t="inlineStr"/>
-      <c r="G679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="n">
@@ -16078,9 +14047,6 @@
           <t>مبني وشغال فعليًا — sentiment_manipulation_guard spoof detection</t>
         </is>
       </c>
-      <c r="E680" t="inlineStr"/>
-      <c r="F680" t="inlineStr"/>
-      <c r="G680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" t="n">
@@ -16101,9 +14067,6 @@
           <t>مبني وشغال فعليًا — arbitrage_engine.build_onchain_context_safe</t>
         </is>
       </c>
-      <c r="E681" t="inlineStr"/>
-      <c r="F681" t="inlineStr"/>
-      <c r="G681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -16124,9 +14087,6 @@
           <t>مبني وشغال فعليًا — bd_platform/whales_institutional_layer.py</t>
         </is>
       </c>
-      <c r="E682" t="inlineStr"/>
-      <c r="F682" t="inlineStr"/>
-      <c r="G682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="n">
@@ -16147,9 +14107,6 @@
           <t>مبني وشغال فعليًا — bd_platform.whales_institutional_layer.build_unified_portfolio_view_81</t>
         </is>
       </c>
-      <c r="E683" t="inlineStr"/>
-      <c r="F683" t="inlineStr"/>
-      <c r="G683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="n">
@@ -16170,9 +14127,6 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
-      <c r="E684" t="inlineStr"/>
-      <c r="F684" t="inlineStr"/>
-      <c r="G684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="n">
@@ -16193,9 +14147,6 @@
           <t>مبني وشغال فعليًا — dashboard.health</t>
         </is>
       </c>
-      <c r="E685" t="inlineStr"/>
-      <c r="F685" t="inlineStr"/>
-      <c r="G685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="n">
@@ -16216,9 +14167,6 @@
           <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
-      <c r="E686" t="inlineStr"/>
-      <c r="F686" t="inlineStr"/>
-      <c r="G686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="n">
@@ -16239,9 +14187,6 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
-      <c r="E687" t="inlineStr"/>
-      <c r="F687" t="inlineStr"/>
-      <c r="G687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="n">
@@ -16262,9 +14207,6 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
-      <c r="E688" t="inlineStr"/>
-      <c r="F688" t="inlineStr"/>
-      <c r="G688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="n">
@@ -16285,9 +14227,6 @@
           <t>مبني وشغال فعليًا — platform_api.drawdown_status</t>
         </is>
       </c>
-      <c r="E689" t="inlineStr"/>
-      <c r="F689" t="inlineStr"/>
-      <c r="G689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="n">
@@ -16308,9 +14247,6 @@
           <t>مبني وشغال فعليًا — bd_platform.security_trust_data_layer.list_etherscan_watchlist_246 via platform_api/oracle/on-chain/watch</t>
         </is>
       </c>
-      <c r="E690" t="inlineStr"/>
-      <c r="F690" t="inlineStr"/>
-      <c r="G690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="n">
@@ -16331,9 +14267,6 @@
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
-      <c r="E691" t="inlineStr"/>
-      <c r="F691" t="inlineStr"/>
-      <c r="G691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="n">
@@ -16354,9 +14287,6 @@
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
-      <c r="E692" t="inlineStr"/>
-      <c r="F692" t="inlineStr"/>
-      <c r="G692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="n">
@@ -16377,9 +14307,6 @@
           <t>مبني وشغال فعليًا — platform_universe.build_manifest_universe_block</t>
         </is>
       </c>
-      <c r="E693" t="inlineStr"/>
-      <c r="F693" t="inlineStr"/>
-      <c r="G693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="n">
@@ -16400,9 +14327,6 @@
           <t>مبني جزئيًا — EXTERNAL_BLOCKED — Polygon.io API license requires human vendor contract; proxy: bd_platform/oneinch_connector.py</t>
         </is>
       </c>
-      <c r="E694" t="inlineStr"/>
-      <c r="F694" t="inlineStr"/>
-      <c r="G694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="n">
@@ -16423,9 +14347,6 @@
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
-      <c r="E695" t="inlineStr"/>
-      <c r="F695" t="inlineStr"/>
-      <c r="G695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="n">
@@ -16446,9 +14367,6 @@
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
-      <c r="E696" t="inlineStr"/>
-      <c r="F696" t="inlineStr"/>
-      <c r="G696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="n">
@@ -16469,9 +14387,6 @@
           <t>مبني وشغال فعليًا — data_sources_registry.registry_summary</t>
         </is>
       </c>
-      <c r="E697" t="inlineStr"/>
-      <c r="F697" t="inlineStr"/>
-      <c r="G697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="n">
@@ -16492,9 +14407,6 @@
           <t>مبني وشغال فعليًا — graphql_schema.graphql_health</t>
         </is>
       </c>
-      <c r="E698" t="inlineStr"/>
-      <c r="F698" t="inlineStr"/>
-      <c r="G698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="n">
@@ -16515,9 +14427,6 @@
           <t>مبني وشغال فعليًا — onchain_tracker.build_onchain_context_safe</t>
         </is>
       </c>
-      <c r="E699" t="inlineStr"/>
-      <c r="F699" t="inlineStr"/>
-      <c r="G699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="n">
@@ -16538,9 +14447,6 @@
           <t>مبني وشغال فعليًا — bd_platform.arbitrage_portfolio_ux_layer.b2b_fund_integration_status_183 via platform_api/business/b2b-fund-integration-status</t>
         </is>
       </c>
-      <c r="E700" t="inlineStr"/>
-      <c r="F700" t="inlineStr"/>
-      <c r="G700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="n">
@@ -16561,9 +14467,6 @@
           <t>مبني وشغال فعليًا — bd_platform.pro_trader_layer.build_whale_narrative_71</t>
         </is>
       </c>
-      <c r="E701" t="inlineStr"/>
-      <c r="F701" t="inlineStr"/>
-      <c r="G701" t="inlineStr"/>
     </row>
     <row r="702">
 